--- a/CF.xlsx
+++ b/CF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcelo.dilena\Desktop\CF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E9AF90-6599-469F-A9E0-8B8D1F06E195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FADDC6-6050-4606-8608-1D4C12F3CD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77BA92B8-604E-40A7-9BF0-42801C1F048B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="84">
   <si>
     <t>Descrição</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>Doce Festa</t>
+  </si>
+  <si>
+    <t>HAVAN (BLOCOS JULIA)</t>
   </si>
 </sst>
 </file>
@@ -1079,7 +1082,7 @@
       </c>
       <c r="D4" s="2">
         <f>'Nubank M'!C1+'Nubank V'!C1+'C6'!C1+CONTAS!C1</f>
-        <v>-10988.339999999998</v>
+        <v>-11068.329999999998</v>
       </c>
       <c r="E4" s="2">
         <f>'Nubank M'!D1+'Nubank V'!D1+'C6'!D1+CONTAS!D1</f>
@@ -1189,7 +1192,7 @@
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>1495.2900000000027</v>
+        <v>1415.3000000000029</v>
       </c>
       <c r="E8" s="4">
         <f t="shared" si="0"/>
@@ -10129,7 +10132,7 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C61)</f>
-        <v>-3463.89</v>
+        <v>-3543.8799999999997</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
@@ -10472,7 +10475,12 @@
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C24" s="2"/>
+      <c r="A24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="2">
+        <v>-79.989999999999995</v>
+      </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>

--- a/CF.xlsx
+++ b/CF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcelo.dilena\Desktop\CF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FADDC6-6050-4606-8608-1D4C12F3CD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E9D2B0-9BB3-4091-8D3B-5507F855A3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77BA92B8-604E-40A7-9BF0-42801C1F048B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="86">
   <si>
     <t>Descrição</t>
   </si>
@@ -294,6 +294,12 @@
   </si>
   <si>
     <t>HAVAN (BLOCOS JULIA)</t>
+  </si>
+  <si>
+    <t>Shopee</t>
+  </si>
+  <si>
+    <t>SHOPEE</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1088,7 @@
       </c>
       <c r="D4" s="2">
         <f>'Nubank M'!C1+'Nubank V'!C1+'C6'!C1+CONTAS!C1</f>
-        <v>-11068.329999999998</v>
+        <v>-11103.32</v>
       </c>
       <c r="E4" s="2">
         <f>'Nubank M'!D1+'Nubank V'!D1+'C6'!D1+CONTAS!D1</f>
@@ -1192,7 +1198,7 @@
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>1415.3000000000029</v>
+        <v>1380.3100000000013</v>
       </c>
       <c r="E8" s="4">
         <f t="shared" si="0"/>
@@ -7133,7 +7139,7 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C72)</f>
-        <v>-555.20000000000005</v>
+        <v>-570.19000000000005</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
@@ -7284,7 +7290,12 @@
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C10" s="2"/>
+      <c r="A10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="2">
+        <v>-14.99</v>
+      </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -10132,7 +10143,7 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C61)</f>
-        <v>-3543.8799999999997</v>
+        <v>-3563.8799999999997</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
@@ -10487,7 +10498,12 @@
       <c r="G24" s="2"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C25" s="2"/>
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="2">
+        <v>-20</v>
+      </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>

--- a/CF.xlsx
+++ b/CF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcelo.dilena\Desktop\CF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E9D2B0-9BB3-4091-8D3B-5507F855A3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0999B9E7-B481-4F46-BC40-EA9C91959EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77BA92B8-604E-40A7-9BF0-42801C1F048B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="91">
   <si>
     <t>Descrição</t>
   </si>
@@ -301,6 +301,21 @@
   <si>
     <t>SHOPEE</t>
   </si>
+  <si>
+    <t>CHAVEIRO</t>
+  </si>
+  <si>
+    <t>Vacina Laila</t>
+  </si>
+  <si>
+    <t>Espetinho Renal</t>
+  </si>
+  <si>
+    <t>Ifood</t>
+  </si>
+  <si>
+    <t>Mercado</t>
+  </si>
 </sst>
 </file>
 
@@ -536,13 +551,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -571,9 +589,6 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -588,82 +603,82 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}" name="Tabela3" displayName="Tabela3" ref="B2:H8" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}" name="Tabela3" displayName="Tabela3" ref="B2:H8" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="B2:H8" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{58D126D3-568C-4239-BE5B-8ECB2D761C36}" name="DESCRIÇÃO" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{1F251373-CBF5-4FD2-A8E8-CF6062FD64F2}" name="Março" dataDxfId="47">
+    <tableColumn id="1" xr3:uid="{58D126D3-568C-4239-BE5B-8ECB2D761C36}" name="DESCRIÇÃO" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{1F251373-CBF5-4FD2-A8E8-CF6062FD64F2}" name="Março" dataDxfId="40">
       <calculatedColumnFormula>'Nubank M'!#REF!</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{608B1772-8BF8-49B0-8AFC-DEE0FB385234}" name="Agosto" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{460D0C88-9D72-4E82-9E1F-AAB479149278}" name="Setembro" dataDxfId="45"/>
-    <tableColumn id="9" xr3:uid="{23262E17-D89E-4C5C-B21A-AA6FC4C1D40C}" name="Outubro" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{E80B29F7-DE09-4634-94B9-3F39D450DCAB}" name="Novembro" dataDxfId="43"/>
-    <tableColumn id="11" xr3:uid="{4129935B-5A93-47DA-AEA2-4182BB765146}" name="Dezembro" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{608B1772-8BF8-49B0-8AFC-DEE0FB385234}" name="Agosto" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{460D0C88-9D72-4E82-9E1F-AAB479149278}" name="Setembro" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{23262E17-D89E-4C5C-B21A-AA6FC4C1D40C}" name="Outubro" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{E80B29F7-DE09-4634-94B9-3F39D450DCAB}" name="Novembro" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{4129935B-5A93-47DA-AEA2-4182BB765146}" name="Dezembro" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07287E34-3C32-457D-AAFA-84A213BA4A5A}" name="Tabela13" displayName="Tabela13" ref="A2:G13" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07287E34-3C32-457D-AAFA-84A213BA4A5A}" name="Tabela13" displayName="Tabela13" ref="A2:G13" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
   <autoFilter ref="A2:G13" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{DCAB2E16-31E8-4D04-8D57-D2E5DE1C2D43}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{3D8A892C-E943-4ADC-99A7-8AD45EE19110}" name="Etiqueta"/>
-    <tableColumn id="8" xr3:uid="{79A6E2B3-690F-41B1-9D52-A513160176B5}" name="Agosto" dataDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{238D4DE7-9EC7-4216-9399-4E8F8C6AB056}" name="Setembro" dataDxfId="38"/>
-    <tableColumn id="10" xr3:uid="{C47303D5-51F9-45CA-9893-ECCF6302049A}" name="Outubro" dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{F025E820-7D9B-4E4E-975D-064D86088E6B}" name="Novembro" dataDxfId="36"/>
-    <tableColumn id="12" xr3:uid="{3257B979-DC12-48AF-ADD1-57C50933386F}" name="Dezembro" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{79A6E2B3-690F-41B1-9D52-A513160176B5}" name="Agosto" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{238D4DE7-9EC7-4216-9399-4E8F8C6AB056}" name="Setembro" dataDxfId="31"/>
+    <tableColumn id="10" xr3:uid="{C47303D5-51F9-45CA-9893-ECCF6302049A}" name="Outubro" dataDxfId="30"/>
+    <tableColumn id="11" xr3:uid="{F025E820-7D9B-4E4E-975D-064D86088E6B}" name="Novembro" dataDxfId="29"/>
+    <tableColumn id="12" xr3:uid="{3257B979-DC12-48AF-ADD1-57C50933386F}" name="Dezembro" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}" name="Tabela1" displayName="Tabela1" ref="A2:G33" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}" name="Tabela1" displayName="Tabela1" ref="A2:G33" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A2:G33" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{C87F2D82-D889-44BD-B683-F742DA7A464D}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{0E8E6474-9FDD-4A00-9A17-A21C82D5D587}" name="Etiqueta"/>
-    <tableColumn id="8" xr3:uid="{7862103E-D3DD-4DBC-A949-CAD0F6635209}" name="Agosto" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{3B6669B4-3F3F-4630-B924-79DF6A7F7F62}" name="Setembro" dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{14FB9208-D81C-4F3A-B267-6330F6D0C538}" name="Outubro" dataDxfId="30"/>
-    <tableColumn id="11" xr3:uid="{6233639A-A9AB-4395-B906-D5078629897E}" name="Novembro" dataDxfId="29"/>
-    <tableColumn id="12" xr3:uid="{C439927D-5643-4771-B3A5-8D95278E13CB}" name="Dezembro" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{7862103E-D3DD-4DBC-A949-CAD0F6635209}" name="Agosto" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{3B6669B4-3F3F-4630-B924-79DF6A7F7F62}" name="Setembro" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{14FB9208-D81C-4F3A-B267-6330F6D0C538}" name="Outubro" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{6233639A-A9AB-4395-B906-D5078629897E}" name="Novembro" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{C439927D-5643-4771-B3A5-8D95278E13CB}" name="Dezembro" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8C70EA2E-3E0C-43D6-9BC8-DC48D3EA5D71}" name="Tabela16" displayName="Tabela16" ref="A2:G22" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8C70EA2E-3E0C-43D6-9BC8-DC48D3EA5D71}" name="Tabela16" displayName="Tabela16" ref="A2:G22" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="A2:G22" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{22A6603B-5472-41A0-9FE9-85A4D0D9BBEE}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{06CEE4B6-AC33-4E62-9594-04D875A198B2}" name="Etiqueta"/>
-    <tableColumn id="8" xr3:uid="{2656ECEA-2193-4302-A2B8-E5E698D3100B}" name="Agosto" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{75A68C75-5CA6-4D2D-9E9F-4937EA24AB5F}" name="Setembro" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{194CFE84-FB4C-4B9B-B080-CDC3D8C87B60}" name="Outubro" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{7BCDD7DE-693C-49E3-BE77-A773DD3F9C6D}" name="Novembro" dataDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{6AD89F40-09D6-41BD-86DC-C8B11C25AAE5}" name="Dezembro" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{2656ECEA-2193-4302-A2B8-E5E698D3100B}" name="Agosto" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{75A68C75-5CA6-4D2D-9E9F-4937EA24AB5F}" name="Setembro" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{194CFE84-FB4C-4B9B-B080-CDC3D8C87B60}" name="Outubro" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{7BCDD7DE-693C-49E3-BE77-A773DD3F9C6D}" name="Novembro" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{6AD89F40-09D6-41BD-86DC-C8B11C25AAE5}" name="Dezembro" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{578AF0ED-5772-4022-8C30-EC0F3D1A9977}" name="Tabela167" displayName="Tabela167" ref="A2:G32" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{578AF0ED-5772-4022-8C30-EC0F3D1A9977}" name="Tabela167" displayName="Tabela167" ref="A2:G32" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
   <autoFilter ref="A2:G32" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{4228253B-5CDE-4046-B86A-62CA3FEFCC45}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{FB9FB8A1-7786-42A2-8D12-2078EB6F038D}" name="Etiqueta"/>
-    <tableColumn id="8" xr3:uid="{AF93C4B2-2123-4A55-8BF7-D31E5E1A098B}" name="Agosto" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{578EBB3E-CFFD-4504-AD40-629D4AF624D5}" name="Setembro" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{6A1DAFCF-51CB-4511-A4D6-00F9ACEC373F}" name="Outubro" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{A7544E74-4742-4201-99B7-579A2AAF4EA6}" name="Novembro" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{2FB52C65-8F63-4EB5-88CF-20854E86EB8D}" name="Dezembro" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{AF93C4B2-2123-4A55-8BF7-D31E5E1A098B}" name="Agosto" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{578EBB3E-CFFD-4504-AD40-629D4AF624D5}" name="Setembro" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{6A1DAFCF-51CB-4511-A4D6-00F9ACEC373F}" name="Outubro" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{A7544E74-4742-4201-99B7-579A2AAF4EA6}" name="Novembro" dataDxfId="45"/>
+    <tableColumn id="12" xr3:uid="{2FB52C65-8F63-4EB5-88CF-20854E86EB8D}" name="Dezembro" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1088,23 +1103,23 @@
       </c>
       <c r="D4" s="2">
         <f>'Nubank M'!C1+'Nubank V'!C1+'C6'!C1+CONTAS!C1</f>
-        <v>-11103.32</v>
+        <v>-11557.23</v>
       </c>
       <c r="E4" s="2">
         <f>'Nubank M'!D1+'Nubank V'!D1+'C6'!D1+CONTAS!D1</f>
-        <v>-7264.19</v>
+        <v>-7286.82</v>
       </c>
       <c r="F4" s="2">
         <f>'Nubank M'!E1+'Nubank V'!E1+'C6'!E1+CONTAS!E1</f>
-        <v>-5583.5999999999995</v>
+        <v>-5606.23</v>
       </c>
       <c r="G4" s="2">
         <f>'Nubank M'!F1+'Nubank V'!F1+'C6'!F1+CONTAS!F1</f>
-        <v>-5448.15</v>
+        <v>-5470.7799999999988</v>
       </c>
       <c r="H4" s="2">
         <f>'Nubank M'!G1+'Nubank V'!G1+'C6'!G1+CONTAS!G1</f>
-        <v>-5100.1499999999996</v>
+        <v>-5122.7799999999988</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
@@ -1117,7 +1132,7 @@
       </c>
       <c r="D5" s="2">
         <f>PREVISÃO!C3</f>
-        <v>-1200</v>
+        <v>-1142.01</v>
       </c>
       <c r="E5" s="2">
         <f>PREVISÃO!D3</f>
@@ -1198,23 +1213,23 @@
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>1380.3100000000013</v>
+        <v>984.39000000000124</v>
       </c>
       <c r="E8" s="4">
         <f t="shared" si="0"/>
-        <v>3567.4700000000012</v>
+        <v>3544.84</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="0"/>
-        <v>4091.5299999999988</v>
+        <v>4068.8999999999996</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
-        <v>4226.9799999999996</v>
+        <v>4204.3500000000004</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="0"/>
-        <v>4574.9799999999996</v>
+        <v>4552.3500000000004</v>
       </c>
     </row>
   </sheetData>
@@ -4174,7 +4189,7 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C55)</f>
-        <v>-2394.2799999999997</v>
+        <v>-2428.5699999999997</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
@@ -4500,7 +4515,12 @@
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C23" s="2"/>
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="2">
+        <v>-34.29</v>
+      </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -7139,7 +7159,7 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C72)</f>
-        <v>-570.19000000000005</v>
+        <v>-628.18000000000006</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
@@ -7302,7 +7322,12 @@
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C11" s="2"/>
+      <c r="A11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="2">
+        <v>-57.99</v>
+      </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -10143,23 +10168,23 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C61)</f>
-        <v>-3563.8799999999997</v>
+        <v>-3925.5099999999998</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>-1497.81</v>
+        <v>-1520.44</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
-        <v>-823.76</v>
+        <v>-846.39</v>
       </c>
       <c r="F1" s="2">
         <f t="shared" si="0"/>
-        <v>-743.77</v>
+        <v>-766.4</v>
       </c>
       <c r="G1" s="2">
         <f t="shared" si="0"/>
-        <v>-743.77</v>
+        <v>-766.4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -10374,19 +10399,19 @@
         <v>35</v>
       </c>
       <c r="C15" s="2">
-        <v>-108.88</v>
+        <v>-131.51</v>
       </c>
       <c r="D15" s="2">
-        <v>-108.88</v>
+        <v>-131.51</v>
       </c>
       <c r="E15" s="2">
-        <v>-108.88</v>
+        <v>-131.51</v>
       </c>
       <c r="F15" s="2">
-        <v>-108.88</v>
+        <v>-131.51</v>
       </c>
       <c r="G15" s="2">
-        <v>-108.88</v>
+        <v>-131.51</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -10502,7 +10527,7 @@
         <v>85</v>
       </c>
       <c r="C25" s="2">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -10510,21 +10535,36 @@
       <c r="G25" s="2"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C26" s="2"/>
+      <c r="A26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="2">
+        <v>-15</v>
+      </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C27" s="2"/>
+      <c r="A27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="2">
+        <v>-100</v>
+      </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C28" s="2"/>
+      <c r="A28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="2">
+        <v>-225</v>
+      </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -16341,7 +16381,7 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C58)</f>
-        <v>-1750</v>
+        <v>-1692.01</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
@@ -16388,7 +16428,8 @@
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>-1200</v>
+        <f>(-1200+57.99)</f>
+        <v>-1142.01</v>
       </c>
       <c r="D3" s="2">
         <v>-2000</v>

--- a/CF.xlsx
+++ b/CF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcelo.dilena\Desktop\CF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0999B9E7-B481-4F46-BC40-EA9C91959EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAA615E-A1C6-4BD8-9549-B22FBF5E799C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77BA92B8-604E-40A7-9BF0-42801C1F048B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="1" xr2:uid="{77BA92B8-604E-40A7-9BF0-42801C1F048B}"/>
   </bookViews>
   <sheets>
     <sheet name="DashBord" sheetId="3" r:id="rId1"/>
@@ -26,23 +26,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="105">
   <si>
     <t>Descrição</t>
   </si>
@@ -316,6 +305,48 @@
   <si>
     <t>Mercado</t>
   </si>
+  <si>
+    <t>Uber</t>
+  </si>
+  <si>
+    <t>Havan</t>
+  </si>
+  <si>
+    <t>Dona do Bolo</t>
+  </si>
+  <si>
+    <t>Ração</t>
+  </si>
+  <si>
+    <t>Salgado</t>
+  </si>
+  <si>
+    <t>Queijo</t>
+  </si>
+  <si>
+    <t>Gilete</t>
+  </si>
+  <si>
+    <t>Palmem</t>
+  </si>
+  <si>
+    <t>Mercado Livre</t>
+  </si>
+  <si>
+    <t>Pimpinela</t>
+  </si>
+  <si>
+    <t>Paulistão</t>
+  </si>
+  <si>
+    <t>Cenourão</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Marmita</t>
+  </si>
 </sst>
 </file>
 
@@ -551,16 +582,13 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -589,6 +617,9 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -603,82 +634,82 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}" name="Tabela3" displayName="Tabela3" ref="B2:H8" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}" name="Tabela3" displayName="Tabela3" ref="B2:H8" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
   <autoFilter ref="B2:H8" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{58D126D3-568C-4239-BE5B-8ECB2D761C36}" name="DESCRIÇÃO" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{1F251373-CBF5-4FD2-A8E8-CF6062FD64F2}" name="Março" dataDxfId="40">
+    <tableColumn id="1" xr3:uid="{58D126D3-568C-4239-BE5B-8ECB2D761C36}" name="DESCRIÇÃO" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{1F251373-CBF5-4FD2-A8E8-CF6062FD64F2}" name="Março" dataDxfId="47">
       <calculatedColumnFormula>'Nubank M'!#REF!</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{608B1772-8BF8-49B0-8AFC-DEE0FB385234}" name="Agosto" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{460D0C88-9D72-4E82-9E1F-AAB479149278}" name="Setembro" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{23262E17-D89E-4C5C-B21A-AA6FC4C1D40C}" name="Outubro" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{E80B29F7-DE09-4634-94B9-3F39D450DCAB}" name="Novembro" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{4129935B-5A93-47DA-AEA2-4182BB765146}" name="Dezembro" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{608B1772-8BF8-49B0-8AFC-DEE0FB385234}" name="Agosto" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{460D0C88-9D72-4E82-9E1F-AAB479149278}" name="Setembro" dataDxfId="45"/>
+    <tableColumn id="9" xr3:uid="{23262E17-D89E-4C5C-B21A-AA6FC4C1D40C}" name="Outubro" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{E80B29F7-DE09-4634-94B9-3F39D450DCAB}" name="Novembro" dataDxfId="43"/>
+    <tableColumn id="11" xr3:uid="{4129935B-5A93-47DA-AEA2-4182BB765146}" name="Dezembro" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07287E34-3C32-457D-AAFA-84A213BA4A5A}" name="Tabela13" displayName="Tabela13" ref="A2:G13" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07287E34-3C32-457D-AAFA-84A213BA4A5A}" name="Tabela13" displayName="Tabela13" ref="A2:G13" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
   <autoFilter ref="A2:G13" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{DCAB2E16-31E8-4D04-8D57-D2E5DE1C2D43}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{3D8A892C-E943-4ADC-99A7-8AD45EE19110}" name="Etiqueta"/>
-    <tableColumn id="8" xr3:uid="{79A6E2B3-690F-41B1-9D52-A513160176B5}" name="Agosto" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{238D4DE7-9EC7-4216-9399-4E8F8C6AB056}" name="Setembro" dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{C47303D5-51F9-45CA-9893-ECCF6302049A}" name="Outubro" dataDxfId="30"/>
-    <tableColumn id="11" xr3:uid="{F025E820-7D9B-4E4E-975D-064D86088E6B}" name="Novembro" dataDxfId="29"/>
-    <tableColumn id="12" xr3:uid="{3257B979-DC12-48AF-ADD1-57C50933386F}" name="Dezembro" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{79A6E2B3-690F-41B1-9D52-A513160176B5}" name="Agosto" dataDxfId="39"/>
+    <tableColumn id="9" xr3:uid="{238D4DE7-9EC7-4216-9399-4E8F8C6AB056}" name="Setembro" dataDxfId="38"/>
+    <tableColumn id="10" xr3:uid="{C47303D5-51F9-45CA-9893-ECCF6302049A}" name="Outubro" dataDxfId="37"/>
+    <tableColumn id="11" xr3:uid="{F025E820-7D9B-4E4E-975D-064D86088E6B}" name="Novembro" dataDxfId="36"/>
+    <tableColumn id="12" xr3:uid="{3257B979-DC12-48AF-ADD1-57C50933386F}" name="Dezembro" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}" name="Tabela1" displayName="Tabela1" ref="A2:G33" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A2:G33" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}" name="Tabela1" displayName="Tabela1" ref="A2:G36" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+  <autoFilter ref="A2:G36" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{C87F2D82-D889-44BD-B683-F742DA7A464D}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{0E8E6474-9FDD-4A00-9A17-A21C82D5D587}" name="Etiqueta"/>
-    <tableColumn id="8" xr3:uid="{7862103E-D3DD-4DBC-A949-CAD0F6635209}" name="Agosto" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{3B6669B4-3F3F-4630-B924-79DF6A7F7F62}" name="Setembro" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{14FB9208-D81C-4F3A-B267-6330F6D0C538}" name="Outubro" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{6233639A-A9AB-4395-B906-D5078629897E}" name="Novembro" dataDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{C439927D-5643-4771-B3A5-8D95278E13CB}" name="Dezembro" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{7862103E-D3DD-4DBC-A949-CAD0F6635209}" name="Agosto" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{3B6669B4-3F3F-4630-B924-79DF6A7F7F62}" name="Setembro" dataDxfId="31"/>
+    <tableColumn id="10" xr3:uid="{14FB9208-D81C-4F3A-B267-6330F6D0C538}" name="Outubro" dataDxfId="30"/>
+    <tableColumn id="11" xr3:uid="{6233639A-A9AB-4395-B906-D5078629897E}" name="Novembro" dataDxfId="29"/>
+    <tableColumn id="12" xr3:uid="{C439927D-5643-4771-B3A5-8D95278E13CB}" name="Dezembro" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8C70EA2E-3E0C-43D6-9BC8-DC48D3EA5D71}" name="Tabela16" displayName="Tabela16" ref="A2:G22" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8C70EA2E-3E0C-43D6-9BC8-DC48D3EA5D71}" name="Tabela16" displayName="Tabela16" ref="A2:G22" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A2:G22" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{22A6603B-5472-41A0-9FE9-85A4D0D9BBEE}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{06CEE4B6-AC33-4E62-9594-04D875A198B2}" name="Etiqueta"/>
-    <tableColumn id="8" xr3:uid="{2656ECEA-2193-4302-A2B8-E5E698D3100B}" name="Agosto" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{75A68C75-5CA6-4D2D-9E9F-4937EA24AB5F}" name="Setembro" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{194CFE84-FB4C-4B9B-B080-CDC3D8C87B60}" name="Outubro" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{7BCDD7DE-693C-49E3-BE77-A773DD3F9C6D}" name="Novembro" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{6AD89F40-09D6-41BD-86DC-C8B11C25AAE5}" name="Dezembro" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{2656ECEA-2193-4302-A2B8-E5E698D3100B}" name="Agosto" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{75A68C75-5CA6-4D2D-9E9F-4937EA24AB5F}" name="Setembro" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{194CFE84-FB4C-4B9B-B080-CDC3D8C87B60}" name="Outubro" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{7BCDD7DE-693C-49E3-BE77-A773DD3F9C6D}" name="Novembro" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{6AD89F40-09D6-41BD-86DC-C8B11C25AAE5}" name="Dezembro" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{578AF0ED-5772-4022-8C30-EC0F3D1A9977}" name="Tabela167" displayName="Tabela167" ref="A2:G32" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
-  <autoFilter ref="A2:G32" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{578AF0ED-5772-4022-8C30-EC0F3D1A9977}" name="Tabela167" displayName="Tabela167" ref="A2:G42" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="A2:G42" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{4228253B-5CDE-4046-B86A-62CA3FEFCC45}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{FB9FB8A1-7786-42A2-8D12-2078EB6F038D}" name="Etiqueta"/>
-    <tableColumn id="8" xr3:uid="{AF93C4B2-2123-4A55-8BF7-D31E5E1A098B}" name="Agosto" dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{578EBB3E-CFFD-4504-AD40-629D4AF624D5}" name="Setembro" dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{6A1DAFCF-51CB-4511-A4D6-00F9ACEC373F}" name="Outubro" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{A7544E74-4742-4201-99B7-579A2AAF4EA6}" name="Novembro" dataDxfId="45"/>
-    <tableColumn id="12" xr3:uid="{2FB52C65-8F63-4EB5-88CF-20854E86EB8D}" name="Dezembro" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{AF93C4B2-2123-4A55-8BF7-D31E5E1A098B}" name="Agosto" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{578EBB3E-CFFD-4504-AD40-629D4AF624D5}" name="Setembro" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{6A1DAFCF-51CB-4511-A4D6-00F9ACEC373F}" name="Outubro" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{A7544E74-4742-4201-99B7-579A2AAF4EA6}" name="Novembro" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{2FB52C65-8F63-4EB5-88CF-20854E86EB8D}" name="Dezembro" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1074,7 +1105,7 @@
       </c>
       <c r="D3" s="2">
         <f>Receita!C1</f>
-        <v>18233.63</v>
+        <v>17818.68</v>
       </c>
       <c r="E3" s="2">
         <f>Receita!D1</f>
@@ -1103,23 +1134,23 @@
       </c>
       <c r="D4" s="2">
         <f>'Nubank M'!C1+'Nubank V'!C1+'C6'!C1+CONTAS!C1</f>
-        <v>-11557.23</v>
+        <v>-12503.63</v>
       </c>
       <c r="E4" s="2">
         <f>'Nubank M'!D1+'Nubank V'!D1+'C6'!D1+CONTAS!D1</f>
-        <v>-7286.82</v>
+        <v>-7344.2999999999993</v>
       </c>
       <c r="F4" s="2">
         <f>'Nubank M'!E1+'Nubank V'!E1+'C6'!E1+CONTAS!E1</f>
-        <v>-5606.23</v>
+        <v>-5620.1299999999992</v>
       </c>
       <c r="G4" s="2">
         <f>'Nubank M'!F1+'Nubank V'!F1+'C6'!F1+CONTAS!F1</f>
-        <v>-5470.7799999999988</v>
+        <v>-5484.6799999999994</v>
       </c>
       <c r="H4" s="2">
         <f>'Nubank M'!G1+'Nubank V'!G1+'C6'!G1+CONTAS!G1</f>
-        <v>-5122.7799999999988</v>
+        <v>-5136.6799999999994</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
@@ -1132,7 +1163,7 @@
       </c>
       <c r="D5" s="2">
         <f>PREVISÃO!C3</f>
-        <v>-1142.01</v>
+        <v>-800</v>
       </c>
       <c r="E5" s="2">
         <f>PREVISÃO!D3</f>
@@ -1161,7 +1192,7 @@
       </c>
       <c r="D6" s="2">
         <f>PREVISÃO!C4</f>
-        <v>-550</v>
+        <v>-394.87</v>
       </c>
       <c r="E6" s="2">
         <f>PREVISÃO!D4</f>
@@ -1188,7 +1219,7 @@
         <v>-4000</v>
       </c>
       <c r="D7" s="2">
-        <v>-4000</v>
+        <v>-3000</v>
       </c>
       <c r="E7" s="2">
         <v>-4000</v>
@@ -1213,23 +1244,23 @@
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>984.39000000000124</v>
+        <v>1120.1800000000012</v>
       </c>
       <c r="E8" s="4">
         <f t="shared" si="0"/>
-        <v>3544.84</v>
+        <v>3487.3600000000006</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="0"/>
-        <v>4068.8999999999996</v>
+        <v>4055</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
-        <v>4204.3500000000004</v>
+        <v>4190.4500000000007</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="0"/>
-        <v>4552.3500000000004</v>
+        <v>4538.4500000000007</v>
       </c>
     </row>
   </sheetData>
@@ -1253,7 +1284,7 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C59)</f>
-        <v>18233.63</v>
+        <v>17818.68</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
@@ -1417,9 +1448,7 @@
       <c r="A10" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="2">
-        <v>475.13</v>
-      </c>
+      <c r="C10" s="2"/>
       <c r="D10" s="2">
         <v>475.13</v>
       </c>
@@ -1446,7 +1475,12 @@
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C12" s="2"/>
+      <c r="A12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="2">
+        <v>60.18</v>
+      </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -4189,11 +4223,11 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C55)</f>
-        <v>-2428.5699999999997</v>
+        <v>-3044.5299999999997</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>-680.18000000000006</v>
+        <v>-723.7600000000001</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
@@ -4527,174 +4561,244 @@
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C24" s="2"/>
+      <c r="A24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="2">
+        <v>-19.98</v>
+      </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C25" s="2"/>
+      <c r="A25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" s="2">
+        <v>-27</v>
+      </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="A26" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="2">
+        <v>-43.58</v>
+      </c>
+      <c r="D26" s="2">
+        <v>-43.58</v>
+      </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C27" s="2"/>
+      <c r="A27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" s="2">
+        <v>-70</v>
+      </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C28" s="2"/>
+      <c r="A28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="2">
+        <v>-60.18</v>
+      </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C29" s="2"/>
+      <c r="A29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="2">
+        <v>-36</v>
+      </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C30" s="2"/>
+      <c r="A30" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="2">
+        <v>-15</v>
+      </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C31" s="2"/>
+      <c r="A31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="2">
+        <v>-53.54</v>
+      </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C32" s="2"/>
+      <c r="A32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="2">
+        <v>-33.82</v>
+      </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C33" s="2"/>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="2">
+        <v>-20</v>
+      </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C34" s="2"/>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="2">
+        <v>-51.98</v>
+      </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C35" s="2"/>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" s="2">
+        <v>-17.98</v>
+      </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C36" s="2"/>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="2">
+        <v>-166.9</v>
+      </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -10157,7 +10261,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37F3A864-C585-421C-A8F8-7E679BFCCC8A}">
-  <dimension ref="A1:G402"/>
+  <dimension ref="A1:G412"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" customWidth="1"/>
@@ -10167,24 +10271,24 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
-        <f t="shared" ref="C1:G1" si="0">SUM(C3:C61)</f>
-        <v>-3925.5099999999998</v>
+        <f t="shared" ref="C1:G1" si="0">SUM(C3:C71)</f>
+        <v>-4731.0999999999995</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>-1520.44</v>
+        <v>-1534.3400000000001</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
-        <v>-846.39</v>
+        <v>-860.29</v>
       </c>
       <c r="F1" s="2">
         <f t="shared" si="0"/>
-        <v>-766.4</v>
+        <v>-780.3</v>
       </c>
       <c r="G1" s="2">
         <f t="shared" si="0"/>
-        <v>-766.4</v>
+        <v>-780.3</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -10571,139 +10675,182 @@
       <c r="G28" s="2"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C29" s="2"/>
+      <c r="A29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="2">
+        <v>-115.41</v>
+      </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C30" s="2"/>
+      <c r="A30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="2">
+        <v>-21.9</v>
+      </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C31" s="2"/>
+      <c r="A31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="2">
+        <v>-92.62</v>
+      </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C32" s="2"/>
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="2">
+        <v>-155.13</v>
+      </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C33" s="2"/>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="2">
+        <v>-376.63</v>
+      </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C35" s="2"/>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" s="2">
+        <v>-13.9</v>
+      </c>
+      <c r="D34" s="2">
+        <v>-13.9</v>
+      </c>
+      <c r="E34" s="2">
+        <v>-13.9</v>
+      </c>
+      <c r="F34" s="2">
+        <v>-13.9</v>
+      </c>
+      <c r="G34" s="2">
+        <v>-13.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="2">
+        <v>-30</v>
+      </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -13187,6 +13334,76 @@
       <c r="E402" s="2"/>
       <c r="F402" s="2"/>
       <c r="G402" s="2"/>
+    </row>
+    <row r="403" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C403" s="2"/>
+      <c r="D403" s="2"/>
+      <c r="E403" s="2"/>
+      <c r="F403" s="2"/>
+      <c r="G403" s="2"/>
+    </row>
+    <row r="404" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C404" s="2"/>
+      <c r="D404" s="2"/>
+      <c r="E404" s="2"/>
+      <c r="F404" s="2"/>
+      <c r="G404" s="2"/>
+    </row>
+    <row r="405" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C405" s="2"/>
+      <c r="D405" s="2"/>
+      <c r="E405" s="2"/>
+      <c r="F405" s="2"/>
+      <c r="G405" s="2"/>
+    </row>
+    <row r="406" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C406" s="2"/>
+      <c r="D406" s="2"/>
+      <c r="E406" s="2"/>
+      <c r="F406" s="2"/>
+      <c r="G406" s="2"/>
+    </row>
+    <row r="407" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C407" s="2"/>
+      <c r="D407" s="2"/>
+      <c r="E407" s="2"/>
+      <c r="F407" s="2"/>
+      <c r="G407" s="2"/>
+    </row>
+    <row r="408" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C408" s="2"/>
+      <c r="D408" s="2"/>
+      <c r="E408" s="2"/>
+      <c r="F408" s="2"/>
+      <c r="G408" s="2"/>
+    </row>
+    <row r="409" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C409" s="2"/>
+      <c r="D409" s="2"/>
+      <c r="E409" s="2"/>
+      <c r="F409" s="2"/>
+      <c r="G409" s="2"/>
+    </row>
+    <row r="410" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C410" s="2"/>
+      <c r="D410" s="2"/>
+      <c r="E410" s="2"/>
+      <c r="F410" s="2"/>
+      <c r="G410" s="2"/>
+    </row>
+    <row r="411" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C411" s="2"/>
+      <c r="D411" s="2"/>
+      <c r="E411" s="2"/>
+      <c r="F411" s="2"/>
+      <c r="G411" s="2"/>
+    </row>
+    <row r="412" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C412" s="2"/>
+      <c r="D412" s="2"/>
+      <c r="E412" s="2"/>
+      <c r="F412" s="2"/>
+      <c r="G412" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -13209,7 +13426,7 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C76)</f>
-        <v>-4574.9699999999993</v>
+        <v>-4099.82</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
@@ -13275,9 +13492,7 @@
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2">
-        <v>-475.15</v>
-      </c>
+      <c r="C4" s="2"/>
       <c r="D4" s="2">
         <v>-475.15</v>
       </c>
@@ -16381,7 +16596,7 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C58)</f>
-        <v>-1692.01</v>
+        <v>-1194.8699999999999</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
@@ -16428,8 +16643,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <f>(-1200+57.99)</f>
-        <v>-1142.01</v>
+        <v>-800</v>
       </c>
       <c r="D3" s="2">
         <v>-2000</v>
@@ -16449,7 +16663,8 @@
         <v>41</v>
       </c>
       <c r="C4" s="2">
-        <v>-550</v>
+        <f>-(550-(155.13))</f>
+        <v>-394.87</v>
       </c>
       <c r="D4" s="2">
         <v>-600</v>

--- a/CF.xlsx
+++ b/CF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcelo.dilena\Desktop\CF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAA615E-A1C6-4BD8-9549-B22FBF5E799C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D5D9F14-82F6-4C28-82B6-470BD4745450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="1" xr2:uid="{77BA92B8-604E-40A7-9BF0-42801C1F048B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{77BA92B8-604E-40A7-9BF0-42801C1F048B}"/>
   </bookViews>
   <sheets>
     <sheet name="DashBord" sheetId="3" r:id="rId1"/>
@@ -26,12 +26,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="105">
   <si>
     <t>Descrição</t>
   </si>
@@ -261,9 +272,6 @@
     <t>ITENS FESTA JULIA</t>
   </si>
   <si>
-    <t>Roupa</t>
-  </si>
-  <si>
     <t>Renner</t>
   </si>
   <si>
@@ -347,6 +355,9 @@
   <si>
     <t>Marmita</t>
   </si>
+  <si>
+    <t>Botina Mercado Livre</t>
+  </si>
 </sst>
 </file>
 
@@ -386,12 +397,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -407,7 +424,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -425,38 +442,18 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{9058775E-F3AA-4FB6-A33D-2239824B6A96}"/>
   </cellStyles>
   <dxfs count="51">
-    <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -620,6 +617,32 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -634,42 +657,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}" name="Tabela3" displayName="Tabela3" ref="B2:H8" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}" name="Tabela3" displayName="Tabela3" ref="B2:H8" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="B2:H8" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{58D126D3-568C-4239-BE5B-8ECB2D761C36}" name="DESCRIÇÃO" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{1F251373-CBF5-4FD2-A8E8-CF6062FD64F2}" name="Março" dataDxfId="47">
+    <tableColumn id="1" xr3:uid="{58D126D3-568C-4239-BE5B-8ECB2D761C36}" name="DESCRIÇÃO" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{1F251373-CBF5-4FD2-A8E8-CF6062FD64F2}" name="Março" dataDxfId="40">
       <calculatedColumnFormula>'Nubank M'!#REF!</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{608B1772-8BF8-49B0-8AFC-DEE0FB385234}" name="Agosto" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{460D0C88-9D72-4E82-9E1F-AAB479149278}" name="Setembro" dataDxfId="45"/>
-    <tableColumn id="9" xr3:uid="{23262E17-D89E-4C5C-B21A-AA6FC4C1D40C}" name="Outubro" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{E80B29F7-DE09-4634-94B9-3F39D450DCAB}" name="Novembro" dataDxfId="43"/>
-    <tableColumn id="11" xr3:uid="{4129935B-5A93-47DA-AEA2-4182BB765146}" name="Dezembro" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{608B1772-8BF8-49B0-8AFC-DEE0FB385234}" name="Agosto" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{460D0C88-9D72-4E82-9E1F-AAB479149278}" name="Setembro" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{23262E17-D89E-4C5C-B21A-AA6FC4C1D40C}" name="Outubro" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{E80B29F7-DE09-4634-94B9-3F39D450DCAB}" name="Novembro" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{4129935B-5A93-47DA-AEA2-4182BB765146}" name="Dezembro" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07287E34-3C32-457D-AAFA-84A213BA4A5A}" name="Tabela13" displayName="Tabela13" ref="A2:G13" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07287E34-3C32-457D-AAFA-84A213BA4A5A}" name="Tabela13" displayName="Tabela13" ref="A2:G13" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
   <autoFilter ref="A2:G13" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{DCAB2E16-31E8-4D04-8D57-D2E5DE1C2D43}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{3D8A892C-E943-4ADC-99A7-8AD45EE19110}" name="Etiqueta"/>
-    <tableColumn id="8" xr3:uid="{79A6E2B3-690F-41B1-9D52-A513160176B5}" name="Agosto" dataDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{238D4DE7-9EC7-4216-9399-4E8F8C6AB056}" name="Setembro" dataDxfId="38"/>
-    <tableColumn id="10" xr3:uid="{C47303D5-51F9-45CA-9893-ECCF6302049A}" name="Outubro" dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{F025E820-7D9B-4E4E-975D-064D86088E6B}" name="Novembro" dataDxfId="36"/>
-    <tableColumn id="12" xr3:uid="{3257B979-DC12-48AF-ADD1-57C50933386F}" name="Dezembro" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{79A6E2B3-690F-41B1-9D52-A513160176B5}" name="Agosto" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{238D4DE7-9EC7-4216-9399-4E8F8C6AB056}" name="Setembro" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{C47303D5-51F9-45CA-9893-ECCF6302049A}" name="Outubro" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{F025E820-7D9B-4E4E-975D-064D86088E6B}" name="Novembro" dataDxfId="45"/>
+    <tableColumn id="12" xr3:uid="{3257B979-DC12-48AF-ADD1-57C50933386F}" name="Dezembro" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}" name="Tabela1" displayName="Tabela1" ref="A2:G36" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
-  <autoFilter ref="A2:G36" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}" name="Tabela1" displayName="Tabela1" ref="A2:G40" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+  <autoFilter ref="A2:G40" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{C87F2D82-D889-44BD-B683-F742DA7A464D}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{0E8E6474-9FDD-4A00-9A17-A21C82D5D587}" name="Etiqueta"/>
@@ -684,8 +707,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8C70EA2E-3E0C-43D6-9BC8-DC48D3EA5D71}" name="Tabela16" displayName="Tabela16" ref="A2:G22" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A2:G22" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8C70EA2E-3E0C-43D6-9BC8-DC48D3EA5D71}" name="Tabela16" displayName="Tabela16" ref="A2:G21" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="A2:G21" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{22A6603B-5472-41A0-9FE9-85A4D0D9BBEE}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{06CEE4B6-AC33-4E62-9594-04D875A198B2}" name="Etiqueta"/>
@@ -700,8 +723,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{578AF0ED-5772-4022-8C30-EC0F3D1A9977}" name="Tabela167" displayName="Tabela167" ref="A2:G42" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
-  <autoFilter ref="A2:G42" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{578AF0ED-5772-4022-8C30-EC0F3D1A9977}" name="Tabela167" displayName="Tabela167" ref="A2:G54" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="A2:G54" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{4228253B-5CDE-4046-B86A-62CA3FEFCC45}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{FB9FB8A1-7786-42A2-8D12-2078EB6F038D}" name="Etiqueta"/>
@@ -1105,7 +1128,7 @@
       </c>
       <c r="D3" s="2">
         <f>Receita!C1</f>
-        <v>17818.68</v>
+        <v>18118.68</v>
       </c>
       <c r="E3" s="2">
         <f>Receita!D1</f>
@@ -1134,23 +1157,23 @@
       </c>
       <c r="D4" s="2">
         <f>'Nubank M'!C1+'Nubank V'!C1+'C6'!C1+CONTAS!C1</f>
-        <v>-12503.63</v>
+        <v>-12638.01</v>
       </c>
       <c r="E4" s="2">
         <f>'Nubank M'!D1+'Nubank V'!D1+'C6'!D1+CONTAS!D1</f>
-        <v>-7344.2999999999993</v>
+        <v>-7315.4</v>
       </c>
       <c r="F4" s="2">
         <f>'Nubank M'!E1+'Nubank V'!E1+'C6'!E1+CONTAS!E1</f>
-        <v>-5620.1299999999992</v>
+        <v>-5675.48</v>
       </c>
       <c r="G4" s="2">
         <f>'Nubank M'!F1+'Nubank V'!F1+'C6'!F1+CONTAS!F1</f>
-        <v>-5484.6799999999994</v>
+        <v>-5540.0299999999988</v>
       </c>
       <c r="H4" s="2">
         <f>'Nubank M'!G1+'Nubank V'!G1+'C6'!G1+CONTAS!G1</f>
-        <v>-5136.6799999999994</v>
+        <v>-5192.0299999999988</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
@@ -1163,7 +1186,7 @@
       </c>
       <c r="D5" s="2">
         <f>PREVISÃO!C3</f>
-        <v>-800</v>
+        <v>-400</v>
       </c>
       <c r="E5" s="2">
         <f>PREVISÃO!D3</f>
@@ -1192,7 +1215,7 @@
       </c>
       <c r="D6" s="2">
         <f>PREVISÃO!C4</f>
-        <v>-394.87</v>
+        <v>-200</v>
       </c>
       <c r="E6" s="2">
         <f>PREVISÃO!D4</f>
@@ -1219,7 +1242,7 @@
         <v>-4000</v>
       </c>
       <c r="D7" s="2">
-        <v>-3000</v>
+        <v>-4000</v>
       </c>
       <c r="E7" s="2">
         <v>-4000</v>
@@ -1244,23 +1267,23 @@
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>1120.1800000000012</v>
+        <v>880.67000000000007</v>
       </c>
       <c r="E8" s="4">
         <f t="shared" si="0"/>
-        <v>3487.3600000000006</v>
+        <v>3516.26</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="0"/>
-        <v>4055</v>
+        <v>3999.6499999999996</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
-        <v>4190.4500000000007</v>
+        <v>4135.1000000000004</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="0"/>
-        <v>4538.4500000000007</v>
+        <v>4483.1000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -1284,7 +1307,7 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C59)</f>
-        <v>17818.68</v>
+        <v>18118.68</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
@@ -1446,7 +1469,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2">
@@ -1476,7 +1499,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>96</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
       </c>
       <c r="C12" s="2">
         <v>60.18</v>
@@ -1487,7 +1513,9 @@
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C13" s="2"/>
+      <c r="C13" s="2">
+        <v>300</v>
+      </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -4223,23 +4251,23 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C55)</f>
-        <v>-3044.5299999999997</v>
+        <v>-3126.8099999999995</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>-723.7600000000001</v>
+        <v>-779.11000000000013</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
-        <v>-107.47</v>
+        <v>-162.82</v>
       </c>
       <c r="F1" s="2">
         <f t="shared" si="0"/>
-        <v>-52.01</v>
+        <v>-107.36</v>
       </c>
       <c r="G1" s="2">
         <f t="shared" si="0"/>
-        <v>-52.01</v>
+        <v>-107.36</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4538,7 +4566,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C22" s="2">
         <v>-14.5</v>
@@ -4550,7 +4578,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C23" s="2">
         <v>-34.29</v>
@@ -4562,7 +4590,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C24" s="2">
         <v>-19.98</v>
@@ -4574,7 +4602,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C25" s="2">
         <v>-27</v>
@@ -4586,7 +4614,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C26" s="2">
         <v>-43.58</v>
@@ -4600,7 +4628,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C27" s="2">
         <v>-70</v>
@@ -4612,7 +4640,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B28" t="s">
         <v>70</v>
@@ -4627,7 +4655,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C29" s="2">
         <v>-36</v>
@@ -4639,7 +4667,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C30" s="2">
         <v>-15</v>
@@ -4651,7 +4679,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C31" s="2">
         <v>-53.54</v>
@@ -4663,7 +4691,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C32" s="2">
         <v>-33.82</v>
@@ -4675,7 +4703,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C33" s="2">
         <v>-20</v>
@@ -4687,7 +4715,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C34" s="2">
         <v>-51.98</v>
@@ -4699,7 +4727,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C35" s="2">
         <v>-17.98</v>
@@ -4711,7 +4739,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C36" s="2">
         <v>-166.9</v>
@@ -4722,32 +4750,60 @@
       <c r="G36" s="2"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C37" s="2"/>
+      <c r="A37" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="2">
+        <v>-3</v>
+      </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C38" s="2"/>
+      <c r="A38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" s="2">
+        <v>-15.98</v>
+      </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C39" s="2"/>
+      <c r="A39" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="2">
+        <v>-7.95</v>
+      </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
+      <c r="A40" t="s">
+        <v>104</v>
+      </c>
+      <c r="C40" s="2">
+        <v>-55.35</v>
+      </c>
+      <c r="D40" s="2">
+        <v>-55.35</v>
+      </c>
+      <c r="E40" s="2">
+        <v>-55.35</v>
+      </c>
+      <c r="F40" s="2">
+        <v>-55.35</v>
+      </c>
+      <c r="G40" s="2">
+        <v>-55.35</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C41" s="2"/>
@@ -7252,3015 +7308,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F01D07ED-902F-4033-9A87-355F7134C802}">
-  <dimension ref="A1:G413"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="29.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="7" width="12.7109375" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C1" s="2">
-        <f t="shared" ref="C1:G1" si="0">SUM(C3:C72)</f>
-        <v>-628.18000000000006</v>
-      </c>
-      <c r="D1" s="2">
-        <f t="shared" si="0"/>
-        <v>-505.23</v>
-      </c>
-      <c r="E1" s="2">
-        <f t="shared" si="0"/>
-        <v>-71.400000000000006</v>
-      </c>
-      <c r="F1" s="2">
-        <f t="shared" si="0"/>
-        <v>-71.400000000000006</v>
-      </c>
-      <c r="G1" s="2">
-        <f t="shared" si="0"/>
-        <v>-71.400000000000006</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="6">
-        <v>-44.9</v>
-      </c>
-      <c r="D3" s="6">
-        <v>-44.9</v>
-      </c>
-      <c r="E3" s="6">
-        <v>-44.9</v>
-      </c>
-      <c r="F3" s="6">
-        <v>-44.9</v>
-      </c>
-      <c r="G3" s="6">
-        <v>-44.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="6">
-        <v>-26.5</v>
-      </c>
-      <c r="D4" s="6">
-        <v>-26.5</v>
-      </c>
-      <c r="E4" s="6">
-        <v>-26.5</v>
-      </c>
-      <c r="F4" s="6">
-        <v>-26.5</v>
-      </c>
-      <c r="G4" s="6">
-        <v>-26.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="6">
-        <v>-84.25</v>
-      </c>
-      <c r="D5" s="6">
-        <v>-84.25</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="6">
-        <v>-49.97</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-154.34</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-154.34</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="2">
-        <v>-111</v>
-      </c>
-      <c r="D8" s="2">
-        <v>-111</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="2">
-        <v>-84.24</v>
-      </c>
-      <c r="D9" s="2">
-        <v>-84.24</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="2">
-        <v>-14.99</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" s="2">
-        <v>-57.99</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-    </row>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-    </row>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-    </row>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-    </row>
-    <row r="53" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-    </row>
-    <row r="54" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-    </row>
-    <row r="55" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-    </row>
-    <row r="56" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-    </row>
-    <row r="57" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-    </row>
-    <row r="58" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-    </row>
-    <row r="59" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-    </row>
-    <row r="60" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-    </row>
-    <row r="61" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-    </row>
-    <row r="62" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-    </row>
-    <row r="63" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-    </row>
-    <row r="64" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-    </row>
-    <row r="65" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-    </row>
-    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-    </row>
-    <row r="67" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-    </row>
-    <row r="68" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-    </row>
-    <row r="69" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-    </row>
-    <row r="70" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-    </row>
-    <row r="71" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-    </row>
-    <row r="72" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-    </row>
-    <row r="73" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-    </row>
-    <row r="74" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-    </row>
-    <row r="75" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-    </row>
-    <row r="76" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-    </row>
-    <row r="77" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-    </row>
-    <row r="78" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-    </row>
-    <row r="79" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-    </row>
-    <row r="80" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-    </row>
-    <row r="81" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-    </row>
-    <row r="82" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-    </row>
-    <row r="83" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-    </row>
-    <row r="84" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-    </row>
-    <row r="85" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-    </row>
-    <row r="86" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-    </row>
-    <row r="87" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-    </row>
-    <row r="88" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-    </row>
-    <row r="89" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-    </row>
-    <row r="90" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-    </row>
-    <row r="91" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-    </row>
-    <row r="92" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-    </row>
-    <row r="93" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-    </row>
-    <row r="94" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-    </row>
-    <row r="95" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-    </row>
-    <row r="96" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-    </row>
-    <row r="97" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-    </row>
-    <row r="98" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-    </row>
-    <row r="99" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-    </row>
-    <row r="100" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-    </row>
-    <row r="101" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-    </row>
-    <row r="102" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-    </row>
-    <row r="103" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-    </row>
-    <row r="104" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-    </row>
-    <row r="105" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-    </row>
-    <row r="106" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-    </row>
-    <row r="107" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-    </row>
-    <row r="108" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-    </row>
-    <row r="109" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-    </row>
-    <row r="110" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-    </row>
-    <row r="111" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-    </row>
-    <row r="112" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-    </row>
-    <row r="113" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-    </row>
-    <row r="114" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-    </row>
-    <row r="115" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-    </row>
-    <row r="116" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-    </row>
-    <row r="117" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-    </row>
-    <row r="118" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-    </row>
-    <row r="119" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-    </row>
-    <row r="120" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
-      <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-    </row>
-    <row r="121" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-    </row>
-    <row r="122" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
-      <c r="E122" s="2"/>
-      <c r="F122" s="2"/>
-      <c r="G122" s="2"/>
-    </row>
-    <row r="123" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
-      <c r="E123" s="2"/>
-      <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
-    </row>
-    <row r="124" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
-      <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
-    </row>
-    <row r="125" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
-      <c r="E125" s="2"/>
-      <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-    </row>
-    <row r="126" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
-      <c r="E126" s="2"/>
-      <c r="F126" s="2"/>
-      <c r="G126" s="2"/>
-    </row>
-    <row r="127" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
-      <c r="E127" s="2"/>
-      <c r="F127" s="2"/>
-      <c r="G127" s="2"/>
-    </row>
-    <row r="128" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
-      <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
-    </row>
-    <row r="129" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
-      <c r="F129" s="2"/>
-      <c r="G129" s="2"/>
-    </row>
-    <row r="130" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
-      <c r="E130" s="2"/>
-      <c r="F130" s="2"/>
-      <c r="G130" s="2"/>
-    </row>
-    <row r="131" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
-      <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-    </row>
-    <row r="132" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
-      <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-    </row>
-    <row r="133" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
-      <c r="E133" s="2"/>
-      <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-    </row>
-    <row r="134" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C134" s="2"/>
-      <c r="D134" s="2"/>
-      <c r="E134" s="2"/>
-      <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
-    </row>
-    <row r="135" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
-      <c r="E135" s="2"/>
-      <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-    </row>
-    <row r="136" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
-      <c r="E136" s="2"/>
-      <c r="F136" s="2"/>
-      <c r="G136" s="2"/>
-    </row>
-    <row r="137" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
-      <c r="E137" s="2"/>
-      <c r="F137" s="2"/>
-      <c r="G137" s="2"/>
-    </row>
-    <row r="138" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
-      <c r="E138" s="2"/>
-      <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
-    </row>
-    <row r="139" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C139" s="2"/>
-      <c r="D139" s="2"/>
-      <c r="E139" s="2"/>
-      <c r="F139" s="2"/>
-      <c r="G139" s="2"/>
-    </row>
-    <row r="140" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
-      <c r="E140" s="2"/>
-      <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-    </row>
-    <row r="141" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="2"/>
-      <c r="F141" s="2"/>
-      <c r="G141" s="2"/>
-    </row>
-    <row r="142" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
-      <c r="F142" s="2"/>
-      <c r="G142" s="2"/>
-    </row>
-    <row r="143" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
-      <c r="E143" s="2"/>
-      <c r="F143" s="2"/>
-      <c r="G143" s="2"/>
-    </row>
-    <row r="144" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
-      <c r="F144" s="2"/>
-      <c r="G144" s="2"/>
-    </row>
-    <row r="145" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
-      <c r="F145" s="2"/>
-      <c r="G145" s="2"/>
-    </row>
-    <row r="146" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
-      <c r="E146" s="2"/>
-      <c r="F146" s="2"/>
-      <c r="G146" s="2"/>
-    </row>
-    <row r="147" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
-      <c r="F147" s="2"/>
-      <c r="G147" s="2"/>
-    </row>
-    <row r="148" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
-      <c r="E148" s="2"/>
-      <c r="F148" s="2"/>
-      <c r="G148" s="2"/>
-    </row>
-    <row r="149" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
-      <c r="E149" s="2"/>
-      <c r="F149" s="2"/>
-      <c r="G149" s="2"/>
-    </row>
-    <row r="150" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C150" s="2"/>
-      <c r="D150" s="2"/>
-      <c r="E150" s="2"/>
-      <c r="F150" s="2"/>
-      <c r="G150" s="2"/>
-    </row>
-    <row r="151" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C151" s="2"/>
-      <c r="D151" s="2"/>
-      <c r="E151" s="2"/>
-      <c r="F151" s="2"/>
-      <c r="G151" s="2"/>
-    </row>
-    <row r="152" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C152" s="2"/>
-      <c r="D152" s="2"/>
-      <c r="E152" s="2"/>
-      <c r="F152" s="2"/>
-      <c r="G152" s="2"/>
-    </row>
-    <row r="153" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C153" s="2"/>
-      <c r="D153" s="2"/>
-      <c r="E153" s="2"/>
-      <c r="F153" s="2"/>
-      <c r="G153" s="2"/>
-    </row>
-    <row r="154" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C154" s="2"/>
-      <c r="D154" s="2"/>
-      <c r="E154" s="2"/>
-      <c r="F154" s="2"/>
-      <c r="G154" s="2"/>
-    </row>
-    <row r="155" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C155" s="2"/>
-      <c r="D155" s="2"/>
-      <c r="E155" s="2"/>
-      <c r="F155" s="2"/>
-      <c r="G155" s="2"/>
-    </row>
-    <row r="156" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C156" s="2"/>
-      <c r="D156" s="2"/>
-      <c r="E156" s="2"/>
-      <c r="F156" s="2"/>
-      <c r="G156" s="2"/>
-    </row>
-    <row r="157" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C157" s="2"/>
-      <c r="D157" s="2"/>
-      <c r="E157" s="2"/>
-      <c r="F157" s="2"/>
-      <c r="G157" s="2"/>
-    </row>
-    <row r="158" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C158" s="2"/>
-      <c r="D158" s="2"/>
-      <c r="E158" s="2"/>
-      <c r="F158" s="2"/>
-      <c r="G158" s="2"/>
-    </row>
-    <row r="159" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C159" s="2"/>
-      <c r="D159" s="2"/>
-      <c r="E159" s="2"/>
-      <c r="F159" s="2"/>
-      <c r="G159" s="2"/>
-    </row>
-    <row r="160" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C160" s="2"/>
-      <c r="D160" s="2"/>
-      <c r="E160" s="2"/>
-      <c r="F160" s="2"/>
-      <c r="G160" s="2"/>
-    </row>
-    <row r="161" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C161" s="2"/>
-      <c r="D161" s="2"/>
-      <c r="E161" s="2"/>
-      <c r="F161" s="2"/>
-      <c r="G161" s="2"/>
-    </row>
-    <row r="162" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C162" s="2"/>
-      <c r="D162" s="2"/>
-      <c r="E162" s="2"/>
-      <c r="F162" s="2"/>
-      <c r="G162" s="2"/>
-    </row>
-    <row r="163" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C163" s="2"/>
-      <c r="D163" s="2"/>
-      <c r="E163" s="2"/>
-      <c r="F163" s="2"/>
-      <c r="G163" s="2"/>
-    </row>
-    <row r="164" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C164" s="2"/>
-      <c r="D164" s="2"/>
-      <c r="E164" s="2"/>
-      <c r="F164" s="2"/>
-      <c r="G164" s="2"/>
-    </row>
-    <row r="165" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C165" s="2"/>
-      <c r="D165" s="2"/>
-      <c r="E165" s="2"/>
-      <c r="F165" s="2"/>
-      <c r="G165" s="2"/>
-    </row>
-    <row r="166" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C166" s="2"/>
-      <c r="D166" s="2"/>
-      <c r="E166" s="2"/>
-      <c r="F166" s="2"/>
-      <c r="G166" s="2"/>
-    </row>
-    <row r="167" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C167" s="2"/>
-      <c r="D167" s="2"/>
-      <c r="E167" s="2"/>
-      <c r="F167" s="2"/>
-      <c r="G167" s="2"/>
-    </row>
-    <row r="168" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C168" s="2"/>
-      <c r="D168" s="2"/>
-      <c r="E168" s="2"/>
-      <c r="F168" s="2"/>
-      <c r="G168" s="2"/>
-    </row>
-    <row r="169" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C169" s="2"/>
-      <c r="D169" s="2"/>
-      <c r="E169" s="2"/>
-      <c r="F169" s="2"/>
-      <c r="G169" s="2"/>
-    </row>
-    <row r="170" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C170" s="2"/>
-      <c r="D170" s="2"/>
-      <c r="E170" s="2"/>
-      <c r="F170" s="2"/>
-      <c r="G170" s="2"/>
-    </row>
-    <row r="171" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C171" s="2"/>
-      <c r="D171" s="2"/>
-      <c r="E171" s="2"/>
-      <c r="F171" s="2"/>
-      <c r="G171" s="2"/>
-    </row>
-    <row r="172" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C172" s="2"/>
-      <c r="D172" s="2"/>
-      <c r="E172" s="2"/>
-      <c r="F172" s="2"/>
-      <c r="G172" s="2"/>
-    </row>
-    <row r="173" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C173" s="2"/>
-      <c r="D173" s="2"/>
-      <c r="E173" s="2"/>
-      <c r="F173" s="2"/>
-      <c r="G173" s="2"/>
-    </row>
-    <row r="174" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C174" s="2"/>
-      <c r="D174" s="2"/>
-      <c r="E174" s="2"/>
-      <c r="F174" s="2"/>
-      <c r="G174" s="2"/>
-    </row>
-    <row r="175" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C175" s="2"/>
-      <c r="D175" s="2"/>
-      <c r="E175" s="2"/>
-      <c r="F175" s="2"/>
-      <c r="G175" s="2"/>
-    </row>
-    <row r="176" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C176" s="2"/>
-      <c r="D176" s="2"/>
-      <c r="E176" s="2"/>
-      <c r="F176" s="2"/>
-      <c r="G176" s="2"/>
-    </row>
-    <row r="177" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C177" s="2"/>
-      <c r="D177" s="2"/>
-      <c r="E177" s="2"/>
-      <c r="F177" s="2"/>
-      <c r="G177" s="2"/>
-    </row>
-    <row r="178" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C178" s="2"/>
-      <c r="D178" s="2"/>
-      <c r="E178" s="2"/>
-      <c r="F178" s="2"/>
-      <c r="G178" s="2"/>
-    </row>
-    <row r="179" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C179" s="2"/>
-      <c r="D179" s="2"/>
-      <c r="E179" s="2"/>
-      <c r="F179" s="2"/>
-      <c r="G179" s="2"/>
-    </row>
-    <row r="180" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C180" s="2"/>
-      <c r="D180" s="2"/>
-      <c r="E180" s="2"/>
-      <c r="F180" s="2"/>
-      <c r="G180" s="2"/>
-    </row>
-    <row r="181" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C181" s="2"/>
-      <c r="D181" s="2"/>
-      <c r="E181" s="2"/>
-      <c r="F181" s="2"/>
-      <c r="G181" s="2"/>
-    </row>
-    <row r="182" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C182" s="2"/>
-      <c r="D182" s="2"/>
-      <c r="E182" s="2"/>
-      <c r="F182" s="2"/>
-      <c r="G182" s="2"/>
-    </row>
-    <row r="183" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C183" s="2"/>
-      <c r="D183" s="2"/>
-      <c r="E183" s="2"/>
-      <c r="F183" s="2"/>
-      <c r="G183" s="2"/>
-    </row>
-    <row r="184" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C184" s="2"/>
-      <c r="D184" s="2"/>
-      <c r="E184" s="2"/>
-      <c r="F184" s="2"/>
-      <c r="G184" s="2"/>
-    </row>
-    <row r="185" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C185" s="2"/>
-      <c r="D185" s="2"/>
-      <c r="E185" s="2"/>
-      <c r="F185" s="2"/>
-      <c r="G185" s="2"/>
-    </row>
-    <row r="186" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C186" s="2"/>
-      <c r="D186" s="2"/>
-      <c r="E186" s="2"/>
-      <c r="F186" s="2"/>
-      <c r="G186" s="2"/>
-    </row>
-    <row r="187" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C187" s="2"/>
-      <c r="D187" s="2"/>
-      <c r="E187" s="2"/>
-      <c r="F187" s="2"/>
-      <c r="G187" s="2"/>
-    </row>
-    <row r="188" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C188" s="2"/>
-      <c r="D188" s="2"/>
-      <c r="E188" s="2"/>
-      <c r="F188" s="2"/>
-      <c r="G188" s="2"/>
-    </row>
-    <row r="189" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C189" s="2"/>
-      <c r="D189" s="2"/>
-      <c r="E189" s="2"/>
-      <c r="F189" s="2"/>
-      <c r="G189" s="2"/>
-    </row>
-    <row r="190" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C190" s="2"/>
-      <c r="D190" s="2"/>
-      <c r="E190" s="2"/>
-      <c r="F190" s="2"/>
-      <c r="G190" s="2"/>
-    </row>
-    <row r="191" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C191" s="2"/>
-      <c r="D191" s="2"/>
-      <c r="E191" s="2"/>
-      <c r="F191" s="2"/>
-      <c r="G191" s="2"/>
-    </row>
-    <row r="192" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C192" s="2"/>
-      <c r="D192" s="2"/>
-      <c r="E192" s="2"/>
-      <c r="F192" s="2"/>
-      <c r="G192" s="2"/>
-    </row>
-    <row r="193" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C193" s="2"/>
-      <c r="D193" s="2"/>
-      <c r="E193" s="2"/>
-      <c r="F193" s="2"/>
-      <c r="G193" s="2"/>
-    </row>
-    <row r="194" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C194" s="2"/>
-      <c r="D194" s="2"/>
-      <c r="E194" s="2"/>
-      <c r="F194" s="2"/>
-      <c r="G194" s="2"/>
-    </row>
-    <row r="195" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C195" s="2"/>
-      <c r="D195" s="2"/>
-      <c r="E195" s="2"/>
-      <c r="F195" s="2"/>
-      <c r="G195" s="2"/>
-    </row>
-    <row r="196" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C196" s="2"/>
-      <c r="D196" s="2"/>
-      <c r="E196" s="2"/>
-      <c r="F196" s="2"/>
-      <c r="G196" s="2"/>
-    </row>
-    <row r="197" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C197" s="2"/>
-      <c r="D197" s="2"/>
-      <c r="E197" s="2"/>
-      <c r="F197" s="2"/>
-      <c r="G197" s="2"/>
-    </row>
-    <row r="198" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C198" s="2"/>
-      <c r="D198" s="2"/>
-      <c r="E198" s="2"/>
-      <c r="F198" s="2"/>
-      <c r="G198" s="2"/>
-    </row>
-    <row r="199" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C199" s="2"/>
-      <c r="D199" s="2"/>
-      <c r="E199" s="2"/>
-      <c r="F199" s="2"/>
-      <c r="G199" s="2"/>
-    </row>
-    <row r="200" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C200" s="2"/>
-      <c r="D200" s="2"/>
-      <c r="E200" s="2"/>
-      <c r="F200" s="2"/>
-      <c r="G200" s="2"/>
-    </row>
-    <row r="201" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C201" s="2"/>
-      <c r="D201" s="2"/>
-      <c r="E201" s="2"/>
-      <c r="F201" s="2"/>
-      <c r="G201" s="2"/>
-    </row>
-    <row r="202" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C202" s="2"/>
-      <c r="D202" s="2"/>
-      <c r="E202" s="2"/>
-      <c r="F202" s="2"/>
-      <c r="G202" s="2"/>
-    </row>
-    <row r="203" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C203" s="2"/>
-      <c r="D203" s="2"/>
-      <c r="E203" s="2"/>
-      <c r="F203" s="2"/>
-      <c r="G203" s="2"/>
-    </row>
-    <row r="204" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
-    </row>
-    <row r="205" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-    </row>
-    <row r="206" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C206" s="2"/>
-      <c r="D206" s="2"/>
-      <c r="E206" s="2"/>
-      <c r="F206" s="2"/>
-      <c r="G206" s="2"/>
-    </row>
-    <row r="207" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C207" s="2"/>
-      <c r="D207" s="2"/>
-      <c r="E207" s="2"/>
-      <c r="F207" s="2"/>
-      <c r="G207" s="2"/>
-    </row>
-    <row r="208" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C208" s="2"/>
-      <c r="D208" s="2"/>
-      <c r="E208" s="2"/>
-      <c r="F208" s="2"/>
-      <c r="G208" s="2"/>
-    </row>
-    <row r="209" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C209" s="2"/>
-      <c r="D209" s="2"/>
-      <c r="E209" s="2"/>
-      <c r="F209" s="2"/>
-      <c r="G209" s="2"/>
-    </row>
-    <row r="210" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C210" s="2"/>
-      <c r="D210" s="2"/>
-      <c r="E210" s="2"/>
-      <c r="F210" s="2"/>
-      <c r="G210" s="2"/>
-    </row>
-    <row r="211" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C211" s="2"/>
-      <c r="D211" s="2"/>
-      <c r="E211" s="2"/>
-      <c r="F211" s="2"/>
-      <c r="G211" s="2"/>
-    </row>
-    <row r="212" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C212" s="2"/>
-      <c r="D212" s="2"/>
-      <c r="E212" s="2"/>
-      <c r="F212" s="2"/>
-      <c r="G212" s="2"/>
-    </row>
-    <row r="213" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C213" s="2"/>
-      <c r="D213" s="2"/>
-      <c r="E213" s="2"/>
-      <c r="F213" s="2"/>
-      <c r="G213" s="2"/>
-    </row>
-    <row r="214" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C214" s="2"/>
-      <c r="D214" s="2"/>
-      <c r="E214" s="2"/>
-      <c r="F214" s="2"/>
-      <c r="G214" s="2"/>
-    </row>
-    <row r="215" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C215" s="2"/>
-      <c r="D215" s="2"/>
-      <c r="E215" s="2"/>
-      <c r="F215" s="2"/>
-      <c r="G215" s="2"/>
-    </row>
-    <row r="216" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C216" s="2"/>
-      <c r="D216" s="2"/>
-      <c r="E216" s="2"/>
-      <c r="F216" s="2"/>
-      <c r="G216" s="2"/>
-    </row>
-    <row r="217" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C217" s="2"/>
-      <c r="D217" s="2"/>
-      <c r="E217" s="2"/>
-      <c r="F217" s="2"/>
-      <c r="G217" s="2"/>
-    </row>
-    <row r="218" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C218" s="2"/>
-      <c r="D218" s="2"/>
-      <c r="E218" s="2"/>
-      <c r="F218" s="2"/>
-      <c r="G218" s="2"/>
-    </row>
-    <row r="219" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C219" s="2"/>
-      <c r="D219" s="2"/>
-      <c r="E219" s="2"/>
-      <c r="F219" s="2"/>
-      <c r="G219" s="2"/>
-    </row>
-    <row r="220" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C220" s="2"/>
-      <c r="D220" s="2"/>
-      <c r="E220" s="2"/>
-      <c r="F220" s="2"/>
-      <c r="G220" s="2"/>
-    </row>
-    <row r="221" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C221" s="2"/>
-      <c r="D221" s="2"/>
-      <c r="E221" s="2"/>
-      <c r="F221" s="2"/>
-      <c r="G221" s="2"/>
-    </row>
-    <row r="222" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C222" s="2"/>
-      <c r="D222" s="2"/>
-      <c r="E222" s="2"/>
-      <c r="F222" s="2"/>
-      <c r="G222" s="2"/>
-    </row>
-    <row r="223" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C223" s="2"/>
-      <c r="D223" s="2"/>
-      <c r="E223" s="2"/>
-      <c r="F223" s="2"/>
-      <c r="G223" s="2"/>
-    </row>
-    <row r="224" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C224" s="2"/>
-      <c r="D224" s="2"/>
-      <c r="E224" s="2"/>
-      <c r="F224" s="2"/>
-      <c r="G224" s="2"/>
-    </row>
-    <row r="225" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C225" s="2"/>
-      <c r="D225" s="2"/>
-      <c r="E225" s="2"/>
-      <c r="F225" s="2"/>
-      <c r="G225" s="2"/>
-    </row>
-    <row r="226" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C226" s="2"/>
-      <c r="D226" s="2"/>
-      <c r="E226" s="2"/>
-      <c r="F226" s="2"/>
-      <c r="G226" s="2"/>
-    </row>
-    <row r="227" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C227" s="2"/>
-      <c r="D227" s="2"/>
-      <c r="E227" s="2"/>
-      <c r="F227" s="2"/>
-      <c r="G227" s="2"/>
-    </row>
-    <row r="228" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C228" s="2"/>
-      <c r="D228" s="2"/>
-      <c r="E228" s="2"/>
-      <c r="F228" s="2"/>
-      <c r="G228" s="2"/>
-    </row>
-    <row r="229" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C229" s="2"/>
-      <c r="D229" s="2"/>
-      <c r="E229" s="2"/>
-      <c r="F229" s="2"/>
-      <c r="G229" s="2"/>
-    </row>
-    <row r="230" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C230" s="2"/>
-      <c r="D230" s="2"/>
-      <c r="E230" s="2"/>
-      <c r="F230" s="2"/>
-      <c r="G230" s="2"/>
-    </row>
-    <row r="231" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C231" s="2"/>
-      <c r="D231" s="2"/>
-      <c r="E231" s="2"/>
-      <c r="F231" s="2"/>
-      <c r="G231" s="2"/>
-    </row>
-    <row r="232" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C232" s="2"/>
-      <c r="D232" s="2"/>
-      <c r="E232" s="2"/>
-      <c r="F232" s="2"/>
-      <c r="G232" s="2"/>
-    </row>
-    <row r="233" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C233" s="2"/>
-      <c r="D233" s="2"/>
-      <c r="E233" s="2"/>
-      <c r="F233" s="2"/>
-      <c r="G233" s="2"/>
-    </row>
-    <row r="234" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C234" s="2"/>
-      <c r="D234" s="2"/>
-      <c r="E234" s="2"/>
-      <c r="F234" s="2"/>
-      <c r="G234" s="2"/>
-    </row>
-    <row r="235" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C235" s="2"/>
-      <c r="D235" s="2"/>
-      <c r="E235" s="2"/>
-      <c r="F235" s="2"/>
-      <c r="G235" s="2"/>
-    </row>
-    <row r="236" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C236" s="2"/>
-      <c r="D236" s="2"/>
-      <c r="E236" s="2"/>
-      <c r="F236" s="2"/>
-      <c r="G236" s="2"/>
-    </row>
-    <row r="237" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C237" s="2"/>
-      <c r="D237" s="2"/>
-      <c r="E237" s="2"/>
-      <c r="F237" s="2"/>
-      <c r="G237" s="2"/>
-    </row>
-    <row r="238" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C238" s="2"/>
-      <c r="D238" s="2"/>
-      <c r="E238" s="2"/>
-      <c r="F238" s="2"/>
-      <c r="G238" s="2"/>
-    </row>
-    <row r="239" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C239" s="2"/>
-      <c r="D239" s="2"/>
-      <c r="E239" s="2"/>
-      <c r="F239" s="2"/>
-      <c r="G239" s="2"/>
-    </row>
-    <row r="240" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C240" s="2"/>
-      <c r="D240" s="2"/>
-      <c r="E240" s="2"/>
-      <c r="F240" s="2"/>
-      <c r="G240" s="2"/>
-    </row>
-    <row r="241" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C241" s="2"/>
-      <c r="D241" s="2"/>
-      <c r="E241" s="2"/>
-      <c r="F241" s="2"/>
-      <c r="G241" s="2"/>
-    </row>
-    <row r="242" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C242" s="2"/>
-      <c r="D242" s="2"/>
-      <c r="E242" s="2"/>
-      <c r="F242" s="2"/>
-      <c r="G242" s="2"/>
-    </row>
-    <row r="243" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C243" s="2"/>
-      <c r="D243" s="2"/>
-      <c r="E243" s="2"/>
-      <c r="F243" s="2"/>
-      <c r="G243" s="2"/>
-    </row>
-    <row r="244" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C244" s="2"/>
-      <c r="D244" s="2"/>
-      <c r="E244" s="2"/>
-      <c r="F244" s="2"/>
-      <c r="G244" s="2"/>
-    </row>
-    <row r="245" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C245" s="2"/>
-      <c r="D245" s="2"/>
-      <c r="E245" s="2"/>
-      <c r="F245" s="2"/>
-      <c r="G245" s="2"/>
-    </row>
-    <row r="246" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C246" s="2"/>
-      <c r="D246" s="2"/>
-      <c r="E246" s="2"/>
-      <c r="F246" s="2"/>
-      <c r="G246" s="2"/>
-    </row>
-    <row r="247" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C247" s="2"/>
-      <c r="D247" s="2"/>
-      <c r="E247" s="2"/>
-      <c r="F247" s="2"/>
-      <c r="G247" s="2"/>
-    </row>
-    <row r="248" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C248" s="2"/>
-      <c r="D248" s="2"/>
-      <c r="E248" s="2"/>
-      <c r="F248" s="2"/>
-      <c r="G248" s="2"/>
-    </row>
-    <row r="249" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C249" s="2"/>
-      <c r="D249" s="2"/>
-      <c r="E249" s="2"/>
-      <c r="F249" s="2"/>
-      <c r="G249" s="2"/>
-    </row>
-    <row r="250" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C250" s="2"/>
-      <c r="D250" s="2"/>
-      <c r="E250" s="2"/>
-      <c r="F250" s="2"/>
-      <c r="G250" s="2"/>
-    </row>
-    <row r="251" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C251" s="2"/>
-      <c r="D251" s="2"/>
-      <c r="E251" s="2"/>
-      <c r="F251" s="2"/>
-      <c r="G251" s="2"/>
-    </row>
-    <row r="252" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C252" s="2"/>
-      <c r="D252" s="2"/>
-      <c r="E252" s="2"/>
-      <c r="F252" s="2"/>
-      <c r="G252" s="2"/>
-    </row>
-    <row r="253" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C253" s="2"/>
-      <c r="D253" s="2"/>
-      <c r="E253" s="2"/>
-      <c r="F253" s="2"/>
-      <c r="G253" s="2"/>
-    </row>
-    <row r="254" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C254" s="2"/>
-      <c r="D254" s="2"/>
-      <c r="E254" s="2"/>
-      <c r="F254" s="2"/>
-      <c r="G254" s="2"/>
-    </row>
-    <row r="255" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C255" s="2"/>
-      <c r="D255" s="2"/>
-      <c r="E255" s="2"/>
-      <c r="F255" s="2"/>
-      <c r="G255" s="2"/>
-    </row>
-    <row r="256" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C256" s="2"/>
-      <c r="D256" s="2"/>
-      <c r="E256" s="2"/>
-      <c r="F256" s="2"/>
-      <c r="G256" s="2"/>
-    </row>
-    <row r="257" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C257" s="2"/>
-      <c r="D257" s="2"/>
-      <c r="E257" s="2"/>
-      <c r="F257" s="2"/>
-      <c r="G257" s="2"/>
-    </row>
-    <row r="258" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C258" s="2"/>
-      <c r="D258" s="2"/>
-      <c r="E258" s="2"/>
-      <c r="F258" s="2"/>
-      <c r="G258" s="2"/>
-    </row>
-    <row r="259" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C259" s="2"/>
-      <c r="D259" s="2"/>
-      <c r="E259" s="2"/>
-      <c r="F259" s="2"/>
-      <c r="G259" s="2"/>
-    </row>
-    <row r="260" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C260" s="2"/>
-      <c r="D260" s="2"/>
-      <c r="E260" s="2"/>
-      <c r="F260" s="2"/>
-      <c r="G260" s="2"/>
-    </row>
-    <row r="261" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C261" s="2"/>
-      <c r="D261" s="2"/>
-      <c r="E261" s="2"/>
-      <c r="F261" s="2"/>
-      <c r="G261" s="2"/>
-    </row>
-    <row r="262" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C262" s="2"/>
-      <c r="D262" s="2"/>
-      <c r="E262" s="2"/>
-      <c r="F262" s="2"/>
-      <c r="G262" s="2"/>
-    </row>
-    <row r="263" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C263" s="2"/>
-      <c r="D263" s="2"/>
-      <c r="E263" s="2"/>
-      <c r="F263" s="2"/>
-      <c r="G263" s="2"/>
-    </row>
-    <row r="264" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C264" s="2"/>
-      <c r="D264" s="2"/>
-      <c r="E264" s="2"/>
-      <c r="F264" s="2"/>
-      <c r="G264" s="2"/>
-    </row>
-    <row r="265" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C265" s="2"/>
-      <c r="D265" s="2"/>
-      <c r="E265" s="2"/>
-      <c r="F265" s="2"/>
-      <c r="G265" s="2"/>
-    </row>
-    <row r="266" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C266" s="2"/>
-      <c r="D266" s="2"/>
-      <c r="E266" s="2"/>
-      <c r="F266" s="2"/>
-      <c r="G266" s="2"/>
-    </row>
-    <row r="267" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C267" s="2"/>
-      <c r="D267" s="2"/>
-      <c r="E267" s="2"/>
-      <c r="F267" s="2"/>
-      <c r="G267" s="2"/>
-    </row>
-    <row r="268" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C268" s="2"/>
-      <c r="D268" s="2"/>
-      <c r="E268" s="2"/>
-      <c r="F268" s="2"/>
-      <c r="G268" s="2"/>
-    </row>
-    <row r="269" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C269" s="2"/>
-      <c r="D269" s="2"/>
-      <c r="E269" s="2"/>
-      <c r="F269" s="2"/>
-      <c r="G269" s="2"/>
-    </row>
-    <row r="270" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C270" s="2"/>
-      <c r="D270" s="2"/>
-      <c r="E270" s="2"/>
-      <c r="F270" s="2"/>
-      <c r="G270" s="2"/>
-    </row>
-    <row r="271" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C271" s="2"/>
-      <c r="D271" s="2"/>
-      <c r="E271" s="2"/>
-      <c r="F271" s="2"/>
-      <c r="G271" s="2"/>
-    </row>
-    <row r="272" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C272" s="2"/>
-      <c r="D272" s="2"/>
-      <c r="E272" s="2"/>
-      <c r="F272" s="2"/>
-      <c r="G272" s="2"/>
-    </row>
-    <row r="273" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C273" s="2"/>
-      <c r="D273" s="2"/>
-      <c r="E273" s="2"/>
-      <c r="F273" s="2"/>
-      <c r="G273" s="2"/>
-    </row>
-    <row r="274" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C274" s="2"/>
-      <c r="D274" s="2"/>
-      <c r="E274" s="2"/>
-      <c r="F274" s="2"/>
-      <c r="G274" s="2"/>
-    </row>
-    <row r="275" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C275" s="2"/>
-      <c r="D275" s="2"/>
-      <c r="E275" s="2"/>
-      <c r="F275" s="2"/>
-      <c r="G275" s="2"/>
-    </row>
-    <row r="276" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C276" s="2"/>
-      <c r="D276" s="2"/>
-      <c r="E276" s="2"/>
-      <c r="F276" s="2"/>
-      <c r="G276" s="2"/>
-    </row>
-    <row r="277" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C277" s="2"/>
-      <c r="D277" s="2"/>
-      <c r="E277" s="2"/>
-      <c r="F277" s="2"/>
-      <c r="G277" s="2"/>
-    </row>
-    <row r="278" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C278" s="2"/>
-      <c r="D278" s="2"/>
-      <c r="E278" s="2"/>
-      <c r="F278" s="2"/>
-      <c r="G278" s="2"/>
-    </row>
-    <row r="279" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C279" s="2"/>
-      <c r="D279" s="2"/>
-      <c r="E279" s="2"/>
-      <c r="F279" s="2"/>
-      <c r="G279" s="2"/>
-    </row>
-    <row r="280" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C280" s="2"/>
-      <c r="D280" s="2"/>
-      <c r="E280" s="2"/>
-      <c r="F280" s="2"/>
-      <c r="G280" s="2"/>
-    </row>
-    <row r="281" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C281" s="2"/>
-      <c r="D281" s="2"/>
-      <c r="E281" s="2"/>
-      <c r="F281" s="2"/>
-      <c r="G281" s="2"/>
-    </row>
-    <row r="282" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C282" s="2"/>
-      <c r="D282" s="2"/>
-      <c r="E282" s="2"/>
-      <c r="F282" s="2"/>
-      <c r="G282" s="2"/>
-    </row>
-    <row r="283" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C283" s="2"/>
-      <c r="D283" s="2"/>
-      <c r="E283" s="2"/>
-      <c r="F283" s="2"/>
-      <c r="G283" s="2"/>
-    </row>
-    <row r="284" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C284" s="2"/>
-      <c r="D284" s="2"/>
-      <c r="E284" s="2"/>
-      <c r="F284" s="2"/>
-      <c r="G284" s="2"/>
-    </row>
-    <row r="285" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C285" s="2"/>
-      <c r="D285" s="2"/>
-      <c r="E285" s="2"/>
-      <c r="F285" s="2"/>
-      <c r="G285" s="2"/>
-    </row>
-    <row r="286" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C286" s="2"/>
-      <c r="D286" s="2"/>
-      <c r="E286" s="2"/>
-      <c r="F286" s="2"/>
-      <c r="G286" s="2"/>
-    </row>
-    <row r="287" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C287" s="2"/>
-      <c r="D287" s="2"/>
-      <c r="E287" s="2"/>
-      <c r="F287" s="2"/>
-      <c r="G287" s="2"/>
-    </row>
-    <row r="288" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C288" s="2"/>
-      <c r="D288" s="2"/>
-      <c r="E288" s="2"/>
-      <c r="F288" s="2"/>
-      <c r="G288" s="2"/>
-    </row>
-    <row r="289" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C289" s="2"/>
-      <c r="D289" s="2"/>
-      <c r="E289" s="2"/>
-      <c r="F289" s="2"/>
-      <c r="G289" s="2"/>
-    </row>
-    <row r="290" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C290" s="2"/>
-      <c r="D290" s="2"/>
-      <c r="E290" s="2"/>
-      <c r="F290" s="2"/>
-      <c r="G290" s="2"/>
-    </row>
-    <row r="291" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C291" s="2"/>
-      <c r="D291" s="2"/>
-      <c r="E291" s="2"/>
-      <c r="F291" s="2"/>
-      <c r="G291" s="2"/>
-    </row>
-    <row r="292" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C292" s="2"/>
-      <c r="D292" s="2"/>
-      <c r="E292" s="2"/>
-      <c r="F292" s="2"/>
-      <c r="G292" s="2"/>
-    </row>
-    <row r="293" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C293" s="2"/>
-      <c r="D293" s="2"/>
-      <c r="E293" s="2"/>
-      <c r="F293" s="2"/>
-      <c r="G293" s="2"/>
-    </row>
-    <row r="294" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C294" s="2"/>
-      <c r="D294" s="2"/>
-      <c r="E294" s="2"/>
-      <c r="F294" s="2"/>
-      <c r="G294" s="2"/>
-    </row>
-    <row r="295" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C295" s="2"/>
-      <c r="D295" s="2"/>
-      <c r="E295" s="2"/>
-      <c r="F295" s="2"/>
-      <c r="G295" s="2"/>
-    </row>
-    <row r="296" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C296" s="2"/>
-      <c r="D296" s="2"/>
-      <c r="E296" s="2"/>
-      <c r="F296" s="2"/>
-      <c r="G296" s="2"/>
-    </row>
-    <row r="297" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C297" s="2"/>
-      <c r="D297" s="2"/>
-      <c r="E297" s="2"/>
-      <c r="F297" s="2"/>
-      <c r="G297" s="2"/>
-    </row>
-    <row r="298" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C298" s="2"/>
-      <c r="D298" s="2"/>
-      <c r="E298" s="2"/>
-      <c r="F298" s="2"/>
-      <c r="G298" s="2"/>
-    </row>
-    <row r="299" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C299" s="2"/>
-      <c r="D299" s="2"/>
-      <c r="E299" s="2"/>
-      <c r="F299" s="2"/>
-      <c r="G299" s="2"/>
-    </row>
-    <row r="300" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C300" s="2"/>
-      <c r="D300" s="2"/>
-      <c r="E300" s="2"/>
-      <c r="F300" s="2"/>
-      <c r="G300" s="2"/>
-    </row>
-    <row r="301" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C301" s="2"/>
-      <c r="D301" s="2"/>
-      <c r="E301" s="2"/>
-      <c r="F301" s="2"/>
-      <c r="G301" s="2"/>
-    </row>
-    <row r="302" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C302" s="2"/>
-      <c r="D302" s="2"/>
-      <c r="E302" s="2"/>
-      <c r="F302" s="2"/>
-      <c r="G302" s="2"/>
-    </row>
-    <row r="303" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C303" s="2"/>
-      <c r="D303" s="2"/>
-      <c r="E303" s="2"/>
-      <c r="F303" s="2"/>
-      <c r="G303" s="2"/>
-    </row>
-    <row r="304" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C304" s="2"/>
-      <c r="D304" s="2"/>
-      <c r="E304" s="2"/>
-      <c r="F304" s="2"/>
-      <c r="G304" s="2"/>
-    </row>
-    <row r="305" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C305" s="2"/>
-      <c r="D305" s="2"/>
-      <c r="E305" s="2"/>
-      <c r="F305" s="2"/>
-      <c r="G305" s="2"/>
-    </row>
-    <row r="306" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C306" s="2"/>
-      <c r="D306" s="2"/>
-      <c r="E306" s="2"/>
-      <c r="F306" s="2"/>
-      <c r="G306" s="2"/>
-    </row>
-    <row r="307" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C307" s="2"/>
-      <c r="D307" s="2"/>
-      <c r="E307" s="2"/>
-      <c r="F307" s="2"/>
-      <c r="G307" s="2"/>
-    </row>
-    <row r="308" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C308" s="2"/>
-      <c r="D308" s="2"/>
-      <c r="E308" s="2"/>
-      <c r="F308" s="2"/>
-      <c r="G308" s="2"/>
-    </row>
-    <row r="309" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C309" s="2"/>
-      <c r="D309" s="2"/>
-      <c r="E309" s="2"/>
-      <c r="F309" s="2"/>
-      <c r="G309" s="2"/>
-    </row>
-    <row r="310" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C310" s="2"/>
-      <c r="D310" s="2"/>
-      <c r="E310" s="2"/>
-      <c r="F310" s="2"/>
-      <c r="G310" s="2"/>
-    </row>
-    <row r="311" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C311" s="2"/>
-      <c r="D311" s="2"/>
-      <c r="E311" s="2"/>
-      <c r="F311" s="2"/>
-      <c r="G311" s="2"/>
-    </row>
-    <row r="312" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C312" s="2"/>
-      <c r="D312" s="2"/>
-      <c r="E312" s="2"/>
-      <c r="F312" s="2"/>
-      <c r="G312" s="2"/>
-    </row>
-    <row r="313" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C313" s="2"/>
-      <c r="D313" s="2"/>
-      <c r="E313" s="2"/>
-      <c r="F313" s="2"/>
-      <c r="G313" s="2"/>
-    </row>
-    <row r="314" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C314" s="2"/>
-      <c r="D314" s="2"/>
-      <c r="E314" s="2"/>
-      <c r="F314" s="2"/>
-      <c r="G314" s="2"/>
-    </row>
-    <row r="315" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C315" s="2"/>
-      <c r="D315" s="2"/>
-      <c r="E315" s="2"/>
-      <c r="F315" s="2"/>
-      <c r="G315" s="2"/>
-    </row>
-    <row r="316" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C316" s="2"/>
-      <c r="D316" s="2"/>
-      <c r="E316" s="2"/>
-      <c r="F316" s="2"/>
-      <c r="G316" s="2"/>
-    </row>
-    <row r="317" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C317" s="2"/>
-      <c r="D317" s="2"/>
-      <c r="E317" s="2"/>
-      <c r="F317" s="2"/>
-      <c r="G317" s="2"/>
-    </row>
-    <row r="318" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C318" s="2"/>
-      <c r="D318" s="2"/>
-      <c r="E318" s="2"/>
-      <c r="F318" s="2"/>
-      <c r="G318" s="2"/>
-    </row>
-    <row r="319" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C319" s="2"/>
-      <c r="D319" s="2"/>
-      <c r="E319" s="2"/>
-      <c r="F319" s="2"/>
-      <c r="G319" s="2"/>
-    </row>
-    <row r="320" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C320" s="2"/>
-      <c r="D320" s="2"/>
-      <c r="E320" s="2"/>
-      <c r="F320" s="2"/>
-      <c r="G320" s="2"/>
-    </row>
-    <row r="321" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C321" s="2"/>
-      <c r="D321" s="2"/>
-      <c r="E321" s="2"/>
-      <c r="F321" s="2"/>
-      <c r="G321" s="2"/>
-    </row>
-    <row r="322" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C322" s="2"/>
-      <c r="D322" s="2"/>
-      <c r="E322" s="2"/>
-      <c r="F322" s="2"/>
-      <c r="G322" s="2"/>
-    </row>
-    <row r="323" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C323" s="2"/>
-      <c r="D323" s="2"/>
-      <c r="E323" s="2"/>
-      <c r="F323" s="2"/>
-      <c r="G323" s="2"/>
-    </row>
-    <row r="324" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C324" s="2"/>
-      <c r="D324" s="2"/>
-      <c r="E324" s="2"/>
-      <c r="F324" s="2"/>
-      <c r="G324" s="2"/>
-    </row>
-    <row r="325" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C325" s="2"/>
-      <c r="D325" s="2"/>
-      <c r="E325" s="2"/>
-      <c r="F325" s="2"/>
-      <c r="G325" s="2"/>
-    </row>
-    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C326" s="2"/>
-      <c r="D326" s="2"/>
-      <c r="E326" s="2"/>
-      <c r="F326" s="2"/>
-      <c r="G326" s="2"/>
-    </row>
-    <row r="327" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C327" s="2"/>
-      <c r="D327" s="2"/>
-      <c r="E327" s="2"/>
-      <c r="F327" s="2"/>
-      <c r="G327" s="2"/>
-    </row>
-    <row r="328" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C328" s="2"/>
-      <c r="D328" s="2"/>
-      <c r="E328" s="2"/>
-      <c r="F328" s="2"/>
-      <c r="G328" s="2"/>
-    </row>
-    <row r="329" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C329" s="2"/>
-      <c r="D329" s="2"/>
-      <c r="E329" s="2"/>
-      <c r="F329" s="2"/>
-      <c r="G329" s="2"/>
-    </row>
-    <row r="330" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C330" s="2"/>
-      <c r="D330" s="2"/>
-      <c r="E330" s="2"/>
-      <c r="F330" s="2"/>
-      <c r="G330" s="2"/>
-    </row>
-    <row r="331" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C331" s="2"/>
-      <c r="D331" s="2"/>
-      <c r="E331" s="2"/>
-      <c r="F331" s="2"/>
-      <c r="G331" s="2"/>
-    </row>
-    <row r="332" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C332" s="2"/>
-      <c r="D332" s="2"/>
-      <c r="E332" s="2"/>
-      <c r="F332" s="2"/>
-      <c r="G332" s="2"/>
-    </row>
-    <row r="333" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C333" s="2"/>
-      <c r="D333" s="2"/>
-      <c r="E333" s="2"/>
-      <c r="F333" s="2"/>
-      <c r="G333" s="2"/>
-    </row>
-    <row r="334" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C334" s="2"/>
-      <c r="D334" s="2"/>
-      <c r="E334" s="2"/>
-      <c r="F334" s="2"/>
-      <c r="G334" s="2"/>
-    </row>
-    <row r="335" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C335" s="2"/>
-      <c r="D335" s="2"/>
-      <c r="E335" s="2"/>
-      <c r="F335" s="2"/>
-      <c r="G335" s="2"/>
-    </row>
-    <row r="336" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C336" s="2"/>
-      <c r="D336" s="2"/>
-      <c r="E336" s="2"/>
-      <c r="F336" s="2"/>
-      <c r="G336" s="2"/>
-    </row>
-    <row r="337" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C337" s="2"/>
-      <c r="D337" s="2"/>
-      <c r="E337" s="2"/>
-      <c r="F337" s="2"/>
-      <c r="G337" s="2"/>
-    </row>
-    <row r="338" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C338" s="2"/>
-      <c r="D338" s="2"/>
-      <c r="E338" s="2"/>
-      <c r="F338" s="2"/>
-      <c r="G338" s="2"/>
-    </row>
-    <row r="339" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C339" s="2"/>
-      <c r="D339" s="2"/>
-      <c r="E339" s="2"/>
-      <c r="F339" s="2"/>
-      <c r="G339" s="2"/>
-    </row>
-    <row r="340" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C340" s="2"/>
-      <c r="D340" s="2"/>
-      <c r="E340" s="2"/>
-      <c r="F340" s="2"/>
-      <c r="G340" s="2"/>
-    </row>
-    <row r="341" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C341" s="2"/>
-      <c r="D341" s="2"/>
-      <c r="E341" s="2"/>
-      <c r="F341" s="2"/>
-      <c r="G341" s="2"/>
-    </row>
-    <row r="342" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C342" s="2"/>
-      <c r="D342" s="2"/>
-      <c r="E342" s="2"/>
-      <c r="F342" s="2"/>
-      <c r="G342" s="2"/>
-    </row>
-    <row r="343" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C343" s="2"/>
-      <c r="D343" s="2"/>
-      <c r="E343" s="2"/>
-      <c r="F343" s="2"/>
-      <c r="G343" s="2"/>
-    </row>
-    <row r="344" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C344" s="2"/>
-      <c r="D344" s="2"/>
-      <c r="E344" s="2"/>
-      <c r="F344" s="2"/>
-      <c r="G344" s="2"/>
-    </row>
-    <row r="345" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C345" s="2"/>
-      <c r="D345" s="2"/>
-      <c r="E345" s="2"/>
-      <c r="F345" s="2"/>
-      <c r="G345" s="2"/>
-    </row>
-    <row r="346" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C346" s="2"/>
-      <c r="D346" s="2"/>
-      <c r="E346" s="2"/>
-      <c r="F346" s="2"/>
-      <c r="G346" s="2"/>
-    </row>
-    <row r="347" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C347" s="2"/>
-      <c r="D347" s="2"/>
-      <c r="E347" s="2"/>
-      <c r="F347" s="2"/>
-      <c r="G347" s="2"/>
-    </row>
-    <row r="348" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C348" s="2"/>
-      <c r="D348" s="2"/>
-      <c r="E348" s="2"/>
-      <c r="F348" s="2"/>
-      <c r="G348" s="2"/>
-    </row>
-    <row r="349" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C349" s="2"/>
-      <c r="D349" s="2"/>
-      <c r="E349" s="2"/>
-      <c r="F349" s="2"/>
-      <c r="G349" s="2"/>
-    </row>
-    <row r="350" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C350" s="2"/>
-      <c r="D350" s="2"/>
-      <c r="E350" s="2"/>
-      <c r="F350" s="2"/>
-      <c r="G350" s="2"/>
-    </row>
-    <row r="351" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C351" s="2"/>
-      <c r="D351" s="2"/>
-      <c r="E351" s="2"/>
-      <c r="F351" s="2"/>
-      <c r="G351" s="2"/>
-    </row>
-    <row r="352" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C352" s="2"/>
-      <c r="D352" s="2"/>
-      <c r="E352" s="2"/>
-      <c r="F352" s="2"/>
-      <c r="G352" s="2"/>
-    </row>
-    <row r="353" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C353" s="2"/>
-      <c r="D353" s="2"/>
-      <c r="E353" s="2"/>
-      <c r="F353" s="2"/>
-      <c r="G353" s="2"/>
-    </row>
-    <row r="354" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C354" s="2"/>
-      <c r="D354" s="2"/>
-      <c r="E354" s="2"/>
-      <c r="F354" s="2"/>
-      <c r="G354" s="2"/>
-    </row>
-    <row r="355" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C355" s="2"/>
-      <c r="D355" s="2"/>
-      <c r="E355" s="2"/>
-      <c r="F355" s="2"/>
-      <c r="G355" s="2"/>
-    </row>
-    <row r="356" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C356" s="2"/>
-      <c r="D356" s="2"/>
-      <c r="E356" s="2"/>
-      <c r="F356" s="2"/>
-      <c r="G356" s="2"/>
-    </row>
-    <row r="357" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C357" s="2"/>
-      <c r="D357" s="2"/>
-      <c r="E357" s="2"/>
-      <c r="F357" s="2"/>
-      <c r="G357" s="2"/>
-    </row>
-    <row r="358" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C358" s="2"/>
-      <c r="D358" s="2"/>
-      <c r="E358" s="2"/>
-      <c r="F358" s="2"/>
-      <c r="G358" s="2"/>
-    </row>
-    <row r="359" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C359" s="2"/>
-      <c r="D359" s="2"/>
-      <c r="E359" s="2"/>
-      <c r="F359" s="2"/>
-      <c r="G359" s="2"/>
-    </row>
-    <row r="360" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C360" s="2"/>
-      <c r="D360" s="2"/>
-      <c r="E360" s="2"/>
-      <c r="F360" s="2"/>
-      <c r="G360" s="2"/>
-    </row>
-    <row r="361" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C361" s="2"/>
-      <c r="D361" s="2"/>
-      <c r="E361" s="2"/>
-      <c r="F361" s="2"/>
-      <c r="G361" s="2"/>
-    </row>
-    <row r="362" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C362" s="2"/>
-      <c r="D362" s="2"/>
-      <c r="E362" s="2"/>
-      <c r="F362" s="2"/>
-      <c r="G362" s="2"/>
-    </row>
-    <row r="363" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C363" s="2"/>
-      <c r="D363" s="2"/>
-      <c r="E363" s="2"/>
-      <c r="F363" s="2"/>
-      <c r="G363" s="2"/>
-    </row>
-    <row r="364" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C364" s="2"/>
-      <c r="D364" s="2"/>
-      <c r="E364" s="2"/>
-      <c r="F364" s="2"/>
-      <c r="G364" s="2"/>
-    </row>
-    <row r="365" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C365" s="2"/>
-      <c r="D365" s="2"/>
-      <c r="E365" s="2"/>
-      <c r="F365" s="2"/>
-      <c r="G365" s="2"/>
-    </row>
-    <row r="366" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C366" s="2"/>
-      <c r="D366" s="2"/>
-      <c r="E366" s="2"/>
-      <c r="F366" s="2"/>
-      <c r="G366" s="2"/>
-    </row>
-    <row r="367" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C367" s="2"/>
-      <c r="D367" s="2"/>
-      <c r="E367" s="2"/>
-      <c r="F367" s="2"/>
-      <c r="G367" s="2"/>
-    </row>
-    <row r="368" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C368" s="2"/>
-      <c r="D368" s="2"/>
-      <c r="E368" s="2"/>
-      <c r="F368" s="2"/>
-      <c r="G368" s="2"/>
-    </row>
-    <row r="369" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C369" s="2"/>
-      <c r="D369" s="2"/>
-      <c r="E369" s="2"/>
-      <c r="F369" s="2"/>
-      <c r="G369" s="2"/>
-    </row>
-    <row r="370" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C370" s="2"/>
-      <c r="D370" s="2"/>
-      <c r="E370" s="2"/>
-      <c r="F370" s="2"/>
-      <c r="G370" s="2"/>
-    </row>
-    <row r="371" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C371" s="2"/>
-      <c r="D371" s="2"/>
-      <c r="E371" s="2"/>
-      <c r="F371" s="2"/>
-      <c r="G371" s="2"/>
-    </row>
-    <row r="372" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C372" s="2"/>
-      <c r="D372" s="2"/>
-      <c r="E372" s="2"/>
-      <c r="F372" s="2"/>
-      <c r="G372" s="2"/>
-    </row>
-    <row r="373" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C373" s="2"/>
-      <c r="D373" s="2"/>
-      <c r="E373" s="2"/>
-      <c r="F373" s="2"/>
-      <c r="G373" s="2"/>
-    </row>
-    <row r="374" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C374" s="2"/>
-      <c r="D374" s="2"/>
-      <c r="E374" s="2"/>
-      <c r="F374" s="2"/>
-      <c r="G374" s="2"/>
-    </row>
-    <row r="375" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C375" s="2"/>
-      <c r="D375" s="2"/>
-      <c r="E375" s="2"/>
-      <c r="F375" s="2"/>
-      <c r="G375" s="2"/>
-    </row>
-    <row r="376" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C376" s="2"/>
-      <c r="D376" s="2"/>
-      <c r="E376" s="2"/>
-      <c r="F376" s="2"/>
-      <c r="G376" s="2"/>
-    </row>
-    <row r="377" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C377" s="2"/>
-      <c r="D377" s="2"/>
-      <c r="E377" s="2"/>
-      <c r="F377" s="2"/>
-      <c r="G377" s="2"/>
-    </row>
-    <row r="378" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C378" s="2"/>
-      <c r="D378" s="2"/>
-      <c r="E378" s="2"/>
-      <c r="F378" s="2"/>
-      <c r="G378" s="2"/>
-    </row>
-    <row r="379" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C379" s="2"/>
-      <c r="D379" s="2"/>
-      <c r="E379" s="2"/>
-      <c r="F379" s="2"/>
-      <c r="G379" s="2"/>
-    </row>
-    <row r="380" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C380" s="2"/>
-      <c r="D380" s="2"/>
-      <c r="E380" s="2"/>
-      <c r="F380" s="2"/>
-      <c r="G380" s="2"/>
-    </row>
-    <row r="381" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C381" s="2"/>
-      <c r="D381" s="2"/>
-      <c r="E381" s="2"/>
-      <c r="F381" s="2"/>
-      <c r="G381" s="2"/>
-    </row>
-    <row r="382" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C382" s="2"/>
-      <c r="D382" s="2"/>
-      <c r="E382" s="2"/>
-      <c r="F382" s="2"/>
-      <c r="G382" s="2"/>
-    </row>
-    <row r="383" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C383" s="2"/>
-      <c r="D383" s="2"/>
-      <c r="E383" s="2"/>
-      <c r="F383" s="2"/>
-      <c r="G383" s="2"/>
-    </row>
-    <row r="384" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C384" s="2"/>
-      <c r="D384" s="2"/>
-      <c r="E384" s="2"/>
-      <c r="F384" s="2"/>
-      <c r="G384" s="2"/>
-    </row>
-    <row r="385" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C385" s="2"/>
-      <c r="D385" s="2"/>
-      <c r="E385" s="2"/>
-      <c r="F385" s="2"/>
-      <c r="G385" s="2"/>
-    </row>
-    <row r="386" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C386" s="2"/>
-      <c r="D386" s="2"/>
-      <c r="E386" s="2"/>
-      <c r="F386" s="2"/>
-      <c r="G386" s="2"/>
-    </row>
-    <row r="387" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C387" s="2"/>
-      <c r="D387" s="2"/>
-      <c r="E387" s="2"/>
-      <c r="F387" s="2"/>
-      <c r="G387" s="2"/>
-    </row>
-    <row r="388" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C388" s="2"/>
-      <c r="D388" s="2"/>
-      <c r="E388" s="2"/>
-      <c r="F388" s="2"/>
-      <c r="G388" s="2"/>
-    </row>
-    <row r="389" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C389" s="2"/>
-      <c r="D389" s="2"/>
-      <c r="E389" s="2"/>
-      <c r="F389" s="2"/>
-      <c r="G389" s="2"/>
-    </row>
-    <row r="390" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C390" s="2"/>
-      <c r="D390" s="2"/>
-      <c r="E390" s="2"/>
-      <c r="F390" s="2"/>
-      <c r="G390" s="2"/>
-    </row>
-    <row r="391" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C391" s="2"/>
-      <c r="D391" s="2"/>
-      <c r="E391" s="2"/>
-      <c r="F391" s="2"/>
-      <c r="G391" s="2"/>
-    </row>
-    <row r="392" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C392" s="2"/>
-      <c r="D392" s="2"/>
-      <c r="E392" s="2"/>
-      <c r="F392" s="2"/>
-      <c r="G392" s="2"/>
-    </row>
-    <row r="393" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C393" s="2"/>
-      <c r="D393" s="2"/>
-      <c r="E393" s="2"/>
-      <c r="F393" s="2"/>
-      <c r="G393" s="2"/>
-    </row>
-    <row r="394" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C394" s="2"/>
-      <c r="D394" s="2"/>
-      <c r="E394" s="2"/>
-      <c r="F394" s="2"/>
-      <c r="G394" s="2"/>
-    </row>
-    <row r="395" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C395" s="2"/>
-      <c r="D395" s="2"/>
-      <c r="E395" s="2"/>
-      <c r="F395" s="2"/>
-      <c r="G395" s="2"/>
-    </row>
-    <row r="396" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C396" s="2"/>
-      <c r="D396" s="2"/>
-      <c r="E396" s="2"/>
-      <c r="F396" s="2"/>
-      <c r="G396" s="2"/>
-    </row>
-    <row r="397" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C397" s="2"/>
-      <c r="D397" s="2"/>
-      <c r="E397" s="2"/>
-      <c r="F397" s="2"/>
-      <c r="G397" s="2"/>
-    </row>
-    <row r="398" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C398" s="2"/>
-      <c r="D398" s="2"/>
-      <c r="E398" s="2"/>
-      <c r="F398" s="2"/>
-      <c r="G398" s="2"/>
-    </row>
-    <row r="399" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C399" s="2"/>
-      <c r="D399" s="2"/>
-      <c r="E399" s="2"/>
-      <c r="F399" s="2"/>
-      <c r="G399" s="2"/>
-    </row>
-    <row r="400" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C400" s="2"/>
-      <c r="D400" s="2"/>
-      <c r="E400" s="2"/>
-      <c r="F400" s="2"/>
-      <c r="G400" s="2"/>
-    </row>
-    <row r="401" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C401" s="2"/>
-      <c r="D401" s="2"/>
-      <c r="E401" s="2"/>
-      <c r="F401" s="2"/>
-      <c r="G401" s="2"/>
-    </row>
-    <row r="402" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C402" s="2"/>
-      <c r="D402" s="2"/>
-      <c r="E402" s="2"/>
-      <c r="F402" s="2"/>
-      <c r="G402" s="2"/>
-    </row>
-    <row r="403" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C403" s="2"/>
-      <c r="D403" s="2"/>
-      <c r="E403" s="2"/>
-      <c r="F403" s="2"/>
-      <c r="G403" s="2"/>
-    </row>
-    <row r="404" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C404" s="2"/>
-      <c r="D404" s="2"/>
-      <c r="E404" s="2"/>
-      <c r="F404" s="2"/>
-      <c r="G404" s="2"/>
-    </row>
-    <row r="405" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C405" s="2"/>
-      <c r="D405" s="2"/>
-      <c r="E405" s="2"/>
-      <c r="F405" s="2"/>
-      <c r="G405" s="2"/>
-    </row>
-    <row r="406" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C406" s="2"/>
-      <c r="D406" s="2"/>
-      <c r="E406" s="2"/>
-      <c r="F406" s="2"/>
-      <c r="G406" s="2"/>
-    </row>
-    <row r="407" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C407" s="2"/>
-      <c r="D407" s="2"/>
-      <c r="E407" s="2"/>
-      <c r="F407" s="2"/>
-      <c r="G407" s="2"/>
-    </row>
-    <row r="408" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C408" s="2"/>
-      <c r="D408" s="2"/>
-      <c r="E408" s="2"/>
-      <c r="F408" s="2"/>
-      <c r="G408" s="2"/>
-    </row>
-    <row r="409" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C409" s="2"/>
-      <c r="D409" s="2"/>
-      <c r="E409" s="2"/>
-      <c r="F409" s="2"/>
-      <c r="G409" s="2"/>
-    </row>
-    <row r="410" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C410" s="2"/>
-      <c r="D410" s="2"/>
-      <c r="E410" s="2"/>
-      <c r="F410" s="2"/>
-      <c r="G410" s="2"/>
-    </row>
-    <row r="411" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C411" s="2"/>
-      <c r="D411" s="2"/>
-      <c r="E411" s="2"/>
-      <c r="F411" s="2"/>
-      <c r="G411" s="2"/>
-    </row>
-    <row r="412" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C412" s="2"/>
-      <c r="D412" s="2"/>
-      <c r="E412" s="2"/>
-      <c r="F412" s="2"/>
-      <c r="G412" s="2"/>
-    </row>
-    <row r="413" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C413" s="2"/>
-      <c r="D413" s="2"/>
-      <c r="E413" s="2"/>
-      <c r="F413" s="2"/>
-      <c r="G413" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37F3A864-C585-421C-A8F8-7E679BFCCC8A}">
   <dimension ref="A1:G412"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10272,23 +7319,23 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C71)</f>
-        <v>-4731.0999999999995</v>
+        <v>-574.97000000000014</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>-1534.3400000000001</v>
+        <v>-420.98</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
-        <v>-860.29</v>
+        <v>-71.400000000000006</v>
       </c>
       <c r="F1" s="2">
         <f t="shared" si="0"/>
-        <v>-780.3</v>
+        <v>-71.400000000000006</v>
       </c>
       <c r="G1" s="2">
         <f t="shared" si="0"/>
-        <v>-780.3</v>
+        <v>-71.400000000000006</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -10315,88 +7362,94 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="2">
-        <v>-199.3</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="A3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="8">
+        <v>-44.9</v>
+      </c>
+      <c r="D3" s="6">
+        <v>-44.9</v>
+      </c>
+      <c r="E3" s="6">
+        <v>-44.9</v>
+      </c>
+      <c r="F3" s="6">
+        <v>-44.9</v>
+      </c>
+      <c r="G3" s="6">
+        <v>-44.9</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="2">
-        <v>-176.6</v>
-      </c>
-      <c r="D4" s="2">
-        <v>-176.6</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="A4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="8">
+        <v>-26.5</v>
+      </c>
+      <c r="D4" s="6">
+        <v>-26.5</v>
+      </c>
+      <c r="E4" s="6">
+        <v>-26.5</v>
+      </c>
+      <c r="F4" s="6">
+        <v>-26.5</v>
+      </c>
+      <c r="G4" s="6">
+        <v>-26.5</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="2">
-        <v>-149.99</v>
-      </c>
-      <c r="D5" s="2">
-        <v>-149.99</v>
-      </c>
-      <c r="E5" s="2">
-        <v>-149.99</v>
-      </c>
-      <c r="F5" s="2">
-        <v>-149.99</v>
-      </c>
-      <c r="G5" s="2">
-        <v>-149.99</v>
-      </c>
+      <c r="A5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="8">
+        <v>-49.97</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="2">
-        <v>-67.900000000000006</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="A6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="8">
+        <v>-154.34</v>
+      </c>
+      <c r="D6" s="6">
+        <v>-154.34</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="2">
-        <v>-79.989999999999995</v>
+        <v>79</v>
+      </c>
+      <c r="C7" s="7">
+        <v>-111</v>
       </c>
       <c r="D7" s="2">
-        <v>-79.989999999999995</v>
-      </c>
-      <c r="E7" s="2">
-        <v>-79.989999999999995</v>
-      </c>
+        <v>-111</v>
+      </c>
+      <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="2">
-        <v>-497.45</v>
+        <v>80</v>
+      </c>
+      <c r="C8" s="7">
+        <v>-84.24</v>
       </c>
       <c r="D8" s="2">
-        <v>-497.45</v>
+        <v>-84.24</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -10404,10 +7457,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="2">
-        <v>-58.33</v>
+        <v>83</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-14.99</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -10416,10 +7469,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="C10" s="2">
-        <v>-89.36</v>
+        <v>-57.99</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -10428,30 +7481,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="2">
-        <v>-160</v>
-      </c>
-      <c r="D11" s="2">
-        <v>-160</v>
-      </c>
-      <c r="E11" s="2">
-        <v>-160</v>
-      </c>
-      <c r="F11" s="2">
-        <v>-160</v>
-      </c>
-      <c r="G11" s="2">
-        <v>-160</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-17.95</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="2">
-        <v>-160.5</v>
+        <v>90</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-13.09</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -10459,378 +7504,3405 @@
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="2">
-        <v>-31.9</v>
-      </c>
-      <c r="D13" s="2">
-        <v>-31.9</v>
-      </c>
-      <c r="E13" s="2">
-        <v>-31.9</v>
-      </c>
-      <c r="F13" s="2">
-        <v>-31.9</v>
-      </c>
-      <c r="G13" s="2">
-        <v>-31.9</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="2">
-        <v>-293</v>
-      </c>
-      <c r="D14" s="2">
-        <v>-293</v>
-      </c>
-      <c r="E14" s="2">
-        <v>-293</v>
-      </c>
-      <c r="F14" s="2">
-        <v>-293</v>
-      </c>
-      <c r="G14" s="2">
-        <v>-293</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="2">
-        <v>-131.51</v>
-      </c>
-      <c r="D15" s="2">
-        <v>-131.51</v>
-      </c>
-      <c r="E15" s="2">
-        <v>-131.51</v>
-      </c>
-      <c r="F15" s="2">
-        <v>-131.51</v>
-      </c>
-      <c r="G15" s="2">
-        <v>-131.51</v>
-      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="2">
-        <v>-324.57</v>
-      </c>
+      <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="2">
-        <v>-411</v>
-      </c>
+    <row r="17" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="2">
-        <v>-169.06</v>
-      </c>
+    <row r="18" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="2">
-        <v>-30</v>
-      </c>
+    <row r="19" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="2">
-        <v>-224.9</v>
-      </c>
+    <row r="20" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="2">
-        <v>-150</v>
-      </c>
+    <row r="21" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="2">
-        <v>-43.66</v>
-      </c>
+    <row r="22" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="2">
-        <v>-37.5</v>
-      </c>
+    <row r="23" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="2">
-        <v>-79.989999999999995</v>
-      </c>
+    <row r="24" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="2">
-        <v>-19</v>
-      </c>
+    <row r="25" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" s="2">
-        <v>-15</v>
-      </c>
+    <row r="26" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="2">
-        <v>-100</v>
-      </c>
+    <row r="27" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" s="2">
-        <v>-225</v>
-      </c>
+    <row r="28" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>101</v>
-      </c>
-      <c r="C29" s="2">
-        <v>-115.41</v>
-      </c>
+    <row r="29" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" s="2">
-        <v>-21.9</v>
-      </c>
+    <row r="30" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" s="2">
-        <v>-92.62</v>
-      </c>
+    <row r="31" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="2">
-        <v>-155.13</v>
-      </c>
+    <row r="32" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>90</v>
-      </c>
-      <c r="C33" s="2">
-        <v>-376.63</v>
-      </c>
+    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" s="2">
-        <v>-13.9</v>
-      </c>
-      <c r="D34" s="2">
-        <v>-13.9</v>
-      </c>
-      <c r="E34" s="2">
-        <v>-13.9</v>
-      </c>
-      <c r="F34" s="2">
-        <v>-13.9</v>
-      </c>
-      <c r="G34" s="2">
-        <v>-13.9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>104</v>
-      </c>
-      <c r="C35" s="2">
-        <v>-30</v>
-      </c>
+    <row r="34" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
+    <row r="45" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+    </row>
+    <row r="46" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="52" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+    </row>
+    <row r="54" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+    </row>
+    <row r="55" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+    </row>
+    <row r="56" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+    </row>
+    <row r="57" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+    </row>
+    <row r="59" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+    </row>
+    <row r="60" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+    </row>
+    <row r="61" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+    </row>
+    <row r="62" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+    </row>
+    <row r="63" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+    </row>
+    <row r="64" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+    </row>
+    <row r="65" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+    </row>
+    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+    </row>
+    <row r="67" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+    </row>
+    <row r="68" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+    </row>
+    <row r="69" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+    </row>
+    <row r="70" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+    </row>
+    <row r="71" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+    </row>
+    <row r="72" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+    </row>
+    <row r="73" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+    </row>
+    <row r="74" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+    </row>
+    <row r="75" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+    </row>
+    <row r="76" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+    </row>
+    <row r="77" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+    </row>
+    <row r="78" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+    </row>
+    <row r="79" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+    </row>
+    <row r="80" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+    </row>
+    <row r="81" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+    </row>
+    <row r="82" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+    </row>
+    <row r="83" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+    </row>
+    <row r="84" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+    </row>
+    <row r="85" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+    </row>
+    <row r="86" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+    </row>
+    <row r="87" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+    </row>
+    <row r="88" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+    </row>
+    <row r="89" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+    </row>
+    <row r="90" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+    </row>
+    <row r="91" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+    </row>
+    <row r="92" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+    </row>
+    <row r="93" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+    </row>
+    <row r="94" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+    </row>
+    <row r="95" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+    </row>
+    <row r="96" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+    </row>
+    <row r="97" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+    </row>
+    <row r="98" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+    </row>
+    <row r="99" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+    </row>
+    <row r="100" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+    </row>
+    <row r="101" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+    </row>
+    <row r="102" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+    </row>
+    <row r="103" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+    </row>
+    <row r="104" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+    </row>
+    <row r="105" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+    </row>
+    <row r="106" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+    </row>
+    <row r="107" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+    </row>
+    <row r="108" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+    </row>
+    <row r="109" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+    </row>
+    <row r="110" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+    </row>
+    <row r="111" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+    </row>
+    <row r="112" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+    </row>
+    <row r="113" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+    </row>
+    <row r="114" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+    </row>
+    <row r="115" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+    </row>
+    <row r="116" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+    </row>
+    <row r="117" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+    </row>
+    <row r="118" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+    </row>
+    <row r="119" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+    </row>
+    <row r="120" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+    </row>
+    <row r="121" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+    </row>
+    <row r="122" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+    </row>
+    <row r="123" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+    </row>
+    <row r="124" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+    </row>
+    <row r="125" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="2"/>
+    </row>
+    <row r="126" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+    </row>
+    <row r="127" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="2"/>
+    </row>
+    <row r="128" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="2"/>
+    </row>
+    <row r="129" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="2"/>
+    </row>
+    <row r="130" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="2"/>
+    </row>
+    <row r="131" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
+      <c r="G131" s="2"/>
+    </row>
+    <row r="132" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+      <c r="F132" s="2"/>
+      <c r="G132" s="2"/>
+    </row>
+    <row r="133" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+    </row>
+    <row r="134" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
+      <c r="F134" s="2"/>
+      <c r="G134" s="2"/>
+    </row>
+    <row r="135" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
+      <c r="G135" s="2"/>
+    </row>
+    <row r="136" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="2"/>
+    </row>
+    <row r="137" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="2"/>
+    </row>
+    <row r="138" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+      <c r="F138" s="2"/>
+      <c r="G138" s="2"/>
+    </row>
+    <row r="139" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+      <c r="F139" s="2"/>
+      <c r="G139" s="2"/>
+    </row>
+    <row r="140" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
+      <c r="F140" s="2"/>
+      <c r="G140" s="2"/>
+    </row>
+    <row r="141" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
+      <c r="F141" s="2"/>
+      <c r="G141" s="2"/>
+    </row>
+    <row r="142" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
+      <c r="F142" s="2"/>
+      <c r="G142" s="2"/>
+    </row>
+    <row r="143" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2"/>
+      <c r="F143" s="2"/>
+      <c r="G143" s="2"/>
+    </row>
+    <row r="144" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
+      <c r="F144" s="2"/>
+      <c r="G144" s="2"/>
+    </row>
+    <row r="145" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2"/>
+      <c r="F145" s="2"/>
+      <c r="G145" s="2"/>
+    </row>
+    <row r="146" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2"/>
+      <c r="G146" s="2"/>
+    </row>
+    <row r="147" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
+      <c r="F147" s="2"/>
+      <c r="G147" s="2"/>
+    </row>
+    <row r="148" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2"/>
+      <c r="F148" s="2"/>
+      <c r="G148" s="2"/>
+    </row>
+    <row r="149" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2"/>
+      <c r="F149" s="2"/>
+      <c r="G149" s="2"/>
+    </row>
+    <row r="150" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2"/>
+      <c r="G150" s="2"/>
+    </row>
+    <row r="151" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+      <c r="F151" s="2"/>
+      <c r="G151" s="2"/>
+    </row>
+    <row r="152" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+      <c r="F152" s="2"/>
+      <c r="G152" s="2"/>
+    </row>
+    <row r="153" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2"/>
+      <c r="G153" s="2"/>
+    </row>
+    <row r="154" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+      <c r="F154" s="2"/>
+      <c r="G154" s="2"/>
+    </row>
+    <row r="155" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+      <c r="F155" s="2"/>
+      <c r="G155" s="2"/>
+    </row>
+    <row r="156" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+      <c r="F156" s="2"/>
+      <c r="G156" s="2"/>
+    </row>
+    <row r="157" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
+      <c r="F157" s="2"/>
+      <c r="G157" s="2"/>
+    </row>
+    <row r="158" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="2"/>
+      <c r="F158" s="2"/>
+      <c r="G158" s="2"/>
+    </row>
+    <row r="159" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+      <c r="E159" s="2"/>
+      <c r="F159" s="2"/>
+      <c r="G159" s="2"/>
+    </row>
+    <row r="160" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+      <c r="E160" s="2"/>
+      <c r="F160" s="2"/>
+      <c r="G160" s="2"/>
+    </row>
+    <row r="161" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+      <c r="E161" s="2"/>
+      <c r="F161" s="2"/>
+      <c r="G161" s="2"/>
+    </row>
+    <row r="162" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+      <c r="E162" s="2"/>
+      <c r="F162" s="2"/>
+      <c r="G162" s="2"/>
+    </row>
+    <row r="163" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+      <c r="E163" s="2"/>
+      <c r="F163" s="2"/>
+      <c r="G163" s="2"/>
+    </row>
+    <row r="164" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="2"/>
+      <c r="F164" s="2"/>
+      <c r="G164" s="2"/>
+    </row>
+    <row r="165" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2"/>
+      <c r="G165" s="2"/>
+    </row>
+    <row r="166" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="2"/>
+      <c r="F166" s="2"/>
+      <c r="G166" s="2"/>
+    </row>
+    <row r="167" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="2"/>
+      <c r="F167" s="2"/>
+      <c r="G167" s="2"/>
+    </row>
+    <row r="168" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+      <c r="E168" s="2"/>
+      <c r="F168" s="2"/>
+      <c r="G168" s="2"/>
+    </row>
+    <row r="169" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+      <c r="E169" s="2"/>
+      <c r="F169" s="2"/>
+      <c r="G169" s="2"/>
+    </row>
+    <row r="170" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="2"/>
+    </row>
+    <row r="171" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
+      <c r="F171" s="2"/>
+      <c r="G171" s="2"/>
+    </row>
+    <row r="172" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
+      <c r="G172" s="2"/>
+    </row>
+    <row r="173" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+    </row>
+    <row r="174" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+    </row>
+    <row r="175" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+      <c r="E175" s="2"/>
+      <c r="F175" s="2"/>
+      <c r="G175" s="2"/>
+    </row>
+    <row r="176" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
+      <c r="E176" s="2"/>
+      <c r="F176" s="2"/>
+      <c r="G176" s="2"/>
+    </row>
+    <row r="177" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2"/>
+      <c r="G177" s="2"/>
+    </row>
+    <row r="178" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+      <c r="E178" s="2"/>
+      <c r="F178" s="2"/>
+      <c r="G178" s="2"/>
+    </row>
+    <row r="179" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
+      <c r="E179" s="2"/>
+      <c r="F179" s="2"/>
+      <c r="G179" s="2"/>
+    </row>
+    <row r="180" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
+      <c r="E180" s="2"/>
+      <c r="F180" s="2"/>
+      <c r="G180" s="2"/>
+    </row>
+    <row r="181" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
+      <c r="E181" s="2"/>
+      <c r="F181" s="2"/>
+      <c r="G181" s="2"/>
+    </row>
+    <row r="182" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C182" s="2"/>
+      <c r="D182" s="2"/>
+      <c r="E182" s="2"/>
+      <c r="F182" s="2"/>
+      <c r="G182" s="2"/>
+    </row>
+    <row r="183" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
+      <c r="E183" s="2"/>
+      <c r="F183" s="2"/>
+      <c r="G183" s="2"/>
+    </row>
+    <row r="184" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
+      <c r="E184" s="2"/>
+      <c r="F184" s="2"/>
+      <c r="G184" s="2"/>
+    </row>
+    <row r="185" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
+      <c r="E185" s="2"/>
+      <c r="F185" s="2"/>
+      <c r="G185" s="2"/>
+    </row>
+    <row r="186" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
+      <c r="E186" s="2"/>
+      <c r="F186" s="2"/>
+      <c r="G186" s="2"/>
+    </row>
+    <row r="187" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
+      <c r="E187" s="2"/>
+      <c r="F187" s="2"/>
+      <c r="G187" s="2"/>
+    </row>
+    <row r="188" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
+      <c r="E188" s="2"/>
+      <c r="F188" s="2"/>
+      <c r="G188" s="2"/>
+    </row>
+    <row r="189" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C189" s="2"/>
+      <c r="D189" s="2"/>
+      <c r="E189" s="2"/>
+      <c r="F189" s="2"/>
+      <c r="G189" s="2"/>
+    </row>
+    <row r="190" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C190" s="2"/>
+      <c r="D190" s="2"/>
+      <c r="E190" s="2"/>
+      <c r="F190" s="2"/>
+      <c r="G190" s="2"/>
+    </row>
+    <row r="191" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C191" s="2"/>
+      <c r="D191" s="2"/>
+      <c r="E191" s="2"/>
+      <c r="F191" s="2"/>
+      <c r="G191" s="2"/>
+    </row>
+    <row r="192" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
+      <c r="E192" s="2"/>
+      <c r="F192" s="2"/>
+      <c r="G192" s="2"/>
+    </row>
+    <row r="193" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C193" s="2"/>
+      <c r="D193" s="2"/>
+      <c r="E193" s="2"/>
+      <c r="F193" s="2"/>
+      <c r="G193" s="2"/>
+    </row>
+    <row r="194" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C194" s="2"/>
+      <c r="D194" s="2"/>
+      <c r="E194" s="2"/>
+      <c r="F194" s="2"/>
+      <c r="G194" s="2"/>
+    </row>
+    <row r="195" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C195" s="2"/>
+      <c r="D195" s="2"/>
+      <c r="E195" s="2"/>
+      <c r="F195" s="2"/>
+      <c r="G195" s="2"/>
+    </row>
+    <row r="196" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C196" s="2"/>
+      <c r="D196" s="2"/>
+      <c r="E196" s="2"/>
+      <c r="F196" s="2"/>
+      <c r="G196" s="2"/>
+    </row>
+    <row r="197" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
+      <c r="E197" s="2"/>
+      <c r="F197" s="2"/>
+      <c r="G197" s="2"/>
+    </row>
+    <row r="198" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
+      <c r="E198" s="2"/>
+      <c r="F198" s="2"/>
+      <c r="G198" s="2"/>
+    </row>
+    <row r="199" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
+      <c r="E199" s="2"/>
+      <c r="F199" s="2"/>
+      <c r="G199" s="2"/>
+    </row>
+    <row r="200" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
+      <c r="E200" s="2"/>
+      <c r="F200" s="2"/>
+      <c r="G200" s="2"/>
+    </row>
+    <row r="201" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C201" s="2"/>
+      <c r="D201" s="2"/>
+      <c r="E201" s="2"/>
+      <c r="F201" s="2"/>
+      <c r="G201" s="2"/>
+    </row>
+    <row r="202" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C202" s="2"/>
+      <c r="D202" s="2"/>
+      <c r="E202" s="2"/>
+      <c r="F202" s="2"/>
+      <c r="G202" s="2"/>
+    </row>
+    <row r="203" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C203" s="2"/>
+      <c r="D203" s="2"/>
+      <c r="E203" s="2"/>
+      <c r="F203" s="2"/>
+      <c r="G203" s="2"/>
+    </row>
+    <row r="204" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
+      <c r="E204" s="2"/>
+      <c r="F204" s="2"/>
+      <c r="G204" s="2"/>
+    </row>
+    <row r="205" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C205" s="2"/>
+      <c r="D205" s="2"/>
+      <c r="E205" s="2"/>
+      <c r="F205" s="2"/>
+      <c r="G205" s="2"/>
+    </row>
+    <row r="206" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C206" s="2"/>
+      <c r="D206" s="2"/>
+      <c r="E206" s="2"/>
+      <c r="F206" s="2"/>
+      <c r="G206" s="2"/>
+    </row>
+    <row r="207" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C207" s="2"/>
+      <c r="D207" s="2"/>
+      <c r="E207" s="2"/>
+      <c r="F207" s="2"/>
+      <c r="G207" s="2"/>
+    </row>
+    <row r="208" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C208" s="2"/>
+      <c r="D208" s="2"/>
+      <c r="E208" s="2"/>
+      <c r="F208" s="2"/>
+      <c r="G208" s="2"/>
+    </row>
+    <row r="209" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C209" s="2"/>
+      <c r="D209" s="2"/>
+      <c r="E209" s="2"/>
+      <c r="F209" s="2"/>
+      <c r="G209" s="2"/>
+    </row>
+    <row r="210" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C210" s="2"/>
+      <c r="D210" s="2"/>
+      <c r="E210" s="2"/>
+      <c r="F210" s="2"/>
+      <c r="G210" s="2"/>
+    </row>
+    <row r="211" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
+      <c r="E211" s="2"/>
+      <c r="F211" s="2"/>
+      <c r="G211" s="2"/>
+    </row>
+    <row r="212" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C212" s="2"/>
+      <c r="D212" s="2"/>
+      <c r="E212" s="2"/>
+      <c r="F212" s="2"/>
+      <c r="G212" s="2"/>
+    </row>
+    <row r="213" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C213" s="2"/>
+      <c r="D213" s="2"/>
+      <c r="E213" s="2"/>
+      <c r="F213" s="2"/>
+      <c r="G213" s="2"/>
+    </row>
+    <row r="214" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C214" s="2"/>
+      <c r="D214" s="2"/>
+      <c r="E214" s="2"/>
+      <c r="F214" s="2"/>
+      <c r="G214" s="2"/>
+    </row>
+    <row r="215" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+      <c r="E215" s="2"/>
+      <c r="F215" s="2"/>
+      <c r="G215" s="2"/>
+    </row>
+    <row r="216" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C216" s="2"/>
+      <c r="D216" s="2"/>
+      <c r="E216" s="2"/>
+      <c r="F216" s="2"/>
+      <c r="G216" s="2"/>
+    </row>
+    <row r="217" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C217" s="2"/>
+      <c r="D217" s="2"/>
+      <c r="E217" s="2"/>
+      <c r="F217" s="2"/>
+      <c r="G217" s="2"/>
+    </row>
+    <row r="218" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
+      <c r="E218" s="2"/>
+      <c r="F218" s="2"/>
+      <c r="G218" s="2"/>
+    </row>
+    <row r="219" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C219" s="2"/>
+      <c r="D219" s="2"/>
+      <c r="E219" s="2"/>
+      <c r="F219" s="2"/>
+      <c r="G219" s="2"/>
+    </row>
+    <row r="220" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="2"/>
+    </row>
+    <row r="221" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
+      <c r="E221" s="2"/>
+      <c r="F221" s="2"/>
+      <c r="G221" s="2"/>
+    </row>
+    <row r="222" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
+      <c r="E222" s="2"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="2"/>
+    </row>
+    <row r="223" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
+      <c r="G223" s="2"/>
+    </row>
+    <row r="224" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
+      <c r="E224" s="2"/>
+      <c r="F224" s="2"/>
+      <c r="G224" s="2"/>
+    </row>
+    <row r="225" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C225" s="2"/>
+      <c r="D225" s="2"/>
+      <c r="E225" s="2"/>
+      <c r="F225" s="2"/>
+      <c r="G225" s="2"/>
+    </row>
+    <row r="226" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C226" s="2"/>
+      <c r="D226" s="2"/>
+      <c r="E226" s="2"/>
+      <c r="F226" s="2"/>
+      <c r="G226" s="2"/>
+    </row>
+    <row r="227" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C227" s="2"/>
+      <c r="D227" s="2"/>
+      <c r="E227" s="2"/>
+      <c r="F227" s="2"/>
+      <c r="G227" s="2"/>
+    </row>
+    <row r="228" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C228" s="2"/>
+      <c r="D228" s="2"/>
+      <c r="E228" s="2"/>
+      <c r="F228" s="2"/>
+      <c r="G228" s="2"/>
+    </row>
+    <row r="229" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C229" s="2"/>
+      <c r="D229" s="2"/>
+      <c r="E229" s="2"/>
+      <c r="F229" s="2"/>
+      <c r="G229" s="2"/>
+    </row>
+    <row r="230" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C230" s="2"/>
+      <c r="D230" s="2"/>
+      <c r="E230" s="2"/>
+      <c r="F230" s="2"/>
+      <c r="G230" s="2"/>
+    </row>
+    <row r="231" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C231" s="2"/>
+      <c r="D231" s="2"/>
+      <c r="E231" s="2"/>
+      <c r="F231" s="2"/>
+      <c r="G231" s="2"/>
+    </row>
+    <row r="232" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C232" s="2"/>
+      <c r="D232" s="2"/>
+      <c r="E232" s="2"/>
+      <c r="F232" s="2"/>
+      <c r="G232" s="2"/>
+    </row>
+    <row r="233" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C233" s="2"/>
+      <c r="D233" s="2"/>
+      <c r="E233" s="2"/>
+      <c r="F233" s="2"/>
+      <c r="G233" s="2"/>
+    </row>
+    <row r="234" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C234" s="2"/>
+      <c r="D234" s="2"/>
+      <c r="E234" s="2"/>
+      <c r="F234" s="2"/>
+      <c r="G234" s="2"/>
+    </row>
+    <row r="235" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C235" s="2"/>
+      <c r="D235" s="2"/>
+      <c r="E235" s="2"/>
+      <c r="F235" s="2"/>
+      <c r="G235" s="2"/>
+    </row>
+    <row r="236" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C236" s="2"/>
+      <c r="D236" s="2"/>
+      <c r="E236" s="2"/>
+      <c r="F236" s="2"/>
+      <c r="G236" s="2"/>
+    </row>
+    <row r="237" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C237" s="2"/>
+      <c r="D237" s="2"/>
+      <c r="E237" s="2"/>
+      <c r="F237" s="2"/>
+      <c r="G237" s="2"/>
+    </row>
+    <row r="238" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C238" s="2"/>
+      <c r="D238" s="2"/>
+      <c r="E238" s="2"/>
+      <c r="F238" s="2"/>
+      <c r="G238" s="2"/>
+    </row>
+    <row r="239" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
+      <c r="E239" s="2"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="2"/>
+    </row>
+    <row r="240" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
+      <c r="E240" s="2"/>
+      <c r="F240" s="2"/>
+      <c r="G240" s="2"/>
+    </row>
+    <row r="241" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C241" s="2"/>
+      <c r="D241" s="2"/>
+      <c r="E241" s="2"/>
+      <c r="F241" s="2"/>
+      <c r="G241" s="2"/>
+    </row>
+    <row r="242" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C242" s="2"/>
+      <c r="D242" s="2"/>
+      <c r="E242" s="2"/>
+      <c r="F242" s="2"/>
+      <c r="G242" s="2"/>
+    </row>
+    <row r="243" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C243" s="2"/>
+      <c r="D243" s="2"/>
+      <c r="E243" s="2"/>
+      <c r="F243" s="2"/>
+      <c r="G243" s="2"/>
+    </row>
+    <row r="244" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C244" s="2"/>
+      <c r="D244" s="2"/>
+      <c r="E244" s="2"/>
+      <c r="F244" s="2"/>
+      <c r="G244" s="2"/>
+    </row>
+    <row r="245" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C245" s="2"/>
+      <c r="D245" s="2"/>
+      <c r="E245" s="2"/>
+      <c r="F245" s="2"/>
+      <c r="G245" s="2"/>
+    </row>
+    <row r="246" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C246" s="2"/>
+      <c r="D246" s="2"/>
+      <c r="E246" s="2"/>
+      <c r="F246" s="2"/>
+      <c r="G246" s="2"/>
+    </row>
+    <row r="247" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C247" s="2"/>
+      <c r="D247" s="2"/>
+      <c r="E247" s="2"/>
+      <c r="F247" s="2"/>
+      <c r="G247" s="2"/>
+    </row>
+    <row r="248" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
+      <c r="E248" s="2"/>
+      <c r="F248" s="2"/>
+      <c r="G248" s="2"/>
+    </row>
+    <row r="249" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C249" s="2"/>
+      <c r="D249" s="2"/>
+      <c r="E249" s="2"/>
+      <c r="F249" s="2"/>
+      <c r="G249" s="2"/>
+    </row>
+    <row r="250" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C250" s="2"/>
+      <c r="D250" s="2"/>
+      <c r="E250" s="2"/>
+      <c r="F250" s="2"/>
+      <c r="G250" s="2"/>
+    </row>
+    <row r="251" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C251" s="2"/>
+      <c r="D251" s="2"/>
+      <c r="E251" s="2"/>
+      <c r="F251" s="2"/>
+      <c r="G251" s="2"/>
+    </row>
+    <row r="252" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C252" s="2"/>
+      <c r="D252" s="2"/>
+      <c r="E252" s="2"/>
+      <c r="F252" s="2"/>
+      <c r="G252" s="2"/>
+    </row>
+    <row r="253" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C253" s="2"/>
+      <c r="D253" s="2"/>
+      <c r="E253" s="2"/>
+      <c r="F253" s="2"/>
+      <c r="G253" s="2"/>
+    </row>
+    <row r="254" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C254" s="2"/>
+      <c r="D254" s="2"/>
+      <c r="E254" s="2"/>
+      <c r="F254" s="2"/>
+      <c r="G254" s="2"/>
+    </row>
+    <row r="255" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C255" s="2"/>
+      <c r="D255" s="2"/>
+      <c r="E255" s="2"/>
+      <c r="F255" s="2"/>
+      <c r="G255" s="2"/>
+    </row>
+    <row r="256" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C256" s="2"/>
+      <c r="D256" s="2"/>
+      <c r="E256" s="2"/>
+      <c r="F256" s="2"/>
+      <c r="G256" s="2"/>
+    </row>
+    <row r="257" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C257" s="2"/>
+      <c r="D257" s="2"/>
+      <c r="E257" s="2"/>
+      <c r="F257" s="2"/>
+      <c r="G257" s="2"/>
+    </row>
+    <row r="258" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C258" s="2"/>
+      <c r="D258" s="2"/>
+      <c r="E258" s="2"/>
+      <c r="F258" s="2"/>
+      <c r="G258" s="2"/>
+    </row>
+    <row r="259" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C259" s="2"/>
+      <c r="D259" s="2"/>
+      <c r="E259" s="2"/>
+      <c r="F259" s="2"/>
+      <c r="G259" s="2"/>
+    </row>
+    <row r="260" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C260" s="2"/>
+      <c r="D260" s="2"/>
+      <c r="E260" s="2"/>
+      <c r="F260" s="2"/>
+      <c r="G260" s="2"/>
+    </row>
+    <row r="261" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C261" s="2"/>
+      <c r="D261" s="2"/>
+      <c r="E261" s="2"/>
+      <c r="F261" s="2"/>
+      <c r="G261" s="2"/>
+    </row>
+    <row r="262" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C262" s="2"/>
+      <c r="D262" s="2"/>
+      <c r="E262" s="2"/>
+      <c r="F262" s="2"/>
+      <c r="G262" s="2"/>
+    </row>
+    <row r="263" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C263" s="2"/>
+      <c r="D263" s="2"/>
+      <c r="E263" s="2"/>
+      <c r="F263" s="2"/>
+      <c r="G263" s="2"/>
+    </row>
+    <row r="264" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C264" s="2"/>
+      <c r="D264" s="2"/>
+      <c r="E264" s="2"/>
+      <c r="F264" s="2"/>
+      <c r="G264" s="2"/>
+    </row>
+    <row r="265" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C265" s="2"/>
+      <c r="D265" s="2"/>
+      <c r="E265" s="2"/>
+      <c r="F265" s="2"/>
+      <c r="G265" s="2"/>
+    </row>
+    <row r="266" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C266" s="2"/>
+      <c r="D266" s="2"/>
+      <c r="E266" s="2"/>
+      <c r="F266" s="2"/>
+      <c r="G266" s="2"/>
+    </row>
+    <row r="267" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C267" s="2"/>
+      <c r="D267" s="2"/>
+      <c r="E267" s="2"/>
+      <c r="F267" s="2"/>
+      <c r="G267" s="2"/>
+    </row>
+    <row r="268" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C268" s="2"/>
+      <c r="D268" s="2"/>
+      <c r="E268" s="2"/>
+      <c r="F268" s="2"/>
+      <c r="G268" s="2"/>
+    </row>
+    <row r="269" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C269" s="2"/>
+      <c r="D269" s="2"/>
+      <c r="E269" s="2"/>
+      <c r="F269" s="2"/>
+      <c r="G269" s="2"/>
+    </row>
+    <row r="270" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C270" s="2"/>
+      <c r="D270" s="2"/>
+      <c r="E270" s="2"/>
+      <c r="F270" s="2"/>
+      <c r="G270" s="2"/>
+    </row>
+    <row r="271" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C271" s="2"/>
+      <c r="D271" s="2"/>
+      <c r="E271" s="2"/>
+      <c r="F271" s="2"/>
+      <c r="G271" s="2"/>
+    </row>
+    <row r="272" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C272" s="2"/>
+      <c r="D272" s="2"/>
+      <c r="E272" s="2"/>
+      <c r="F272" s="2"/>
+      <c r="G272" s="2"/>
+    </row>
+    <row r="273" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C273" s="2"/>
+      <c r="D273" s="2"/>
+      <c r="E273" s="2"/>
+      <c r="F273" s="2"/>
+      <c r="G273" s="2"/>
+    </row>
+    <row r="274" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C274" s="2"/>
+      <c r="D274" s="2"/>
+      <c r="E274" s="2"/>
+      <c r="F274" s="2"/>
+      <c r="G274" s="2"/>
+    </row>
+    <row r="275" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C275" s="2"/>
+      <c r="D275" s="2"/>
+      <c r="E275" s="2"/>
+      <c r="F275" s="2"/>
+      <c r="G275" s="2"/>
+    </row>
+    <row r="276" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C276" s="2"/>
+      <c r="D276" s="2"/>
+      <c r="E276" s="2"/>
+      <c r="F276" s="2"/>
+      <c r="G276" s="2"/>
+    </row>
+    <row r="277" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C277" s="2"/>
+      <c r="D277" s="2"/>
+      <c r="E277" s="2"/>
+      <c r="F277" s="2"/>
+      <c r="G277" s="2"/>
+    </row>
+    <row r="278" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C278" s="2"/>
+      <c r="D278" s="2"/>
+      <c r="E278" s="2"/>
+      <c r="F278" s="2"/>
+      <c r="G278" s="2"/>
+    </row>
+    <row r="279" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C279" s="2"/>
+      <c r="D279" s="2"/>
+      <c r="E279" s="2"/>
+      <c r="F279" s="2"/>
+      <c r="G279" s="2"/>
+    </row>
+    <row r="280" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C280" s="2"/>
+      <c r="D280" s="2"/>
+      <c r="E280" s="2"/>
+      <c r="F280" s="2"/>
+      <c r="G280" s="2"/>
+    </row>
+    <row r="281" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C281" s="2"/>
+      <c r="D281" s="2"/>
+      <c r="E281" s="2"/>
+      <c r="F281" s="2"/>
+      <c r="G281" s="2"/>
+    </row>
+    <row r="282" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C282" s="2"/>
+      <c r="D282" s="2"/>
+      <c r="E282" s="2"/>
+      <c r="F282" s="2"/>
+      <c r="G282" s="2"/>
+    </row>
+    <row r="283" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C283" s="2"/>
+      <c r="D283" s="2"/>
+      <c r="E283" s="2"/>
+      <c r="F283" s="2"/>
+      <c r="G283" s="2"/>
+    </row>
+    <row r="284" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C284" s="2"/>
+      <c r="D284" s="2"/>
+      <c r="E284" s="2"/>
+      <c r="F284" s="2"/>
+      <c r="G284" s="2"/>
+    </row>
+    <row r="285" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C285" s="2"/>
+      <c r="D285" s="2"/>
+      <c r="E285" s="2"/>
+      <c r="F285" s="2"/>
+      <c r="G285" s="2"/>
+    </row>
+    <row r="286" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C286" s="2"/>
+      <c r="D286" s="2"/>
+      <c r="E286" s="2"/>
+      <c r="F286" s="2"/>
+      <c r="G286" s="2"/>
+    </row>
+    <row r="287" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C287" s="2"/>
+      <c r="D287" s="2"/>
+      <c r="E287" s="2"/>
+      <c r="F287" s="2"/>
+      <c r="G287" s="2"/>
+    </row>
+    <row r="288" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C288" s="2"/>
+      <c r="D288" s="2"/>
+      <c r="E288" s="2"/>
+      <c r="F288" s="2"/>
+      <c r="G288" s="2"/>
+    </row>
+    <row r="289" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C289" s="2"/>
+      <c r="D289" s="2"/>
+      <c r="E289" s="2"/>
+      <c r="F289" s="2"/>
+      <c r="G289" s="2"/>
+    </row>
+    <row r="290" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C290" s="2"/>
+      <c r="D290" s="2"/>
+      <c r="E290" s="2"/>
+      <c r="F290" s="2"/>
+      <c r="G290" s="2"/>
+    </row>
+    <row r="291" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C291" s="2"/>
+      <c r="D291" s="2"/>
+      <c r="E291" s="2"/>
+      <c r="F291" s="2"/>
+      <c r="G291" s="2"/>
+    </row>
+    <row r="292" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C292" s="2"/>
+      <c r="D292" s="2"/>
+      <c r="E292" s="2"/>
+      <c r="F292" s="2"/>
+      <c r="G292" s="2"/>
+    </row>
+    <row r="293" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C293" s="2"/>
+      <c r="D293" s="2"/>
+      <c r="E293" s="2"/>
+      <c r="F293" s="2"/>
+      <c r="G293" s="2"/>
+    </row>
+    <row r="294" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C294" s="2"/>
+      <c r="D294" s="2"/>
+      <c r="E294" s="2"/>
+      <c r="F294" s="2"/>
+      <c r="G294" s="2"/>
+    </row>
+    <row r="295" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C295" s="2"/>
+      <c r="D295" s="2"/>
+      <c r="E295" s="2"/>
+      <c r="F295" s="2"/>
+      <c r="G295" s="2"/>
+    </row>
+    <row r="296" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C296" s="2"/>
+      <c r="D296" s="2"/>
+      <c r="E296" s="2"/>
+      <c r="F296" s="2"/>
+      <c r="G296" s="2"/>
+    </row>
+    <row r="297" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C297" s="2"/>
+      <c r="D297" s="2"/>
+      <c r="E297" s="2"/>
+      <c r="F297" s="2"/>
+      <c r="G297" s="2"/>
+    </row>
+    <row r="298" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C298" s="2"/>
+      <c r="D298" s="2"/>
+      <c r="E298" s="2"/>
+      <c r="F298" s="2"/>
+      <c r="G298" s="2"/>
+    </row>
+    <row r="299" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C299" s="2"/>
+      <c r="D299" s="2"/>
+      <c r="E299" s="2"/>
+      <c r="F299" s="2"/>
+      <c r="G299" s="2"/>
+    </row>
+    <row r="300" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C300" s="2"/>
+      <c r="D300" s="2"/>
+      <c r="E300" s="2"/>
+      <c r="F300" s="2"/>
+      <c r="G300" s="2"/>
+    </row>
+    <row r="301" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C301" s="2"/>
+      <c r="D301" s="2"/>
+      <c r="E301" s="2"/>
+      <c r="F301" s="2"/>
+      <c r="G301" s="2"/>
+    </row>
+    <row r="302" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C302" s="2"/>
+      <c r="D302" s="2"/>
+      <c r="E302" s="2"/>
+      <c r="F302" s="2"/>
+      <c r="G302" s="2"/>
+    </row>
+    <row r="303" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C303" s="2"/>
+      <c r="D303" s="2"/>
+      <c r="E303" s="2"/>
+      <c r="F303" s="2"/>
+      <c r="G303" s="2"/>
+    </row>
+    <row r="304" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C304" s="2"/>
+      <c r="D304" s="2"/>
+      <c r="E304" s="2"/>
+      <c r="F304" s="2"/>
+      <c r="G304" s="2"/>
+    </row>
+    <row r="305" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C305" s="2"/>
+      <c r="D305" s="2"/>
+      <c r="E305" s="2"/>
+      <c r="F305" s="2"/>
+      <c r="G305" s="2"/>
+    </row>
+    <row r="306" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C306" s="2"/>
+      <c r="D306" s="2"/>
+      <c r="E306" s="2"/>
+      <c r="F306" s="2"/>
+      <c r="G306" s="2"/>
+    </row>
+    <row r="307" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C307" s="2"/>
+      <c r="D307" s="2"/>
+      <c r="E307" s="2"/>
+      <c r="F307" s="2"/>
+      <c r="G307" s="2"/>
+    </row>
+    <row r="308" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C308" s="2"/>
+      <c r="D308" s="2"/>
+      <c r="E308" s="2"/>
+      <c r="F308" s="2"/>
+      <c r="G308" s="2"/>
+    </row>
+    <row r="309" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C309" s="2"/>
+      <c r="D309" s="2"/>
+      <c r="E309" s="2"/>
+      <c r="F309" s="2"/>
+      <c r="G309" s="2"/>
+    </row>
+    <row r="310" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C310" s="2"/>
+      <c r="D310" s="2"/>
+      <c r="E310" s="2"/>
+      <c r="F310" s="2"/>
+      <c r="G310" s="2"/>
+    </row>
+    <row r="311" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C311" s="2"/>
+      <c r="D311" s="2"/>
+      <c r="E311" s="2"/>
+      <c r="F311" s="2"/>
+      <c r="G311" s="2"/>
+    </row>
+    <row r="312" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C312" s="2"/>
+      <c r="D312" s="2"/>
+      <c r="E312" s="2"/>
+      <c r="F312" s="2"/>
+      <c r="G312" s="2"/>
+    </row>
+    <row r="313" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C313" s="2"/>
+      <c r="D313" s="2"/>
+      <c r="E313" s="2"/>
+      <c r="F313" s="2"/>
+      <c r="G313" s="2"/>
+    </row>
+    <row r="314" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C314" s="2"/>
+      <c r="D314" s="2"/>
+      <c r="E314" s="2"/>
+      <c r="F314" s="2"/>
+      <c r="G314" s="2"/>
+    </row>
+    <row r="315" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C315" s="2"/>
+      <c r="D315" s="2"/>
+      <c r="E315" s="2"/>
+      <c r="F315" s="2"/>
+      <c r="G315" s="2"/>
+    </row>
+    <row r="316" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C316" s="2"/>
+      <c r="D316" s="2"/>
+      <c r="E316" s="2"/>
+      <c r="F316" s="2"/>
+      <c r="G316" s="2"/>
+    </row>
+    <row r="317" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C317" s="2"/>
+      <c r="D317" s="2"/>
+      <c r="E317" s="2"/>
+      <c r="F317" s="2"/>
+      <c r="G317" s="2"/>
+    </row>
+    <row r="318" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C318" s="2"/>
+      <c r="D318" s="2"/>
+      <c r="E318" s="2"/>
+      <c r="F318" s="2"/>
+      <c r="G318" s="2"/>
+    </row>
+    <row r="319" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C319" s="2"/>
+      <c r="D319" s="2"/>
+      <c r="E319" s="2"/>
+      <c r="F319" s="2"/>
+      <c r="G319" s="2"/>
+    </row>
+    <row r="320" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C320" s="2"/>
+      <c r="D320" s="2"/>
+      <c r="E320" s="2"/>
+      <c r="F320" s="2"/>
+      <c r="G320" s="2"/>
+    </row>
+    <row r="321" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C321" s="2"/>
+      <c r="D321" s="2"/>
+      <c r="E321" s="2"/>
+      <c r="F321" s="2"/>
+      <c r="G321" s="2"/>
+    </row>
+    <row r="322" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C322" s="2"/>
+      <c r="D322" s="2"/>
+      <c r="E322" s="2"/>
+      <c r="F322" s="2"/>
+      <c r="G322" s="2"/>
+    </row>
+    <row r="323" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C323" s="2"/>
+      <c r="D323" s="2"/>
+      <c r="E323" s="2"/>
+      <c r="F323" s="2"/>
+      <c r="G323" s="2"/>
+    </row>
+    <row r="324" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C324" s="2"/>
+      <c r="D324" s="2"/>
+      <c r="E324" s="2"/>
+      <c r="F324" s="2"/>
+      <c r="G324" s="2"/>
+    </row>
+    <row r="325" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C325" s="2"/>
+      <c r="D325" s="2"/>
+      <c r="E325" s="2"/>
+      <c r="F325" s="2"/>
+      <c r="G325" s="2"/>
+    </row>
+    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C326" s="2"/>
+      <c r="D326" s="2"/>
+      <c r="E326" s="2"/>
+      <c r="F326" s="2"/>
+      <c r="G326" s="2"/>
+    </row>
+    <row r="327" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C327" s="2"/>
+      <c r="D327" s="2"/>
+      <c r="E327" s="2"/>
+      <c r="F327" s="2"/>
+      <c r="G327" s="2"/>
+    </row>
+    <row r="328" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C328" s="2"/>
+      <c r="D328" s="2"/>
+      <c r="E328" s="2"/>
+      <c r="F328" s="2"/>
+      <c r="G328" s="2"/>
+    </row>
+    <row r="329" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C329" s="2"/>
+      <c r="D329" s="2"/>
+      <c r="E329" s="2"/>
+      <c r="F329" s="2"/>
+      <c r="G329" s="2"/>
+    </row>
+    <row r="330" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C330" s="2"/>
+      <c r="D330" s="2"/>
+      <c r="E330" s="2"/>
+      <c r="F330" s="2"/>
+      <c r="G330" s="2"/>
+    </row>
+    <row r="331" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C331" s="2"/>
+      <c r="D331" s="2"/>
+      <c r="E331" s="2"/>
+      <c r="F331" s="2"/>
+      <c r="G331" s="2"/>
+    </row>
+    <row r="332" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C332" s="2"/>
+      <c r="D332" s="2"/>
+      <c r="E332" s="2"/>
+      <c r="F332" s="2"/>
+      <c r="G332" s="2"/>
+    </row>
+    <row r="333" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C333" s="2"/>
+      <c r="D333" s="2"/>
+      <c r="E333" s="2"/>
+      <c r="F333" s="2"/>
+      <c r="G333" s="2"/>
+    </row>
+    <row r="334" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C334" s="2"/>
+      <c r="D334" s="2"/>
+      <c r="E334" s="2"/>
+      <c r="F334" s="2"/>
+      <c r="G334" s="2"/>
+    </row>
+    <row r="335" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C335" s="2"/>
+      <c r="D335" s="2"/>
+      <c r="E335" s="2"/>
+      <c r="F335" s="2"/>
+      <c r="G335" s="2"/>
+    </row>
+    <row r="336" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C336" s="2"/>
+      <c r="D336" s="2"/>
+      <c r="E336" s="2"/>
+      <c r="F336" s="2"/>
+      <c r="G336" s="2"/>
+    </row>
+    <row r="337" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C337" s="2"/>
+      <c r="D337" s="2"/>
+      <c r="E337" s="2"/>
+      <c r="F337" s="2"/>
+      <c r="G337" s="2"/>
+    </row>
+    <row r="338" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C338" s="2"/>
+      <c r="D338" s="2"/>
+      <c r="E338" s="2"/>
+      <c r="F338" s="2"/>
+      <c r="G338" s="2"/>
+    </row>
+    <row r="339" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C339" s="2"/>
+      <c r="D339" s="2"/>
+      <c r="E339" s="2"/>
+      <c r="F339" s="2"/>
+      <c r="G339" s="2"/>
+    </row>
+    <row r="340" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C340" s="2"/>
+      <c r="D340" s="2"/>
+      <c r="E340" s="2"/>
+      <c r="F340" s="2"/>
+      <c r="G340" s="2"/>
+    </row>
+    <row r="341" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C341" s="2"/>
+      <c r="D341" s="2"/>
+      <c r="E341" s="2"/>
+      <c r="F341" s="2"/>
+      <c r="G341" s="2"/>
+    </row>
+    <row r="342" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C342" s="2"/>
+      <c r="D342" s="2"/>
+      <c r="E342" s="2"/>
+      <c r="F342" s="2"/>
+      <c r="G342" s="2"/>
+    </row>
+    <row r="343" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C343" s="2"/>
+      <c r="D343" s="2"/>
+      <c r="E343" s="2"/>
+      <c r="F343" s="2"/>
+      <c r="G343" s="2"/>
+    </row>
+    <row r="344" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C344" s="2"/>
+      <c r="D344" s="2"/>
+      <c r="E344" s="2"/>
+      <c r="F344" s="2"/>
+      <c r="G344" s="2"/>
+    </row>
+    <row r="345" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C345" s="2"/>
+      <c r="D345" s="2"/>
+      <c r="E345" s="2"/>
+      <c r="F345" s="2"/>
+      <c r="G345" s="2"/>
+    </row>
+    <row r="346" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C346" s="2"/>
+      <c r="D346" s="2"/>
+      <c r="E346" s="2"/>
+      <c r="F346" s="2"/>
+      <c r="G346" s="2"/>
+    </row>
+    <row r="347" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C347" s="2"/>
+      <c r="D347" s="2"/>
+      <c r="E347" s="2"/>
+      <c r="F347" s="2"/>
+      <c r="G347" s="2"/>
+    </row>
+    <row r="348" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C348" s="2"/>
+      <c r="D348" s="2"/>
+      <c r="E348" s="2"/>
+      <c r="F348" s="2"/>
+      <c r="G348" s="2"/>
+    </row>
+    <row r="349" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C349" s="2"/>
+      <c r="D349" s="2"/>
+      <c r="E349" s="2"/>
+      <c r="F349" s="2"/>
+      <c r="G349" s="2"/>
+    </row>
+    <row r="350" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C350" s="2"/>
+      <c r="D350" s="2"/>
+      <c r="E350" s="2"/>
+      <c r="F350" s="2"/>
+      <c r="G350" s="2"/>
+    </row>
+    <row r="351" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C351" s="2"/>
+      <c r="D351" s="2"/>
+      <c r="E351" s="2"/>
+      <c r="F351" s="2"/>
+      <c r="G351" s="2"/>
+    </row>
+    <row r="352" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C352" s="2"/>
+      <c r="D352" s="2"/>
+      <c r="E352" s="2"/>
+      <c r="F352" s="2"/>
+      <c r="G352" s="2"/>
+    </row>
+    <row r="353" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C353" s="2"/>
+      <c r="D353" s="2"/>
+      <c r="E353" s="2"/>
+      <c r="F353" s="2"/>
+      <c r="G353" s="2"/>
+    </row>
+    <row r="354" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C354" s="2"/>
+      <c r="D354" s="2"/>
+      <c r="E354" s="2"/>
+      <c r="F354" s="2"/>
+      <c r="G354" s="2"/>
+    </row>
+    <row r="355" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C355" s="2"/>
+      <c r="D355" s="2"/>
+      <c r="E355" s="2"/>
+      <c r="F355" s="2"/>
+      <c r="G355" s="2"/>
+    </row>
+    <row r="356" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C356" s="2"/>
+      <c r="D356" s="2"/>
+      <c r="E356" s="2"/>
+      <c r="F356" s="2"/>
+      <c r="G356" s="2"/>
+    </row>
+    <row r="357" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C357" s="2"/>
+      <c r="D357" s="2"/>
+      <c r="E357" s="2"/>
+      <c r="F357" s="2"/>
+      <c r="G357" s="2"/>
+    </row>
+    <row r="358" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C358" s="2"/>
+      <c r="D358" s="2"/>
+      <c r="E358" s="2"/>
+      <c r="F358" s="2"/>
+      <c r="G358" s="2"/>
+    </row>
+    <row r="359" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C359" s="2"/>
+      <c r="D359" s="2"/>
+      <c r="E359" s="2"/>
+      <c r="F359" s="2"/>
+      <c r="G359" s="2"/>
+    </row>
+    <row r="360" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C360" s="2"/>
+      <c r="D360" s="2"/>
+      <c r="E360" s="2"/>
+      <c r="F360" s="2"/>
+      <c r="G360" s="2"/>
+    </row>
+    <row r="361" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C361" s="2"/>
+      <c r="D361" s="2"/>
+      <c r="E361" s="2"/>
+      <c r="F361" s="2"/>
+      <c r="G361" s="2"/>
+    </row>
+    <row r="362" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C362" s="2"/>
+      <c r="D362" s="2"/>
+      <c r="E362" s="2"/>
+      <c r="F362" s="2"/>
+      <c r="G362" s="2"/>
+    </row>
+    <row r="363" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C363" s="2"/>
+      <c r="D363" s="2"/>
+      <c r="E363" s="2"/>
+      <c r="F363" s="2"/>
+      <c r="G363" s="2"/>
+    </row>
+    <row r="364" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C364" s="2"/>
+      <c r="D364" s="2"/>
+      <c r="E364" s="2"/>
+      <c r="F364" s="2"/>
+      <c r="G364" s="2"/>
+    </row>
+    <row r="365" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C365" s="2"/>
+      <c r="D365" s="2"/>
+      <c r="E365" s="2"/>
+      <c r="F365" s="2"/>
+      <c r="G365" s="2"/>
+    </row>
+    <row r="366" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C366" s="2"/>
+      <c r="D366" s="2"/>
+      <c r="E366" s="2"/>
+      <c r="F366" s="2"/>
+      <c r="G366" s="2"/>
+    </row>
+    <row r="367" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C367" s="2"/>
+      <c r="D367" s="2"/>
+      <c r="E367" s="2"/>
+      <c r="F367" s="2"/>
+      <c r="G367" s="2"/>
+    </row>
+    <row r="368" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C368" s="2"/>
+      <c r="D368" s="2"/>
+      <c r="E368" s="2"/>
+      <c r="F368" s="2"/>
+      <c r="G368" s="2"/>
+    </row>
+    <row r="369" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C369" s="2"/>
+      <c r="D369" s="2"/>
+      <c r="E369" s="2"/>
+      <c r="F369" s="2"/>
+      <c r="G369" s="2"/>
+    </row>
+    <row r="370" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C370" s="2"/>
+      <c r="D370" s="2"/>
+      <c r="E370" s="2"/>
+      <c r="F370" s="2"/>
+      <c r="G370" s="2"/>
+    </row>
+    <row r="371" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C371" s="2"/>
+      <c r="D371" s="2"/>
+      <c r="E371" s="2"/>
+      <c r="F371" s="2"/>
+      <c r="G371" s="2"/>
+    </row>
+    <row r="372" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C372" s="2"/>
+      <c r="D372" s="2"/>
+      <c r="E372" s="2"/>
+      <c r="F372" s="2"/>
+      <c r="G372" s="2"/>
+    </row>
+    <row r="373" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C373" s="2"/>
+      <c r="D373" s="2"/>
+      <c r="E373" s="2"/>
+      <c r="F373" s="2"/>
+      <c r="G373" s="2"/>
+    </row>
+    <row r="374" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C374" s="2"/>
+      <c r="D374" s="2"/>
+      <c r="E374" s="2"/>
+      <c r="F374" s="2"/>
+      <c r="G374" s="2"/>
+    </row>
+    <row r="375" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C375" s="2"/>
+      <c r="D375" s="2"/>
+      <c r="E375" s="2"/>
+      <c r="F375" s="2"/>
+      <c r="G375" s="2"/>
+    </row>
+    <row r="376" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C376" s="2"/>
+      <c r="D376" s="2"/>
+      <c r="E376" s="2"/>
+      <c r="F376" s="2"/>
+      <c r="G376" s="2"/>
+    </row>
+    <row r="377" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C377" s="2"/>
+      <c r="D377" s="2"/>
+      <c r="E377" s="2"/>
+      <c r="F377" s="2"/>
+      <c r="G377" s="2"/>
+    </row>
+    <row r="378" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C378" s="2"/>
+      <c r="D378" s="2"/>
+      <c r="E378" s="2"/>
+      <c r="F378" s="2"/>
+      <c r="G378" s="2"/>
+    </row>
+    <row r="379" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C379" s="2"/>
+      <c r="D379" s="2"/>
+      <c r="E379" s="2"/>
+      <c r="F379" s="2"/>
+      <c r="G379" s="2"/>
+    </row>
+    <row r="380" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C380" s="2"/>
+      <c r="D380" s="2"/>
+      <c r="E380" s="2"/>
+      <c r="F380" s="2"/>
+      <c r="G380" s="2"/>
+    </row>
+    <row r="381" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C381" s="2"/>
+      <c r="D381" s="2"/>
+      <c r="E381" s="2"/>
+      <c r="F381" s="2"/>
+      <c r="G381" s="2"/>
+    </row>
+    <row r="382" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C382" s="2"/>
+      <c r="D382" s="2"/>
+      <c r="E382" s="2"/>
+      <c r="F382" s="2"/>
+      <c r="G382" s="2"/>
+    </row>
+    <row r="383" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C383" s="2"/>
+      <c r="D383" s="2"/>
+      <c r="E383" s="2"/>
+      <c r="F383" s="2"/>
+      <c r="G383" s="2"/>
+    </row>
+    <row r="384" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C384" s="2"/>
+      <c r="D384" s="2"/>
+      <c r="E384" s="2"/>
+      <c r="F384" s="2"/>
+      <c r="G384" s="2"/>
+    </row>
+    <row r="385" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C385" s="2"/>
+      <c r="D385" s="2"/>
+      <c r="E385" s="2"/>
+      <c r="F385" s="2"/>
+      <c r="G385" s="2"/>
+    </row>
+    <row r="386" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C386" s="2"/>
+      <c r="D386" s="2"/>
+      <c r="E386" s="2"/>
+      <c r="F386" s="2"/>
+      <c r="G386" s="2"/>
+    </row>
+    <row r="387" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C387" s="2"/>
+      <c r="D387" s="2"/>
+      <c r="E387" s="2"/>
+      <c r="F387" s="2"/>
+      <c r="G387" s="2"/>
+    </row>
+    <row r="388" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C388" s="2"/>
+      <c r="D388" s="2"/>
+      <c r="E388" s="2"/>
+      <c r="F388" s="2"/>
+      <c r="G388" s="2"/>
+    </row>
+    <row r="389" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C389" s="2"/>
+      <c r="D389" s="2"/>
+      <c r="E389" s="2"/>
+      <c r="F389" s="2"/>
+      <c r="G389" s="2"/>
+    </row>
+    <row r="390" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C390" s="2"/>
+      <c r="D390" s="2"/>
+      <c r="E390" s="2"/>
+      <c r="F390" s="2"/>
+      <c r="G390" s="2"/>
+    </row>
+    <row r="391" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C391" s="2"/>
+      <c r="D391" s="2"/>
+      <c r="E391" s="2"/>
+      <c r="F391" s="2"/>
+      <c r="G391" s="2"/>
+    </row>
+    <row r="392" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C392" s="2"/>
+      <c r="D392" s="2"/>
+      <c r="E392" s="2"/>
+      <c r="F392" s="2"/>
+      <c r="G392" s="2"/>
+    </row>
+    <row r="393" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C393" s="2"/>
+      <c r="D393" s="2"/>
+      <c r="E393" s="2"/>
+      <c r="F393" s="2"/>
+      <c r="G393" s="2"/>
+    </row>
+    <row r="394" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C394" s="2"/>
+      <c r="D394" s="2"/>
+      <c r="E394" s="2"/>
+      <c r="F394" s="2"/>
+      <c r="G394" s="2"/>
+    </row>
+    <row r="395" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C395" s="2"/>
+      <c r="D395" s="2"/>
+      <c r="E395" s="2"/>
+      <c r="F395" s="2"/>
+      <c r="G395" s="2"/>
+    </row>
+    <row r="396" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C396" s="2"/>
+      <c r="D396" s="2"/>
+      <c r="E396" s="2"/>
+      <c r="F396" s="2"/>
+      <c r="G396" s="2"/>
+    </row>
+    <row r="397" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C397" s="2"/>
+      <c r="D397" s="2"/>
+      <c r="E397" s="2"/>
+      <c r="F397" s="2"/>
+      <c r="G397" s="2"/>
+    </row>
+    <row r="398" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C398" s="2"/>
+      <c r="D398" s="2"/>
+      <c r="E398" s="2"/>
+      <c r="F398" s="2"/>
+      <c r="G398" s="2"/>
+    </row>
+    <row r="399" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C399" s="2"/>
+      <c r="D399" s="2"/>
+      <c r="E399" s="2"/>
+      <c r="F399" s="2"/>
+      <c r="G399" s="2"/>
+    </row>
+    <row r="400" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C400" s="2"/>
+      <c r="D400" s="2"/>
+      <c r="E400" s="2"/>
+      <c r="F400" s="2"/>
+      <c r="G400" s="2"/>
+    </row>
+    <row r="401" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C401" s="2"/>
+      <c r="D401" s="2"/>
+      <c r="E401" s="2"/>
+      <c r="F401" s="2"/>
+      <c r="G401" s="2"/>
+    </row>
+    <row r="402" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C402" s="2"/>
+      <c r="D402" s="2"/>
+      <c r="E402" s="2"/>
+      <c r="F402" s="2"/>
+      <c r="G402" s="2"/>
+    </row>
+    <row r="403" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C403" s="2"/>
+      <c r="D403" s="2"/>
+      <c r="E403" s="2"/>
+      <c r="F403" s="2"/>
+      <c r="G403" s="2"/>
+    </row>
+    <row r="404" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C404" s="2"/>
+      <c r="D404" s="2"/>
+      <c r="E404" s="2"/>
+      <c r="F404" s="2"/>
+      <c r="G404" s="2"/>
+    </row>
+    <row r="405" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C405" s="2"/>
+      <c r="D405" s="2"/>
+      <c r="E405" s="2"/>
+      <c r="F405" s="2"/>
+      <c r="G405" s="2"/>
+    </row>
+    <row r="406" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C406" s="2"/>
+      <c r="D406" s="2"/>
+      <c r="E406" s="2"/>
+      <c r="F406" s="2"/>
+      <c r="G406" s="2"/>
+    </row>
+    <row r="407" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C407" s="2"/>
+      <c r="D407" s="2"/>
+      <c r="E407" s="2"/>
+      <c r="F407" s="2"/>
+      <c r="G407" s="2"/>
+    </row>
+    <row r="408" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C408" s="2"/>
+      <c r="D408" s="2"/>
+      <c r="E408" s="2"/>
+      <c r="F408" s="2"/>
+      <c r="G408" s="2"/>
+    </row>
+    <row r="409" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C409" s="2"/>
+      <c r="D409" s="2"/>
+      <c r="E409" s="2"/>
+      <c r="F409" s="2"/>
+      <c r="G409" s="2"/>
+    </row>
+    <row r="410" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C410" s="2"/>
+      <c r="D410" s="2"/>
+      <c r="E410" s="2"/>
+      <c r="F410" s="2"/>
+      <c r="G410" s="2"/>
+    </row>
+    <row r="411" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C411" s="2"/>
+      <c r="D411" s="2"/>
+      <c r="E411" s="2"/>
+      <c r="F411" s="2"/>
+      <c r="G411" s="2"/>
+    </row>
+    <row r="412" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C412" s="2"/>
+      <c r="D412" s="2"/>
+      <c r="E412" s="2"/>
+      <c r="F412" s="2"/>
+      <c r="G412" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37F3A864-C585-421C-A8F8-7E679BFCCC8A}">
+  <dimension ref="A1:G424"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="7" width="12.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C1" s="2">
+        <f t="shared" ref="C1:G1" si="0">SUM(C3:C83)</f>
+        <v>-5536.71</v>
+      </c>
+      <c r="D1" s="2">
+        <f t="shared" si="0"/>
+        <v>-1534.3400000000001</v>
+      </c>
+      <c r="E1" s="2">
+        <f t="shared" si="0"/>
+        <v>-860.29</v>
+      </c>
+      <c r="F1" s="2">
+        <f t="shared" si="0"/>
+        <v>-780.3</v>
+      </c>
+      <c r="G1" s="2">
+        <f t="shared" si="0"/>
+        <v>-780.3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="2">
+        <v>-199.3</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="2">
+        <v>-176.6</v>
+      </c>
+      <c r="D4" s="2">
+        <v>-176.6</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="2">
+        <v>-149.99</v>
+      </c>
+      <c r="D5" s="2">
+        <v>-149.99</v>
+      </c>
+      <c r="E5" s="2">
+        <v>-149.99</v>
+      </c>
+      <c r="F5" s="2">
+        <v>-149.99</v>
+      </c>
+      <c r="G5" s="2">
+        <v>-149.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2">
+        <v>-67.900000000000006</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="2">
+        <v>-79.989999999999995</v>
+      </c>
+      <c r="D7" s="2">
+        <v>-79.989999999999995</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-79.989999999999995</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="2">
+        <v>-497.45</v>
+      </c>
+      <c r="D8" s="2">
+        <v>-497.45</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="2">
+        <v>-58.33</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="2">
+        <v>-89.36</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="2">
+        <v>-160</v>
+      </c>
+      <c r="D11" s="2">
+        <v>-160</v>
+      </c>
+      <c r="E11" s="2">
+        <v>-160</v>
+      </c>
+      <c r="F11" s="2">
+        <v>-160</v>
+      </c>
+      <c r="G11" s="2">
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2">
+        <v>-160.5</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="2">
+        <v>-31.9</v>
+      </c>
+      <c r="D13" s="2">
+        <v>-31.9</v>
+      </c>
+      <c r="E13" s="2">
+        <v>-31.9</v>
+      </c>
+      <c r="F13" s="2">
+        <v>-31.9</v>
+      </c>
+      <c r="G13" s="2">
+        <v>-31.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2">
+        <v>-293</v>
+      </c>
+      <c r="D14" s="2">
+        <v>-293</v>
+      </c>
+      <c r="E14" s="2">
+        <v>-293</v>
+      </c>
+      <c r="F14" s="2">
+        <v>-293</v>
+      </c>
+      <c r="G14" s="2">
+        <v>-293</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="2">
+        <v>-131.51</v>
+      </c>
+      <c r="D15" s="2">
+        <v>-131.51</v>
+      </c>
+      <c r="E15" s="2">
+        <v>-131.51</v>
+      </c>
+      <c r="F15" s="2">
+        <v>-131.51</v>
+      </c>
+      <c r="G15" s="2">
+        <v>-131.51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="2">
+        <v>-324.57</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="2">
+        <v>-411</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="2">
+        <v>-169.06</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="2">
+        <v>-30</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="2">
+        <v>-224.9</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="2">
+        <v>-150</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="2">
+        <v>-43.66</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="2">
+        <v>-37.5</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="2">
+        <v>-79.989999999999995</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="2">
+        <v>-19</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="2">
+        <v>-15</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="2">
+        <v>-100</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="2">
+        <v>-225</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="2">
+        <v>-115.41</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="2">
+        <v>-21.9</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" s="2">
+        <v>-92.62</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="2">
+        <v>-155.13</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="2">
+        <v>-376.63</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="2">
+        <v>-13.9</v>
+      </c>
+      <c r="D34" s="2">
+        <v>-13.9</v>
+      </c>
+      <c r="E34" s="2">
+        <v>-13.9</v>
+      </c>
+      <c r="F34" s="2">
+        <v>-13.9</v>
+      </c>
+      <c r="G34" s="2">
+        <v>-13.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="2">
+        <v>-30</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C36" s="2">
+        <v>-33.42</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C37" s="2">
+        <v>-13</v>
+      </c>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C38" s="2">
+        <v>-205.25</v>
+      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C39" s="2">
+        <v>-43.04</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C40" s="2">
+        <v>-155.63999999999999</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C41" s="2">
+        <v>-58</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C42" s="2">
+        <v>-27.9</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C43" s="2">
+        <v>-35.799999999999997</v>
+      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C44" s="2">
+        <v>-216.59</v>
+      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+    </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C45" s="2"/>
+      <c r="C45" s="2">
+        <v>-16.97</v>
+      </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
@@ -13404,6 +13476,90 @@
       <c r="E412" s="2"/>
       <c r="F412" s="2"/>
       <c r="G412" s="2"/>
+    </row>
+    <row r="413" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C413" s="2"/>
+      <c r="D413" s="2"/>
+      <c r="E413" s="2"/>
+      <c r="F413" s="2"/>
+      <c r="G413" s="2"/>
+    </row>
+    <row r="414" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C414" s="2"/>
+      <c r="D414" s="2"/>
+      <c r="E414" s="2"/>
+      <c r="F414" s="2"/>
+      <c r="G414" s="2"/>
+    </row>
+    <row r="415" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C415" s="2"/>
+      <c r="D415" s="2"/>
+      <c r="E415" s="2"/>
+      <c r="F415" s="2"/>
+      <c r="G415" s="2"/>
+    </row>
+    <row r="416" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C416" s="2"/>
+      <c r="D416" s="2"/>
+      <c r="E416" s="2"/>
+      <c r="F416" s="2"/>
+      <c r="G416" s="2"/>
+    </row>
+    <row r="417" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C417" s="2"/>
+      <c r="D417" s="2"/>
+      <c r="E417" s="2"/>
+      <c r="F417" s="2"/>
+      <c r="G417" s="2"/>
+    </row>
+    <row r="418" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C418" s="2"/>
+      <c r="D418" s="2"/>
+      <c r="E418" s="2"/>
+      <c r="F418" s="2"/>
+      <c r="G418" s="2"/>
+    </row>
+    <row r="419" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C419" s="2"/>
+      <c r="D419" s="2"/>
+      <c r="E419" s="2"/>
+      <c r="F419" s="2"/>
+      <c r="G419" s="2"/>
+    </row>
+    <row r="420" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C420" s="2"/>
+      <c r="D420" s="2"/>
+      <c r="E420" s="2"/>
+      <c r="F420" s="2"/>
+      <c r="G420" s="2"/>
+    </row>
+    <row r="421" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C421" s="2"/>
+      <c r="D421" s="2"/>
+      <c r="E421" s="2"/>
+      <c r="F421" s="2"/>
+      <c r="G421" s="2"/>
+    </row>
+    <row r="422" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C422" s="2"/>
+      <c r="D422" s="2"/>
+      <c r="E422" s="2"/>
+      <c r="F422" s="2"/>
+      <c r="G422" s="2"/>
+    </row>
+    <row r="423" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C423" s="2"/>
+      <c r="D423" s="2"/>
+      <c r="E423" s="2"/>
+      <c r="F423" s="2"/>
+      <c r="G423" s="2"/>
+    </row>
+    <row r="424" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C424" s="2"/>
+      <c r="D424" s="2"/>
+      <c r="E424" s="2"/>
+      <c r="F424" s="2"/>
+      <c r="G424" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -13426,7 +13582,7 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C76)</f>
-        <v>-4099.82</v>
+        <v>-3399.52</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
@@ -13472,9 +13628,7 @@
       <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2">
-        <v>-700.3</v>
-      </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="2">
         <v>-700.3</v>
       </c>
@@ -16596,7 +16750,7 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:G1" si="0">SUM(C3:C58)</f>
-        <v>-1194.8699999999999</v>
+        <v>-600</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
@@ -16643,7 +16797,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>-800</v>
+        <v>-400</v>
       </c>
       <c r="D3" s="2">
         <v>-2000</v>
@@ -16663,8 +16817,7 @@
         <v>41</v>
       </c>
       <c r="C4" s="2">
-        <f>-(550-(155.13))</f>
-        <v>-394.87</v>
+        <v>-200</v>
       </c>
       <c r="D4" s="2">
         <v>-600</v>

--- a/CF.xlsx
+++ b/CF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcelo.dilena\Desktop\CF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBF1DFE-BFDA-4A99-A58C-E2BBCC3B3812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9065D8-01FE-415A-A0CB-E6480858FD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77BA92B8-604E-40A7-9BF0-42801C1F048B}"/>
   </bookViews>
@@ -42,15 +42,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="91">
   <si>
     <t>Descrição</t>
   </si>
   <si>
     <t>Março</t>
-  </si>
-  <si>
-    <t>Agosto</t>
   </si>
   <si>
     <t>Setembro</t>
@@ -386,7 +383,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -407,9 +404,6 @@
     <xf numFmtId="8" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
@@ -417,11 +411,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{9058775E-F3AA-4FB6-A33D-2239824B6A96}"/>
   </cellStyles>
-  <dxfs count="46">
-    <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="44">
     <dxf>
       <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -486,10 +476,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -601,105 +587,103 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}" name="Tabela3" displayName="Tabela3" ref="B2:G8" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}" name="Tabela3" displayName="Tabela3" ref="B2:G8" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
   <autoFilter ref="B2:G8" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{58D126D3-568C-4239-BE5B-8ECB2D761C36}" name="DESCRIÇÃO" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{1F251373-CBF5-4FD2-A8E8-CF6062FD64F2}" name="Março" dataDxfId="36">
+    <tableColumn id="1" xr3:uid="{58D126D3-568C-4239-BE5B-8ECB2D761C36}" name="DESCRIÇÃO" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{1F251373-CBF5-4FD2-A8E8-CF6062FD64F2}" name="Março" dataDxfId="34">
       <calculatedColumnFormula>'Nubank M'!#REF!</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{460D0C88-9D72-4E82-9E1F-AAB479149278}" name="Setembro" dataDxfId="35"/>
-    <tableColumn id="9" xr3:uid="{23262E17-D89E-4C5C-B21A-AA6FC4C1D40C}" name="Outubro" dataDxfId="34"/>
-    <tableColumn id="10" xr3:uid="{E80B29F7-DE09-4634-94B9-3F39D450DCAB}" name="Novembro" dataDxfId="33"/>
-    <tableColumn id="11" xr3:uid="{4129935B-5A93-47DA-AEA2-4182BB765146}" name="Dezembro" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{460D0C88-9D72-4E82-9E1F-AAB479149278}" name="Setembro" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{23262E17-D89E-4C5C-B21A-AA6FC4C1D40C}" name="Outubro" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{E80B29F7-DE09-4634-94B9-3F39D450DCAB}" name="Novembro" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{4129935B-5A93-47DA-AEA2-4182BB765146}" name="Dezembro" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07287E34-3C32-457D-AAFA-84A213BA4A5A}" name="Tabela13" displayName="Tabela13" ref="A2:F13" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07287E34-3C32-457D-AAFA-84A213BA4A5A}" name="Tabela13" displayName="Tabela13" ref="A2:F13" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="A2:F13" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{DCAB2E16-31E8-4D04-8D57-D2E5DE1C2D43}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{3D8A892C-E943-4ADC-99A7-8AD45EE19110}" name="Etiqueta"/>
-    <tableColumn id="9" xr3:uid="{238D4DE7-9EC7-4216-9399-4E8F8C6AB056}" name="Setembro" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{C47303D5-51F9-45CA-9893-ECCF6302049A}" name="Outubro" dataDxfId="42"/>
-    <tableColumn id="11" xr3:uid="{F025E820-7D9B-4E4E-975D-064D86088E6B}" name="Novembro" dataDxfId="41"/>
-    <tableColumn id="12" xr3:uid="{3257B979-DC12-48AF-ADD1-57C50933386F}" name="Dezembro" dataDxfId="40"/>
+    <tableColumn id="9" xr3:uid="{238D4DE7-9EC7-4216-9399-4E8F8C6AB056}" name="Setembro" dataDxfId="41"/>
+    <tableColumn id="10" xr3:uid="{C47303D5-51F9-45CA-9893-ECCF6302049A}" name="Outubro" dataDxfId="40"/>
+    <tableColumn id="11" xr3:uid="{F025E820-7D9B-4E4E-975D-064D86088E6B}" name="Novembro" dataDxfId="39"/>
+    <tableColumn id="12" xr3:uid="{3257B979-DC12-48AF-ADD1-57C50933386F}" name="Dezembro" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}" name="Tabela1" displayName="Tabela1" ref="A2:F38" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}" name="Tabela1" displayName="Tabela1" ref="A2:F38" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
   <autoFilter ref="A2:F38" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{C87F2D82-D889-44BD-B683-F742DA7A464D}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{0E8E6474-9FDD-4A00-9A17-A21C82D5D587}" name="Etiqueta"/>
-    <tableColumn id="9" xr3:uid="{3B6669B4-3F3F-4630-B924-79DF6A7F7F62}" name="Setembro" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{14FB9208-D81C-4F3A-B267-6330F6D0C538}" name="Outubro" dataDxfId="28"/>
-    <tableColumn id="11" xr3:uid="{6233639A-A9AB-4395-B906-D5078629897E}" name="Novembro" dataDxfId="27"/>
-    <tableColumn id="12" xr3:uid="{C439927D-5643-4771-B3A5-8D95278E13CB}" name="Dezembro" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{3B6669B4-3F3F-4630-B924-79DF6A7F7F62}" name="Setembro" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{14FB9208-D81C-4F3A-B267-6330F6D0C538}" name="Outubro" dataDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{6233639A-A9AB-4395-B906-D5078629897E}" name="Novembro" dataDxfId="25"/>
+    <tableColumn id="12" xr3:uid="{C439927D-5643-4771-B3A5-8D95278E13CB}" name="Dezembro" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8C70EA2E-3E0C-43D6-9BC8-DC48D3EA5D71}" name="Tabela16" displayName="Tabela16" ref="A2:G21" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
-  <autoFilter ref="A2:G21" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8C70EA2E-3E0C-43D6-9BC8-DC48D3EA5D71}" name="Tabela16" displayName="Tabela16" ref="A2:F21" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+  <autoFilter ref="A2:F21" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{22A6603B-5472-41A0-9FE9-85A4D0D9BBEE}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{06CEE4B6-AC33-4E62-9594-04D875A198B2}" name="Etiqueta"/>
-    <tableColumn id="8" xr3:uid="{2656ECEA-2193-4302-A2B8-E5E698D3100B}" name="Agosto" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{75A68C75-5CA6-4D2D-9E9F-4937EA24AB5F}" name="Setembro" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{194CFE84-FB4C-4B9B-B080-CDC3D8C87B60}" name="Outubro" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{7BCDD7DE-693C-49E3-BE77-A773DD3F9C6D}" name="Novembro" dataDxfId="20"/>
-    <tableColumn id="12" xr3:uid="{6AD89F40-09D6-41BD-86DC-C8B11C25AAE5}" name="Dezembro" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{75A68C75-5CA6-4D2D-9E9F-4937EA24AB5F}" name="Setembro" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{194CFE84-FB4C-4B9B-B080-CDC3D8C87B60}" name="Outubro" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{7BCDD7DE-693C-49E3-BE77-A773DD3F9C6D}" name="Novembro" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{6AD89F40-09D6-41BD-86DC-C8B11C25AAE5}" name="Dezembro" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{578AF0ED-5772-4022-8C30-EC0F3D1A9977}" name="Tabela167" displayName="Tabela167" ref="A2:F20" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{578AF0ED-5772-4022-8C30-EC0F3D1A9977}" name="Tabela167" displayName="Tabela167" ref="A2:F20" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A2:F20" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{4228253B-5CDE-4046-B86A-62CA3FEFCC45}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{FB9FB8A1-7786-42A2-8D12-2078EB6F038D}" name="Etiqueta"/>
-    <tableColumn id="9" xr3:uid="{578EBB3E-CFFD-4504-AD40-629D4AF624D5}" name="Setembro" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{6A1DAFCF-51CB-4511-A4D6-00F9ACEC373F}" name="Outubro" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{A7544E74-4742-4201-99B7-579A2AAF4EA6}" name="Novembro" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{2FB52C65-8F63-4EB5-88CF-20854E86EB8D}" name="Dezembro" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{578EBB3E-CFFD-4504-AD40-629D4AF624D5}" name="Setembro" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{6A1DAFCF-51CB-4511-A4D6-00F9ACEC373F}" name="Outubro" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{A7544E74-4742-4201-99B7-579A2AAF4EA6}" name="Novembro" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{2FB52C65-8F63-4EB5-88CF-20854E86EB8D}" name="Dezembro" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C42D68CF-FB7A-49F1-AF65-1CC854A08786}" name="Tabela15" displayName="Tabela15" ref="A2:F26" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C42D68CF-FB7A-49F1-AF65-1CC854A08786}" name="Tabela15" displayName="Tabela15" ref="A2:F26" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A2:F26" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{BA8C3527-9CC9-4101-ADF2-133D6542167D}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{1C97F02E-86F8-41A3-864D-AFF0F236028B}" name="Etiqueta"/>
-    <tableColumn id="9" xr3:uid="{6CBF28AE-1BF9-4880-9204-6E24F29EADD0}" name="Setembro" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{D8593E3B-41CB-4EC9-B415-15B668F9A767}" name="Outubro" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{7CEE13BC-0D8F-45CB-9796-89ECEA41DBA5}" name="Novembro" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{6F9434E6-E90C-4661-8EAD-704A967A5FC6}" name="Dezembro" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{6CBF28AE-1BF9-4880-9204-6E24F29EADD0}" name="Setembro" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{D8593E3B-41CB-4EC9-B415-15B668F9A767}" name="Outubro" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{7CEE13BC-0D8F-45CB-9796-89ECEA41DBA5}" name="Novembro" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{6F9434E6-E90C-4661-8EAD-704A967A5FC6}" name="Dezembro" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1C3F671A-F276-4FA7-9AED-2FC42350BA18}" name="Tabela159" displayName="Tabela159" ref="A2:G8" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A2:G8" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1C3F671A-F276-4FA7-9AED-2FC42350BA18}" name="Tabela159" displayName="Tabela159" ref="A2:F8" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A2:F8" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{CFA287F4-8A34-4889-8A0A-A7DEAE85E0BF}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{3CBF417F-9002-43FD-B165-7A66F5BA9FA0}" name="Etiqueta"/>
-    <tableColumn id="8" xr3:uid="{AEBC8C51-65FB-4132-8565-A09105B920C3}" name="Agosto" dataDxfId="4"/>
     <tableColumn id="9" xr3:uid="{C796137F-CBA0-46D7-A349-2A5C6C12647F}" name="Setembro" dataDxfId="3"/>
     <tableColumn id="10" xr3:uid="{F9CC3070-5DF4-452C-AE68-16A232E48A02}" name="Outubro" dataDxfId="2"/>
     <tableColumn id="11" xr3:uid="{7950CD56-BE91-47F0-9A9E-21248A9BCA5D}" name="Novembro" dataDxfId="1"/>
@@ -1036,27 +1020,27 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="e">
         <f>Receita!#REF!</f>
@@ -1081,32 +1065,32 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="e">
         <f>CONTAS!#REF!</f>
         <v>#REF!</v>
       </c>
       <c r="D4" s="2">
-        <f>'Nubank M'!C1+'Nubank V'!D1+'C6'!C1+CONTAS!C1</f>
+        <f>'Nubank M'!C1+'Nubank V'!C1+'C6'!C1+CONTAS!C1</f>
         <v>-11568.28</v>
       </c>
       <c r="E4" s="2">
-        <f>'Nubank M'!D1+'Nubank V'!E1+'C6'!D1+CONTAS!D1</f>
+        <f>'Nubank M'!D1+'Nubank V'!D1+'C6'!D1+CONTAS!D1</f>
         <v>-6930.03</v>
       </c>
       <c r="F4" s="2">
-        <f>'Nubank M'!E1+'Nubank V'!F1+'C6'!E1+CONTAS!E1</f>
+        <f>'Nubank M'!E1+'Nubank V'!E1+'C6'!E1+CONTAS!E1</f>
         <v>-6207.73</v>
       </c>
       <c r="G4" s="2">
-        <f>'Nubank M'!F1+'Nubank V'!G1+'C6'!F1+CONTAS!F1</f>
+        <f>'Nubank M'!F1+'Nubank V'!F1+'C6'!F1+CONTAS!F1</f>
         <v>-5859.73</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="2" t="e">
         <f>'Nubank M'!#REF!</f>
@@ -1116,21 +1100,21 @@
         <v>-1400</v>
       </c>
       <c r="E5" s="2">
+        <f>PREVISÃO!D3</f>
+        <v>-2000</v>
+      </c>
+      <c r="F5" s="2">
         <f>PREVISÃO!E3</f>
         <v>-2000</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="2">
         <f>PREVISÃO!F3</f>
         <v>-2000</v>
       </c>
-      <c r="G5" s="2">
-        <f>PREVISÃO!G3</f>
-        <v>-2000</v>
-      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="e">
         <f>'Nubank M'!#REF!</f>
@@ -1140,21 +1124,21 @@
         <v>-600</v>
       </c>
       <c r="E6" s="2">
+        <f>PREVISÃO!D4</f>
+        <v>-600</v>
+      </c>
+      <c r="F6" s="2">
         <f>PREVISÃO!E4</f>
         <v>-600</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <f>PREVISÃO!F4</f>
         <v>-600</v>
       </c>
-      <c r="G6" s="2">
-        <f>PREVISÃO!G4</f>
-        <v>-600</v>
-      </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2">
         <v>-4000</v>
@@ -1174,7 +1158,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="4" t="e">
         <f t="shared" ref="C8:G8" si="0">SUM(C3:C7)</f>
@@ -1213,7 +1197,7 @@
     <col min="1" max="1" width="29.28515625" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
     <col min="3" max="6" width="12.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" style="9" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" style="8" customWidth="1"/>
     <col min="16" max="16" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1234,10 +1218,10 @@
         <f t="shared" si="0"/>
         <v>16275.13</v>
       </c>
-      <c r="N1" s="9">
+      <c r="N1" s="8">
         <v>17818.68</v>
       </c>
-      <c r="P1" s="9">
+      <c r="P1" s="8">
         <v>4760</v>
       </c>
     </row>
@@ -1246,30 +1230,30 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N2" s="9">
+      <c r="N2" s="8">
         <v>-3433.21</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="8">
         <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2">
         <v>11000</v>
@@ -1283,16 +1267,16 @@
       <c r="F3" s="2">
         <v>11000</v>
       </c>
-      <c r="N3" s="9">
+      <c r="N3" s="8">
         <v>-6857.97</v>
       </c>
-      <c r="P3" s="9">
+      <c r="P3" s="8">
         <v>-574.97</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2">
         <v>4800</v>
@@ -1306,19 +1290,19 @@
       <c r="F4" s="2">
         <v>4800</v>
       </c>
-      <c r="N4" s="9">
+      <c r="N4" s="8">
         <v>-574.97</v>
       </c>
-      <c r="P4" s="9">
+      <c r="P4" s="8">
         <v>-6955.97</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2">
         <v>485.7</v>
@@ -1326,19 +1310,19 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="N5" s="9">
+      <c r="N5" s="8">
         <v>-4099.82</v>
       </c>
-      <c r="P5" s="9">
+      <c r="P5" s="8">
         <v>-1276</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2">
         <v>341.67</v>
@@ -1346,19 +1330,19 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="N6" s="9">
+      <c r="N6" s="8">
         <v>1000</v>
       </c>
-      <c r="P6" s="9">
+      <c r="P6" s="8">
         <v>-3850</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2">
         <v>482.93</v>
@@ -1366,11 +1350,11 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="P7" s="9"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" s="2">
         <v>497</v>
@@ -1378,21 +1362,21 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="N8" s="9">
+      <c r="N8" s="8">
         <f>SUM(N1:N7)</f>
         <v>3852.7100000000009</v>
       </c>
-      <c r="P8" s="9">
+      <c r="P8" s="8">
         <f>SUM(P1:P7)</f>
         <v>-7399.9400000000005</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2">
         <v>176.6</v>
@@ -1400,11 +1384,11 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="P9" s="9"/>
+      <c r="P9" s="8"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2">
         <v>475.13</v>
@@ -1418,18 +1402,18 @@
       <c r="F10" s="2">
         <v>475.13</v>
       </c>
-      <c r="P10" s="9"/>
+      <c r="P10" s="8"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="P11" s="9"/>
+      <c r="P11" s="8"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2">
         <v>1000</v>
@@ -1437,42 +1421,42 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="P12" s="9"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="P13" s="9"/>
+      <c r="P13" s="8"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="P14" s="9"/>
+      <c r="P14" s="8"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="P15" s="9"/>
+      <c r="P15" s="8"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="P16" s="9"/>
+      <c r="P16" s="8"/>
     </row>
     <row r="17" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="P17" s="9"/>
+      <c r="P17" s="8"/>
     </row>
     <row r="18" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C18" s="2"/>
@@ -3813,24 +3797,24 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="7">
         <v>-19.899999999999999</v>
@@ -3847,7 +3831,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" s="7">
         <v>-26.9</v>
@@ -3864,7 +3848,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" s="7">
         <v>-55.44</v>
@@ -3877,7 +3861,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="7">
         <v>-83.26</v>
@@ -3888,7 +3872,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" s="7">
         <v>-4</v>
@@ -3899,7 +3883,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="7">
         <v>-114.29</v>
@@ -3910,10 +3894,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="7">
         <v>-482.93</v>
@@ -3924,7 +3908,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" s="7">
         <v>-55.35</v>
@@ -3941,7 +3925,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" s="7">
         <v>-9.9</v>
@@ -3958,7 +3942,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" s="7">
         <v>-57.8</v>
@@ -3975,7 +3959,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" s="7">
         <v>-21.79</v>
@@ -3986,7 +3970,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C14" s="7">
         <v>-101.17</v>
@@ -3999,7 +3983,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" s="7">
         <v>-5.21</v>
@@ -4016,7 +4000,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" s="2">
         <v>-8.6999999999999993</v>
@@ -4027,7 +4011,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C17" s="2">
         <v>-19</v>
@@ -4038,7 +4022,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C18" s="2">
         <v>-600</v>
@@ -4055,7 +4039,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C19" s="2">
         <v>-17.98</v>
@@ -4066,10 +4050,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" s="2">
         <v>-485.7</v>
@@ -4082,10 +4066,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C21" s="2">
         <v>-341.67</v>
@@ -4096,7 +4080,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C22" s="2">
         <v>-139</v>
@@ -4107,7 +4091,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23" s="2">
         <v>-22</v>
@@ -4118,7 +4102,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C24" s="2">
         <v>-138.69999999999999</v>
@@ -4129,7 +4113,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C25" s="2">
         <v>-137.75</v>
@@ -4140,7 +4124,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C26" s="2">
         <v>-265.54000000000002</v>
@@ -4151,7 +4135,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C27" s="2">
         <v>-149.99</v>
@@ -4162,7 +4146,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C28" s="2">
         <v>-110.33</v>
@@ -4173,7 +4157,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C29" s="2">
         <v>-436.17</v>
@@ -4184,7 +4168,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C30" s="2">
         <v>-30</v>
@@ -4195,7 +4179,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C31" s="2">
         <v>-18.940000000000001</v>
@@ -4206,7 +4190,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C32" s="2">
         <v>-107.12</v>
@@ -4217,7 +4201,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C33" s="2">
         <v>-40</v>
@@ -4228,7 +4212,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C34" s="2">
         <v>-27</v>
@@ -4239,7 +4223,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C35" s="2">
         <v>-15</v>
@@ -4250,7 +4234,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C36" s="2">
         <v>-290</v>
@@ -4261,7 +4245,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C37" s="2">
         <v>-44.75</v>
@@ -4272,7 +4256,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C38" s="2">
         <v>-75</v>
@@ -6266,22 +6250,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F01D07ED-902F-4033-9A87-355F7134C802}">
-  <dimension ref="A1:G412"/>
+  <dimension ref="A1:F412"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="7" width="12.7109375" style="1" customWidth="1"/>
+    <col min="3" max="6" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
-        <f t="shared" ref="C1:G1" si="0">SUM(C3:C71)</f>
-        <v>-574.97000000000014</v>
+        <f t="shared" ref="C1:F1" si="0">SUM(C3:C71)</f>
+        <v>-509.96000000000004</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>-509.96000000000004</v>
+        <v>-71.400000000000006</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
@@ -6291,17 +6275,13 @@
         <f t="shared" si="0"/>
         <v>-71.400000000000006</v>
       </c>
-      <c r="G1" s="2">
-        <f t="shared" si="0"/>
-        <v>-71.400000000000006</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -6315,15 +6295,12 @@
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="8">
+        <v>32</v>
+      </c>
+      <c r="C3" s="6">
         <v>-44.9</v>
       </c>
       <c r="D3" s="6">
@@ -6335,15 +6312,12 @@
       <c r="F3" s="6">
         <v>-44.9</v>
       </c>
-      <c r="G3" s="6">
-        <v>-44.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="8">
+        <v>33</v>
+      </c>
+      <c r="C4" s="6">
         <v>-26.5</v>
       </c>
       <c r="D4" s="6">
@@ -6355,2913 +6329,2486 @@
       <c r="F4" s="6">
         <v>-26.5</v>
       </c>
-      <c r="G4" s="6">
-        <v>-26.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="8">
-        <v>-49.97</v>
-      </c>
-      <c r="D5" s="6">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="6">
         <v>-88.98</v>
       </c>
+      <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="8">
+        <v>60</v>
+      </c>
+      <c r="C6" s="6">
         <v>-154.34</v>
       </c>
-      <c r="D6" s="6">
-        <v>-154.34</v>
-      </c>
+      <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="7">
+        <v>62</v>
+      </c>
+      <c r="C7" s="2">
         <v>-111</v>
       </c>
-      <c r="D7" s="2">
-        <v>-111</v>
-      </c>
+      <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="7">
+        <v>63</v>
+      </c>
+      <c r="C8" s="2">
         <v>-84.24</v>
       </c>
-      <c r="D8" s="2">
-        <v>-84.24</v>
-      </c>
+      <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-14.99</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="2">
-        <v>-57.99</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-17.95</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-13.09</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-    </row>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-    </row>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-    </row>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-    </row>
-    <row r="53" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-    </row>
-    <row r="54" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-    </row>
-    <row r="55" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-    </row>
-    <row r="56" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-    </row>
-    <row r="57" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-    </row>
-    <row r="58" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-    </row>
-    <row r="59" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-    </row>
-    <row r="60" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-    </row>
-    <row r="61" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-    </row>
-    <row r="62" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-    </row>
-    <row r="63" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-    </row>
-    <row r="64" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-    </row>
-    <row r="65" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-    </row>
-    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-    </row>
-    <row r="67" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-    </row>
-    <row r="68" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-    </row>
-    <row r="69" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-    </row>
-    <row r="70" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-    </row>
-    <row r="71" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-    </row>
-    <row r="72" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-    </row>
-    <row r="73" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-    </row>
-    <row r="74" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-    </row>
-    <row r="75" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-    </row>
-    <row r="76" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-    </row>
-    <row r="77" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-    </row>
-    <row r="78" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-    </row>
-    <row r="79" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-    </row>
-    <row r="80" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-    </row>
-    <row r="81" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-    </row>
-    <row r="82" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-    </row>
-    <row r="83" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-    </row>
-    <row r="84" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-    </row>
-    <row r="85" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-    </row>
-    <row r="86" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-    </row>
-    <row r="87" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-    </row>
-    <row r="88" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-    </row>
-    <row r="89" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-    </row>
-    <row r="90" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-    </row>
-    <row r="91" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-    </row>
-    <row r="92" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-    </row>
-    <row r="93" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-    </row>
-    <row r="94" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-    </row>
-    <row r="95" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-    </row>
-    <row r="96" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-    </row>
-    <row r="97" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-    </row>
-    <row r="98" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-    </row>
-    <row r="99" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-    </row>
-    <row r="100" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-    </row>
-    <row r="101" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-    </row>
-    <row r="102" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-    </row>
-    <row r="103" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-    </row>
-    <row r="104" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-    </row>
-    <row r="105" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-    </row>
-    <row r="106" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-    </row>
-    <row r="107" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-    </row>
-    <row r="108" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-    </row>
-    <row r="109" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-    </row>
-    <row r="110" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-    </row>
-    <row r="111" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-    </row>
-    <row r="112" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-    </row>
-    <row r="113" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-    </row>
-    <row r="114" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-    </row>
-    <row r="115" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-    </row>
-    <row r="116" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-    </row>
-    <row r="117" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-    </row>
-    <row r="118" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-    </row>
-    <row r="119" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-    </row>
-    <row r="120" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-    </row>
-    <row r="121" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-    </row>
-    <row r="122" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
-      <c r="G122" s="2"/>
-    </row>
-    <row r="123" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
-    </row>
-    <row r="124" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
-    </row>
-    <row r="125" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-    </row>
-    <row r="126" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
-      <c r="G126" s="2"/>
-    </row>
-    <row r="127" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
-      <c r="G127" s="2"/>
-    </row>
-    <row r="128" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
-    </row>
-    <row r="129" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
-      <c r="G129" s="2"/>
-    </row>
-    <row r="130" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
-      <c r="G130" s="2"/>
-    </row>
-    <row r="131" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-    </row>
-    <row r="132" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-    </row>
-    <row r="133" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-    </row>
-    <row r="134" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
-    </row>
-    <row r="135" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-    </row>
-    <row r="136" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
-      <c r="G136" s="2"/>
-    </row>
-    <row r="137" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
-      <c r="G137" s="2"/>
-    </row>
-    <row r="138" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
-    </row>
-    <row r="139" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
-      <c r="G139" s="2"/>
-    </row>
-    <row r="140" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-    </row>
-    <row r="141" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
-      <c r="G141" s="2"/>
-    </row>
-    <row r="142" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
-      <c r="G142" s="2"/>
-    </row>
-    <row r="143" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
-      <c r="G143" s="2"/>
-    </row>
-    <row r="144" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
-      <c r="G144" s="2"/>
-    </row>
-    <row r="145" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
-      <c r="G145" s="2"/>
-    </row>
-    <row r="146" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
-      <c r="G146" s="2"/>
-    </row>
-    <row r="147" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
-      <c r="G147" s="2"/>
-    </row>
-    <row r="148" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
-      <c r="G148" s="2"/>
-    </row>
-    <row r="149" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
-      <c r="G149" s="2"/>
-    </row>
-    <row r="150" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
-      <c r="G150" s="2"/>
-    </row>
-    <row r="151" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
-      <c r="G151" s="2"/>
-    </row>
-    <row r="152" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
-      <c r="G152" s="2"/>
-    </row>
-    <row r="153" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
-      <c r="G153" s="2"/>
-    </row>
-    <row r="154" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
-      <c r="G154" s="2"/>
-    </row>
-    <row r="155" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
-      <c r="G155" s="2"/>
-    </row>
-    <row r="156" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
-      <c r="G156" s="2"/>
-    </row>
-    <row r="157" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
-      <c r="G157" s="2"/>
-    </row>
-    <row r="158" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
-      <c r="G158" s="2"/>
-    </row>
-    <row r="159" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
-      <c r="G159" s="2"/>
-    </row>
-    <row r="160" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
-      <c r="G160" s="2"/>
-    </row>
-    <row r="161" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
-      <c r="G161" s="2"/>
-    </row>
-    <row r="162" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
-      <c r="G162" s="2"/>
-    </row>
-    <row r="163" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
-      <c r="G163" s="2"/>
-    </row>
-    <row r="164" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
-      <c r="G164" s="2"/>
-    </row>
-    <row r="165" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
-      <c r="G165" s="2"/>
-    </row>
-    <row r="166" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
-      <c r="G166" s="2"/>
-    </row>
-    <row r="167" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
-      <c r="G167" s="2"/>
-    </row>
-    <row r="168" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
-      <c r="G168" s="2"/>
-    </row>
-    <row r="169" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
-      <c r="G169" s="2"/>
-    </row>
-    <row r="170" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
-      <c r="G170" s="2"/>
-    </row>
-    <row r="171" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
-      <c r="G171" s="2"/>
-    </row>
-    <row r="172" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
-      <c r="G172" s="2"/>
-    </row>
-    <row r="173" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
-      <c r="G173" s="2"/>
-    </row>
-    <row r="174" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
-      <c r="G174" s="2"/>
-    </row>
-    <row r="175" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
-      <c r="G175" s="2"/>
-    </row>
-    <row r="176" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
-      <c r="G176" s="2"/>
-    </row>
-    <row r="177" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
-      <c r="G177" s="2"/>
-    </row>
-    <row r="178" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
-      <c r="G178" s="2"/>
-    </row>
-    <row r="179" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
-      <c r="G179" s="2"/>
-    </row>
-    <row r="180" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
-      <c r="G180" s="2"/>
-    </row>
-    <row r="181" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
-      <c r="G181" s="2"/>
-    </row>
-    <row r="182" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
-      <c r="G182" s="2"/>
-    </row>
-    <row r="183" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
-      <c r="G183" s="2"/>
-    </row>
-    <row r="184" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
-      <c r="G184" s="2"/>
-    </row>
-    <row r="185" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
-      <c r="G185" s="2"/>
-    </row>
-    <row r="186" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
-      <c r="G186" s="2"/>
-    </row>
-    <row r="187" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
-      <c r="G187" s="2"/>
-    </row>
-    <row r="188" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
-      <c r="G188" s="2"/>
-    </row>
-    <row r="189" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
-      <c r="G189" s="2"/>
-    </row>
-    <row r="190" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
-      <c r="G190" s="2"/>
-    </row>
-    <row r="191" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
-      <c r="G191" s="2"/>
-    </row>
-    <row r="192" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
-      <c r="G192" s="2"/>
-    </row>
-    <row r="193" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
-      <c r="G193" s="2"/>
-    </row>
-    <row r="194" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
-      <c r="G194" s="2"/>
-    </row>
-    <row r="195" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
-      <c r="G195" s="2"/>
-    </row>
-    <row r="196" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
-      <c r="G196" s="2"/>
-    </row>
-    <row r="197" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
-      <c r="G197" s="2"/>
-    </row>
-    <row r="198" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
       <c r="F198" s="2"/>
-      <c r="G198" s="2"/>
-    </row>
-    <row r="199" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
-      <c r="G199" s="2"/>
-    </row>
-    <row r="200" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
-      <c r="G200" s="2"/>
-    </row>
-    <row r="201" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
-      <c r="G201" s="2"/>
-    </row>
-    <row r="202" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
-      <c r="G202" s="2"/>
-    </row>
-    <row r="203" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
       <c r="E203" s="2"/>
       <c r="F203" s="2"/>
-      <c r="G203" s="2"/>
-    </row>
-    <row r="204" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
       <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
-    </row>
-    <row r="205" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-    </row>
-    <row r="206" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="206" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
-      <c r="G206" s="2"/>
-    </row>
-    <row r="207" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
-      <c r="G207" s="2"/>
-    </row>
-    <row r="208" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="208" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
-      <c r="G208" s="2"/>
-    </row>
-    <row r="209" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="209" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
-      <c r="G209" s="2"/>
-    </row>
-    <row r="210" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="210" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
-      <c r="G210" s="2"/>
-    </row>
-    <row r="211" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="211" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
-      <c r="G211" s="2"/>
-    </row>
-    <row r="212" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="212" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
-      <c r="G212" s="2"/>
-    </row>
-    <row r="213" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="213" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
-      <c r="G213" s="2"/>
-    </row>
-    <row r="214" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="214" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
-      <c r="G214" s="2"/>
-    </row>
-    <row r="215" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
-      <c r="G215" s="2"/>
-    </row>
-    <row r="216" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="216" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C216" s="2"/>
       <c r="D216" s="2"/>
       <c r="E216" s="2"/>
       <c r="F216" s="2"/>
-      <c r="G216" s="2"/>
-    </row>
-    <row r="217" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="217" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C217" s="2"/>
       <c r="D217" s="2"/>
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
-      <c r="G217" s="2"/>
-    </row>
-    <row r="218" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="218" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
-      <c r="G218" s="2"/>
-    </row>
-    <row r="219" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="219" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C219" s="2"/>
       <c r="D219" s="2"/>
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
-      <c r="G219" s="2"/>
-    </row>
-    <row r="220" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
       <c r="E220" s="2"/>
       <c r="F220" s="2"/>
-      <c r="G220" s="2"/>
-    </row>
-    <row r="221" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="221" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>
       <c r="E221" s="2"/>
       <c r="F221" s="2"/>
-      <c r="G221" s="2"/>
-    </row>
-    <row r="222" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="222" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
       <c r="E222" s="2"/>
       <c r="F222" s="2"/>
-      <c r="G222" s="2"/>
-    </row>
-    <row r="223" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="223" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C223" s="2"/>
       <c r="D223" s="2"/>
       <c r="E223" s="2"/>
       <c r="F223" s="2"/>
-      <c r="G223" s="2"/>
-    </row>
-    <row r="224" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="224" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C224" s="2"/>
       <c r="D224" s="2"/>
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
-      <c r="G224" s="2"/>
-    </row>
-    <row r="225" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C225" s="2"/>
       <c r="D225" s="2"/>
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
-      <c r="G225" s="2"/>
-    </row>
-    <row r="226" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="226" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C226" s="2"/>
       <c r="D226" s="2"/>
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
-      <c r="G226" s="2"/>
-    </row>
-    <row r="227" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="227" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C227" s="2"/>
       <c r="D227" s="2"/>
       <c r="E227" s="2"/>
       <c r="F227" s="2"/>
-      <c r="G227" s="2"/>
-    </row>
-    <row r="228" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="228" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
       <c r="E228" s="2"/>
       <c r="F228" s="2"/>
-      <c r="G228" s="2"/>
-    </row>
-    <row r="229" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
-      <c r="G229" s="2"/>
-    </row>
-    <row r="230" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
-      <c r="G230" s="2"/>
-    </row>
-    <row r="231" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="231" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C231" s="2"/>
       <c r="D231" s="2"/>
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
-      <c r="G231" s="2"/>
-    </row>
-    <row r="232" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="232" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C232" s="2"/>
       <c r="D232" s="2"/>
       <c r="E232" s="2"/>
       <c r="F232" s="2"/>
-      <c r="G232" s="2"/>
-    </row>
-    <row r="233" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="233" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C233" s="2"/>
       <c r="D233" s="2"/>
       <c r="E233" s="2"/>
       <c r="F233" s="2"/>
-      <c r="G233" s="2"/>
-    </row>
-    <row r="234" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="234" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C234" s="2"/>
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
-      <c r="G234" s="2"/>
-    </row>
-    <row r="235" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="235" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C235" s="2"/>
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
-      <c r="G235" s="2"/>
-    </row>
-    <row r="236" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="236" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C236" s="2"/>
       <c r="D236" s="2"/>
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
-      <c r="G236" s="2"/>
-    </row>
-    <row r="237" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="237" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C237" s="2"/>
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
-      <c r="G237" s="2"/>
-    </row>
-    <row r="238" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="238" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C238" s="2"/>
       <c r="D238" s="2"/>
       <c r="E238" s="2"/>
       <c r="F238" s="2"/>
-      <c r="G238" s="2"/>
-    </row>
-    <row r="239" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="239" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
-      <c r="G239" s="2"/>
-    </row>
-    <row r="240" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="240" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C240" s="2"/>
       <c r="D240" s="2"/>
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
-      <c r="G240" s="2"/>
-    </row>
-    <row r="241" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
       <c r="E241" s="2"/>
       <c r="F241" s="2"/>
-      <c r="G241" s="2"/>
-    </row>
-    <row r="242" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="242" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
       <c r="E242" s="2"/>
       <c r="F242" s="2"/>
-      <c r="G242" s="2"/>
-    </row>
-    <row r="243" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="243" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
       <c r="E243" s="2"/>
       <c r="F243" s="2"/>
-      <c r="G243" s="2"/>
-    </row>
-    <row r="244" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="244" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C244" s="2"/>
       <c r="D244" s="2"/>
       <c r="E244" s="2"/>
       <c r="F244" s="2"/>
-      <c r="G244" s="2"/>
-    </row>
-    <row r="245" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="245" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C245" s="2"/>
       <c r="D245" s="2"/>
       <c r="E245" s="2"/>
       <c r="F245" s="2"/>
-      <c r="G245" s="2"/>
-    </row>
-    <row r="246" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="246" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C246" s="2"/>
       <c r="D246" s="2"/>
       <c r="E246" s="2"/>
       <c r="F246" s="2"/>
-      <c r="G246" s="2"/>
-    </row>
-    <row r="247" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="247" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C247" s="2"/>
       <c r="D247" s="2"/>
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
-      <c r="G247" s="2"/>
-    </row>
-    <row r="248" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="248" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C248" s="2"/>
       <c r="D248" s="2"/>
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
-      <c r="G248" s="2"/>
-    </row>
-    <row r="249" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="249" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
       <c r="E249" s="2"/>
       <c r="F249" s="2"/>
-      <c r="G249" s="2"/>
-    </row>
-    <row r="250" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="250" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C250" s="2"/>
       <c r="D250" s="2"/>
       <c r="E250" s="2"/>
       <c r="F250" s="2"/>
-      <c r="G250" s="2"/>
-    </row>
-    <row r="251" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="251" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C251" s="2"/>
       <c r="D251" s="2"/>
       <c r="E251" s="2"/>
       <c r="F251" s="2"/>
-      <c r="G251" s="2"/>
-    </row>
-    <row r="252" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="252" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C252" s="2"/>
       <c r="D252" s="2"/>
       <c r="E252" s="2"/>
       <c r="F252" s="2"/>
-      <c r="G252" s="2"/>
-    </row>
-    <row r="253" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="253" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C253" s="2"/>
       <c r="D253" s="2"/>
       <c r="E253" s="2"/>
       <c r="F253" s="2"/>
-      <c r="G253" s="2"/>
-    </row>
-    <row r="254" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="254" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C254" s="2"/>
       <c r="D254" s="2"/>
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
-      <c r="G254" s="2"/>
-    </row>
-    <row r="255" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="255" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C255" s="2"/>
       <c r="D255" s="2"/>
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
-      <c r="G255" s="2"/>
-    </row>
-    <row r="256" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="256" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C256" s="2"/>
       <c r="D256" s="2"/>
       <c r="E256" s="2"/>
       <c r="F256" s="2"/>
-      <c r="G256" s="2"/>
-    </row>
-    <row r="257" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="257" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C257" s="2"/>
       <c r="D257" s="2"/>
       <c r="E257" s="2"/>
       <c r="F257" s="2"/>
-      <c r="G257" s="2"/>
-    </row>
-    <row r="258" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="258" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C258" s="2"/>
       <c r="D258" s="2"/>
       <c r="E258" s="2"/>
       <c r="F258" s="2"/>
-      <c r="G258" s="2"/>
-    </row>
-    <row r="259" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C259" s="2"/>
       <c r="D259" s="2"/>
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
-      <c r="G259" s="2"/>
-    </row>
-    <row r="260" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="260" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
-      <c r="G260" s="2"/>
-    </row>
-    <row r="261" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="261" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
       <c r="E261" s="2"/>
       <c r="F261" s="2"/>
-      <c r="G261" s="2"/>
-    </row>
-    <row r="262" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="262" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
       <c r="E262" s="2"/>
       <c r="F262" s="2"/>
-      <c r="G262" s="2"/>
-    </row>
-    <row r="263" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="263" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
       <c r="E263" s="2"/>
       <c r="F263" s="2"/>
-      <c r="G263" s="2"/>
-    </row>
-    <row r="264" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="264" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
       <c r="E264" s="2"/>
       <c r="F264" s="2"/>
-      <c r="G264" s="2"/>
-    </row>
-    <row r="265" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="265" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
-      <c r="G265" s="2"/>
-    </row>
-    <row r="266" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="266" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C266" s="2"/>
       <c r="D266" s="2"/>
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
-      <c r="G266" s="2"/>
-    </row>
-    <row r="267" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="267" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C267" s="2"/>
       <c r="D267" s="2"/>
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
-      <c r="G267" s="2"/>
-    </row>
-    <row r="268" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="268" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C268" s="2"/>
       <c r="D268" s="2"/>
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
-      <c r="G268" s="2"/>
-    </row>
-    <row r="269" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="269" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
-      <c r="G269" s="2"/>
-    </row>
-    <row r="270" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="270" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C270" s="2"/>
       <c r="D270" s="2"/>
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
-      <c r="G270" s="2"/>
-    </row>
-    <row r="271" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="271" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C271" s="2"/>
       <c r="D271" s="2"/>
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
-      <c r="G271" s="2"/>
-    </row>
-    <row r="272" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="272" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
-      <c r="G272" s="2"/>
-    </row>
-    <row r="273" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="273" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
       <c r="E273" s="2"/>
       <c r="F273" s="2"/>
-      <c r="G273" s="2"/>
-    </row>
-    <row r="274" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="274" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C274" s="2"/>
       <c r="D274" s="2"/>
       <c r="E274" s="2"/>
       <c r="F274" s="2"/>
-      <c r="G274" s="2"/>
-    </row>
-    <row r="275" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="275" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
-      <c r="G275" s="2"/>
-    </row>
-    <row r="276" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="276" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
-      <c r="G276" s="2"/>
-    </row>
-    <row r="277" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="277" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C277" s="2"/>
       <c r="D277" s="2"/>
       <c r="E277" s="2"/>
       <c r="F277" s="2"/>
-      <c r="G277" s="2"/>
-    </row>
-    <row r="278" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="278" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C278" s="2"/>
       <c r="D278" s="2"/>
       <c r="E278" s="2"/>
       <c r="F278" s="2"/>
-      <c r="G278" s="2"/>
-    </row>
-    <row r="279" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="279" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C279" s="2"/>
       <c r="D279" s="2"/>
       <c r="E279" s="2"/>
       <c r="F279" s="2"/>
-      <c r="G279" s="2"/>
-    </row>
-    <row r="280" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="280" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C280" s="2"/>
       <c r="D280" s="2"/>
       <c r="E280" s="2"/>
       <c r="F280" s="2"/>
-      <c r="G280" s="2"/>
-    </row>
-    <row r="281" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="281" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C281" s="2"/>
       <c r="D281" s="2"/>
       <c r="E281" s="2"/>
       <c r="F281" s="2"/>
-      <c r="G281" s="2"/>
-    </row>
-    <row r="282" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="282" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C282" s="2"/>
       <c r="D282" s="2"/>
       <c r="E282" s="2"/>
       <c r="F282" s="2"/>
-      <c r="G282" s="2"/>
-    </row>
-    <row r="283" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="283" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C283" s="2"/>
       <c r="D283" s="2"/>
       <c r="E283" s="2"/>
       <c r="F283" s="2"/>
-      <c r="G283" s="2"/>
-    </row>
-    <row r="284" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="284" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C284" s="2"/>
       <c r="D284" s="2"/>
       <c r="E284" s="2"/>
       <c r="F284" s="2"/>
-      <c r="G284" s="2"/>
-    </row>
-    <row r="285" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="285" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C285" s="2"/>
       <c r="D285" s="2"/>
       <c r="E285" s="2"/>
       <c r="F285" s="2"/>
-      <c r="G285" s="2"/>
-    </row>
-    <row r="286" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="286" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C286" s="2"/>
       <c r="D286" s="2"/>
       <c r="E286" s="2"/>
       <c r="F286" s="2"/>
-      <c r="G286" s="2"/>
-    </row>
-    <row r="287" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="287" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C287" s="2"/>
       <c r="D287" s="2"/>
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
-      <c r="G287" s="2"/>
-    </row>
-    <row r="288" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="288" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C288" s="2"/>
       <c r="D288" s="2"/>
       <c r="E288" s="2"/>
       <c r="F288" s="2"/>
-      <c r="G288" s="2"/>
-    </row>
-    <row r="289" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="289" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C289" s="2"/>
       <c r="D289" s="2"/>
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
-      <c r="G289" s="2"/>
-    </row>
-    <row r="290" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="290" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C290" s="2"/>
       <c r="D290" s="2"/>
       <c r="E290" s="2"/>
       <c r="F290" s="2"/>
-      <c r="G290" s="2"/>
-    </row>
-    <row r="291" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="291" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C291" s="2"/>
       <c r="D291" s="2"/>
       <c r="E291" s="2"/>
       <c r="F291" s="2"/>
-      <c r="G291" s="2"/>
-    </row>
-    <row r="292" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="292" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C292" s="2"/>
       <c r="D292" s="2"/>
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
-      <c r="G292" s="2"/>
-    </row>
-    <row r="293" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="293" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C293" s="2"/>
       <c r="D293" s="2"/>
       <c r="E293" s="2"/>
       <c r="F293" s="2"/>
-      <c r="G293" s="2"/>
-    </row>
-    <row r="294" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="294" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C294" s="2"/>
       <c r="D294" s="2"/>
       <c r="E294" s="2"/>
       <c r="F294" s="2"/>
-      <c r="G294" s="2"/>
-    </row>
-    <row r="295" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="295" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C295" s="2"/>
       <c r="D295" s="2"/>
       <c r="E295" s="2"/>
       <c r="F295" s="2"/>
-      <c r="G295" s="2"/>
-    </row>
-    <row r="296" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="296" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C296" s="2"/>
       <c r="D296" s="2"/>
       <c r="E296" s="2"/>
       <c r="F296" s="2"/>
-      <c r="G296" s="2"/>
-    </row>
-    <row r="297" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="297" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C297" s="2"/>
       <c r="D297" s="2"/>
       <c r="E297" s="2"/>
       <c r="F297" s="2"/>
-      <c r="G297" s="2"/>
-    </row>
-    <row r="298" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="298" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C298" s="2"/>
       <c r="D298" s="2"/>
       <c r="E298" s="2"/>
       <c r="F298" s="2"/>
-      <c r="G298" s="2"/>
-    </row>
-    <row r="299" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="299" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C299" s="2"/>
       <c r="D299" s="2"/>
       <c r="E299" s="2"/>
       <c r="F299" s="2"/>
-      <c r="G299" s="2"/>
-    </row>
-    <row r="300" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="300" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C300" s="2"/>
       <c r="D300" s="2"/>
       <c r="E300" s="2"/>
       <c r="F300" s="2"/>
-      <c r="G300" s="2"/>
-    </row>
-    <row r="301" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="301" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C301" s="2"/>
       <c r="D301" s="2"/>
       <c r="E301" s="2"/>
       <c r="F301" s="2"/>
-      <c r="G301" s="2"/>
-    </row>
-    <row r="302" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="302" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C302" s="2"/>
       <c r="D302" s="2"/>
       <c r="E302" s="2"/>
       <c r="F302" s="2"/>
-      <c r="G302" s="2"/>
-    </row>
-    <row r="303" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="303" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C303" s="2"/>
       <c r="D303" s="2"/>
       <c r="E303" s="2"/>
       <c r="F303" s="2"/>
-      <c r="G303" s="2"/>
-    </row>
-    <row r="304" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="304" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C304" s="2"/>
       <c r="D304" s="2"/>
       <c r="E304" s="2"/>
       <c r="F304" s="2"/>
-      <c r="G304" s="2"/>
-    </row>
-    <row r="305" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="305" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C305" s="2"/>
       <c r="D305" s="2"/>
       <c r="E305" s="2"/>
       <c r="F305" s="2"/>
-      <c r="G305" s="2"/>
-    </row>
-    <row r="306" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="306" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C306" s="2"/>
       <c r="D306" s="2"/>
       <c r="E306" s="2"/>
       <c r="F306" s="2"/>
-      <c r="G306" s="2"/>
-    </row>
-    <row r="307" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="307" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C307" s="2"/>
       <c r="D307" s="2"/>
       <c r="E307" s="2"/>
       <c r="F307" s="2"/>
-      <c r="G307" s="2"/>
-    </row>
-    <row r="308" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="308" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C308" s="2"/>
       <c r="D308" s="2"/>
       <c r="E308" s="2"/>
       <c r="F308" s="2"/>
-      <c r="G308" s="2"/>
-    </row>
-    <row r="309" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="309" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C309" s="2"/>
       <c r="D309" s="2"/>
       <c r="E309" s="2"/>
       <c r="F309" s="2"/>
-      <c r="G309" s="2"/>
-    </row>
-    <row r="310" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="310" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C310" s="2"/>
       <c r="D310" s="2"/>
       <c r="E310" s="2"/>
       <c r="F310" s="2"/>
-      <c r="G310" s="2"/>
-    </row>
-    <row r="311" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="311" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C311" s="2"/>
       <c r="D311" s="2"/>
       <c r="E311" s="2"/>
       <c r="F311" s="2"/>
-      <c r="G311" s="2"/>
-    </row>
-    <row r="312" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="312" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C312" s="2"/>
       <c r="D312" s="2"/>
       <c r="E312" s="2"/>
       <c r="F312" s="2"/>
-      <c r="G312" s="2"/>
-    </row>
-    <row r="313" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="313" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C313" s="2"/>
       <c r="D313" s="2"/>
       <c r="E313" s="2"/>
       <c r="F313" s="2"/>
-      <c r="G313" s="2"/>
-    </row>
-    <row r="314" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="314" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C314" s="2"/>
       <c r="D314" s="2"/>
       <c r="E314" s="2"/>
       <c r="F314" s="2"/>
-      <c r="G314" s="2"/>
-    </row>
-    <row r="315" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="315" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C315" s="2"/>
       <c r="D315" s="2"/>
       <c r="E315" s="2"/>
       <c r="F315" s="2"/>
-      <c r="G315" s="2"/>
-    </row>
-    <row r="316" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="316" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C316" s="2"/>
       <c r="D316" s="2"/>
       <c r="E316" s="2"/>
       <c r="F316" s="2"/>
-      <c r="G316" s="2"/>
-    </row>
-    <row r="317" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="317" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C317" s="2"/>
       <c r="D317" s="2"/>
       <c r="E317" s="2"/>
       <c r="F317" s="2"/>
-      <c r="G317" s="2"/>
-    </row>
-    <row r="318" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="318" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C318" s="2"/>
       <c r="D318" s="2"/>
       <c r="E318" s="2"/>
       <c r="F318" s="2"/>
-      <c r="G318" s="2"/>
-    </row>
-    <row r="319" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="319" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C319" s="2"/>
       <c r="D319" s="2"/>
       <c r="E319" s="2"/>
       <c r="F319" s="2"/>
-      <c r="G319" s="2"/>
-    </row>
-    <row r="320" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="320" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C320" s="2"/>
       <c r="D320" s="2"/>
       <c r="E320" s="2"/>
       <c r="F320" s="2"/>
-      <c r="G320" s="2"/>
-    </row>
-    <row r="321" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="321" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C321" s="2"/>
       <c r="D321" s="2"/>
       <c r="E321" s="2"/>
       <c r="F321" s="2"/>
-      <c r="G321" s="2"/>
-    </row>
-    <row r="322" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="322" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C322" s="2"/>
       <c r="D322" s="2"/>
       <c r="E322" s="2"/>
       <c r="F322" s="2"/>
-      <c r="G322" s="2"/>
-    </row>
-    <row r="323" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="323" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C323" s="2"/>
       <c r="D323" s="2"/>
       <c r="E323" s="2"/>
       <c r="F323" s="2"/>
-      <c r="G323" s="2"/>
-    </row>
-    <row r="324" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="324" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C324" s="2"/>
       <c r="D324" s="2"/>
       <c r="E324" s="2"/>
       <c r="F324" s="2"/>
-      <c r="G324" s="2"/>
-    </row>
-    <row r="325" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="325" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C325" s="2"/>
       <c r="D325" s="2"/>
       <c r="E325" s="2"/>
       <c r="F325" s="2"/>
-      <c r="G325" s="2"/>
-    </row>
-    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="326" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C326" s="2"/>
       <c r="D326" s="2"/>
       <c r="E326" s="2"/>
       <c r="F326" s="2"/>
-      <c r="G326" s="2"/>
-    </row>
-    <row r="327" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="327" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C327" s="2"/>
       <c r="D327" s="2"/>
       <c r="E327" s="2"/>
       <c r="F327" s="2"/>
-      <c r="G327" s="2"/>
-    </row>
-    <row r="328" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="328" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C328" s="2"/>
       <c r="D328" s="2"/>
       <c r="E328" s="2"/>
       <c r="F328" s="2"/>
-      <c r="G328" s="2"/>
-    </row>
-    <row r="329" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="329" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C329" s="2"/>
       <c r="D329" s="2"/>
       <c r="E329" s="2"/>
       <c r="F329" s="2"/>
-      <c r="G329" s="2"/>
-    </row>
-    <row r="330" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="330" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C330" s="2"/>
       <c r="D330" s="2"/>
       <c r="E330" s="2"/>
       <c r="F330" s="2"/>
-      <c r="G330" s="2"/>
-    </row>
-    <row r="331" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="331" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C331" s="2"/>
       <c r="D331" s="2"/>
       <c r="E331" s="2"/>
       <c r="F331" s="2"/>
-      <c r="G331" s="2"/>
-    </row>
-    <row r="332" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="332" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C332" s="2"/>
       <c r="D332" s="2"/>
       <c r="E332" s="2"/>
       <c r="F332" s="2"/>
-      <c r="G332" s="2"/>
-    </row>
-    <row r="333" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="333" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C333" s="2"/>
       <c r="D333" s="2"/>
       <c r="E333" s="2"/>
       <c r="F333" s="2"/>
-      <c r="G333" s="2"/>
-    </row>
-    <row r="334" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="334" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C334" s="2"/>
       <c r="D334" s="2"/>
       <c r="E334" s="2"/>
       <c r="F334" s="2"/>
-      <c r="G334" s="2"/>
-    </row>
-    <row r="335" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="335" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C335" s="2"/>
       <c r="D335" s="2"/>
       <c r="E335" s="2"/>
       <c r="F335" s="2"/>
-      <c r="G335" s="2"/>
-    </row>
-    <row r="336" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="336" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C336" s="2"/>
       <c r="D336" s="2"/>
       <c r="E336" s="2"/>
       <c r="F336" s="2"/>
-      <c r="G336" s="2"/>
-    </row>
-    <row r="337" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="337" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C337" s="2"/>
       <c r="D337" s="2"/>
       <c r="E337" s="2"/>
       <c r="F337" s="2"/>
-      <c r="G337" s="2"/>
-    </row>
-    <row r="338" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="338" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C338" s="2"/>
       <c r="D338" s="2"/>
       <c r="E338" s="2"/>
       <c r="F338" s="2"/>
-      <c r="G338" s="2"/>
-    </row>
-    <row r="339" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="339" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C339" s="2"/>
       <c r="D339" s="2"/>
       <c r="E339" s="2"/>
       <c r="F339" s="2"/>
-      <c r="G339" s="2"/>
-    </row>
-    <row r="340" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="340" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C340" s="2"/>
       <c r="D340" s="2"/>
       <c r="E340" s="2"/>
       <c r="F340" s="2"/>
-      <c r="G340" s="2"/>
-    </row>
-    <row r="341" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="341" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C341" s="2"/>
       <c r="D341" s="2"/>
       <c r="E341" s="2"/>
       <c r="F341" s="2"/>
-      <c r="G341" s="2"/>
-    </row>
-    <row r="342" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="342" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C342" s="2"/>
       <c r="D342" s="2"/>
       <c r="E342" s="2"/>
       <c r="F342" s="2"/>
-      <c r="G342" s="2"/>
-    </row>
-    <row r="343" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="343" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C343" s="2"/>
       <c r="D343" s="2"/>
       <c r="E343" s="2"/>
       <c r="F343" s="2"/>
-      <c r="G343" s="2"/>
-    </row>
-    <row r="344" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="344" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C344" s="2"/>
       <c r="D344" s="2"/>
       <c r="E344" s="2"/>
       <c r="F344" s="2"/>
-      <c r="G344" s="2"/>
-    </row>
-    <row r="345" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="345" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C345" s="2"/>
       <c r="D345" s="2"/>
       <c r="E345" s="2"/>
       <c r="F345" s="2"/>
-      <c r="G345" s="2"/>
-    </row>
-    <row r="346" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="346" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C346" s="2"/>
       <c r="D346" s="2"/>
       <c r="E346" s="2"/>
       <c r="F346" s="2"/>
-      <c r="G346" s="2"/>
-    </row>
-    <row r="347" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="347" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C347" s="2"/>
       <c r="D347" s="2"/>
       <c r="E347" s="2"/>
       <c r="F347" s="2"/>
-      <c r="G347" s="2"/>
-    </row>
-    <row r="348" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="348" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C348" s="2"/>
       <c r="D348" s="2"/>
       <c r="E348" s="2"/>
       <c r="F348" s="2"/>
-      <c r="G348" s="2"/>
-    </row>
-    <row r="349" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="349" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C349" s="2"/>
       <c r="D349" s="2"/>
       <c r="E349" s="2"/>
       <c r="F349" s="2"/>
-      <c r="G349" s="2"/>
-    </row>
-    <row r="350" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="350" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C350" s="2"/>
       <c r="D350" s="2"/>
       <c r="E350" s="2"/>
       <c r="F350" s="2"/>
-      <c r="G350" s="2"/>
-    </row>
-    <row r="351" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="351" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C351" s="2"/>
       <c r="D351" s="2"/>
       <c r="E351" s="2"/>
       <c r="F351" s="2"/>
-      <c r="G351" s="2"/>
-    </row>
-    <row r="352" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="352" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C352" s="2"/>
       <c r="D352" s="2"/>
       <c r="E352" s="2"/>
       <c r="F352" s="2"/>
-      <c r="G352" s="2"/>
-    </row>
-    <row r="353" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="353" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C353" s="2"/>
       <c r="D353" s="2"/>
       <c r="E353" s="2"/>
       <c r="F353" s="2"/>
-      <c r="G353" s="2"/>
-    </row>
-    <row r="354" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="354" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C354" s="2"/>
       <c r="D354" s="2"/>
       <c r="E354" s="2"/>
       <c r="F354" s="2"/>
-      <c r="G354" s="2"/>
-    </row>
-    <row r="355" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="355" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C355" s="2"/>
       <c r="D355" s="2"/>
       <c r="E355" s="2"/>
       <c r="F355" s="2"/>
-      <c r="G355" s="2"/>
-    </row>
-    <row r="356" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="356" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C356" s="2"/>
       <c r="D356" s="2"/>
       <c r="E356" s="2"/>
       <c r="F356" s="2"/>
-      <c r="G356" s="2"/>
-    </row>
-    <row r="357" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="357" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C357" s="2"/>
       <c r="D357" s="2"/>
       <c r="E357" s="2"/>
       <c r="F357" s="2"/>
-      <c r="G357" s="2"/>
-    </row>
-    <row r="358" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="358" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C358" s="2"/>
       <c r="D358" s="2"/>
       <c r="E358" s="2"/>
       <c r="F358" s="2"/>
-      <c r="G358" s="2"/>
-    </row>
-    <row r="359" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="359" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C359" s="2"/>
       <c r="D359" s="2"/>
       <c r="E359" s="2"/>
       <c r="F359" s="2"/>
-      <c r="G359" s="2"/>
-    </row>
-    <row r="360" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="360" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C360" s="2"/>
       <c r="D360" s="2"/>
       <c r="E360" s="2"/>
       <c r="F360" s="2"/>
-      <c r="G360" s="2"/>
-    </row>
-    <row r="361" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="361" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C361" s="2"/>
       <c r="D361" s="2"/>
       <c r="E361" s="2"/>
       <c r="F361" s="2"/>
-      <c r="G361" s="2"/>
-    </row>
-    <row r="362" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="362" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C362" s="2"/>
       <c r="D362" s="2"/>
       <c r="E362" s="2"/>
       <c r="F362" s="2"/>
-      <c r="G362" s="2"/>
-    </row>
-    <row r="363" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="363" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C363" s="2"/>
       <c r="D363" s="2"/>
       <c r="E363" s="2"/>
       <c r="F363" s="2"/>
-      <c r="G363" s="2"/>
-    </row>
-    <row r="364" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="364" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C364" s="2"/>
       <c r="D364" s="2"/>
       <c r="E364" s="2"/>
       <c r="F364" s="2"/>
-      <c r="G364" s="2"/>
-    </row>
-    <row r="365" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="365" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C365" s="2"/>
       <c r="D365" s="2"/>
       <c r="E365" s="2"/>
       <c r="F365" s="2"/>
-      <c r="G365" s="2"/>
-    </row>
-    <row r="366" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="366" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C366" s="2"/>
       <c r="D366" s="2"/>
       <c r="E366" s="2"/>
       <c r="F366" s="2"/>
-      <c r="G366" s="2"/>
-    </row>
-    <row r="367" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="367" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C367" s="2"/>
       <c r="D367" s="2"/>
       <c r="E367" s="2"/>
       <c r="F367" s="2"/>
-      <c r="G367" s="2"/>
-    </row>
-    <row r="368" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="368" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C368" s="2"/>
       <c r="D368" s="2"/>
       <c r="E368" s="2"/>
       <c r="F368" s="2"/>
-      <c r="G368" s="2"/>
-    </row>
-    <row r="369" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="369" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C369" s="2"/>
       <c r="D369" s="2"/>
       <c r="E369" s="2"/>
       <c r="F369" s="2"/>
-      <c r="G369" s="2"/>
-    </row>
-    <row r="370" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="370" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C370" s="2"/>
       <c r="D370" s="2"/>
       <c r="E370" s="2"/>
       <c r="F370" s="2"/>
-      <c r="G370" s="2"/>
-    </row>
-    <row r="371" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="371" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C371" s="2"/>
       <c r="D371" s="2"/>
       <c r="E371" s="2"/>
       <c r="F371" s="2"/>
-      <c r="G371" s="2"/>
-    </row>
-    <row r="372" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="372" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C372" s="2"/>
       <c r="D372" s="2"/>
       <c r="E372" s="2"/>
       <c r="F372" s="2"/>
-      <c r="G372" s="2"/>
-    </row>
-    <row r="373" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="373" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C373" s="2"/>
       <c r="D373" s="2"/>
       <c r="E373" s="2"/>
       <c r="F373" s="2"/>
-      <c r="G373" s="2"/>
-    </row>
-    <row r="374" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="374" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C374" s="2"/>
       <c r="D374" s="2"/>
       <c r="E374" s="2"/>
       <c r="F374" s="2"/>
-      <c r="G374" s="2"/>
-    </row>
-    <row r="375" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="375" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C375" s="2"/>
       <c r="D375" s="2"/>
       <c r="E375" s="2"/>
       <c r="F375" s="2"/>
-      <c r="G375" s="2"/>
-    </row>
-    <row r="376" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="376" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C376" s="2"/>
       <c r="D376" s="2"/>
       <c r="E376" s="2"/>
       <c r="F376" s="2"/>
-      <c r="G376" s="2"/>
-    </row>
-    <row r="377" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="377" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C377" s="2"/>
       <c r="D377" s="2"/>
       <c r="E377" s="2"/>
       <c r="F377" s="2"/>
-      <c r="G377" s="2"/>
-    </row>
-    <row r="378" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="378" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C378" s="2"/>
       <c r="D378" s="2"/>
       <c r="E378" s="2"/>
       <c r="F378" s="2"/>
-      <c r="G378" s="2"/>
-    </row>
-    <row r="379" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="379" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C379" s="2"/>
       <c r="D379" s="2"/>
       <c r="E379" s="2"/>
       <c r="F379" s="2"/>
-      <c r="G379" s="2"/>
-    </row>
-    <row r="380" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="380" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C380" s="2"/>
       <c r="D380" s="2"/>
       <c r="E380" s="2"/>
       <c r="F380" s="2"/>
-      <c r="G380" s="2"/>
-    </row>
-    <row r="381" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="381" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C381" s="2"/>
       <c r="D381" s="2"/>
       <c r="E381" s="2"/>
       <c r="F381" s="2"/>
-      <c r="G381" s="2"/>
-    </row>
-    <row r="382" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="382" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C382" s="2"/>
       <c r="D382" s="2"/>
       <c r="E382" s="2"/>
       <c r="F382" s="2"/>
-      <c r="G382" s="2"/>
-    </row>
-    <row r="383" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="383" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C383" s="2"/>
       <c r="D383" s="2"/>
       <c r="E383" s="2"/>
       <c r="F383" s="2"/>
-      <c r="G383" s="2"/>
-    </row>
-    <row r="384" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="384" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C384" s="2"/>
       <c r="D384" s="2"/>
       <c r="E384" s="2"/>
       <c r="F384" s="2"/>
-      <c r="G384" s="2"/>
-    </row>
-    <row r="385" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="385" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C385" s="2"/>
       <c r="D385" s="2"/>
       <c r="E385" s="2"/>
       <c r="F385" s="2"/>
-      <c r="G385" s="2"/>
-    </row>
-    <row r="386" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="386" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C386" s="2"/>
       <c r="D386" s="2"/>
       <c r="E386" s="2"/>
       <c r="F386" s="2"/>
-      <c r="G386" s="2"/>
-    </row>
-    <row r="387" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="387" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C387" s="2"/>
       <c r="D387" s="2"/>
       <c r="E387" s="2"/>
       <c r="F387" s="2"/>
-      <c r="G387" s="2"/>
-    </row>
-    <row r="388" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="388" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C388" s="2"/>
       <c r="D388" s="2"/>
       <c r="E388" s="2"/>
       <c r="F388" s="2"/>
-      <c r="G388" s="2"/>
-    </row>
-    <row r="389" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="389" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C389" s="2"/>
       <c r="D389" s="2"/>
       <c r="E389" s="2"/>
       <c r="F389" s="2"/>
-      <c r="G389" s="2"/>
-    </row>
-    <row r="390" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="390" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C390" s="2"/>
       <c r="D390" s="2"/>
       <c r="E390" s="2"/>
       <c r="F390" s="2"/>
-      <c r="G390" s="2"/>
-    </row>
-    <row r="391" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="391" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C391" s="2"/>
       <c r="D391" s="2"/>
       <c r="E391" s="2"/>
       <c r="F391" s="2"/>
-      <c r="G391" s="2"/>
-    </row>
-    <row r="392" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="392" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C392" s="2"/>
       <c r="D392" s="2"/>
       <c r="E392" s="2"/>
       <c r="F392" s="2"/>
-      <c r="G392" s="2"/>
-    </row>
-    <row r="393" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="393" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C393" s="2"/>
       <c r="D393" s="2"/>
       <c r="E393" s="2"/>
       <c r="F393" s="2"/>
-      <c r="G393" s="2"/>
-    </row>
-    <row r="394" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="394" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C394" s="2"/>
       <c r="D394" s="2"/>
       <c r="E394" s="2"/>
       <c r="F394" s="2"/>
-      <c r="G394" s="2"/>
-    </row>
-    <row r="395" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="395" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C395" s="2"/>
       <c r="D395" s="2"/>
       <c r="E395" s="2"/>
       <c r="F395" s="2"/>
-      <c r="G395" s="2"/>
-    </row>
-    <row r="396" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="396" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C396" s="2"/>
       <c r="D396" s="2"/>
       <c r="E396" s="2"/>
       <c r="F396" s="2"/>
-      <c r="G396" s="2"/>
-    </row>
-    <row r="397" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="397" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C397" s="2"/>
       <c r="D397" s="2"/>
       <c r="E397" s="2"/>
       <c r="F397" s="2"/>
-      <c r="G397" s="2"/>
-    </row>
-    <row r="398" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="398" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C398" s="2"/>
       <c r="D398" s="2"/>
       <c r="E398" s="2"/>
       <c r="F398" s="2"/>
-      <c r="G398" s="2"/>
-    </row>
-    <row r="399" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="399" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C399" s="2"/>
       <c r="D399" s="2"/>
       <c r="E399" s="2"/>
       <c r="F399" s="2"/>
-      <c r="G399" s="2"/>
-    </row>
-    <row r="400" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="400" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C400" s="2"/>
       <c r="D400" s="2"/>
       <c r="E400" s="2"/>
       <c r="F400" s="2"/>
-      <c r="G400" s="2"/>
-    </row>
-    <row r="401" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="401" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C401" s="2"/>
       <c r="D401" s="2"/>
       <c r="E401" s="2"/>
       <c r="F401" s="2"/>
-      <c r="G401" s="2"/>
-    </row>
-    <row r="402" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="402" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C402" s="2"/>
       <c r="D402" s="2"/>
       <c r="E402" s="2"/>
       <c r="F402" s="2"/>
-      <c r="G402" s="2"/>
-    </row>
-    <row r="403" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="403" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C403" s="2"/>
       <c r="D403" s="2"/>
       <c r="E403" s="2"/>
       <c r="F403" s="2"/>
-      <c r="G403" s="2"/>
-    </row>
-    <row r="404" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="404" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C404" s="2"/>
       <c r="D404" s="2"/>
       <c r="E404" s="2"/>
       <c r="F404" s="2"/>
-      <c r="G404" s="2"/>
-    </row>
-    <row r="405" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="405" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C405" s="2"/>
       <c r="D405" s="2"/>
       <c r="E405" s="2"/>
       <c r="F405" s="2"/>
-      <c r="G405" s="2"/>
-    </row>
-    <row r="406" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="406" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C406" s="2"/>
       <c r="D406" s="2"/>
       <c r="E406" s="2"/>
       <c r="F406" s="2"/>
-      <c r="G406" s="2"/>
-    </row>
-    <row r="407" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="407" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C407" s="2"/>
       <c r="D407" s="2"/>
       <c r="E407" s="2"/>
       <c r="F407" s="2"/>
-      <c r="G407" s="2"/>
-    </row>
-    <row r="408" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="408" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C408" s="2"/>
       <c r="D408" s="2"/>
       <c r="E408" s="2"/>
       <c r="F408" s="2"/>
-      <c r="G408" s="2"/>
-    </row>
-    <row r="409" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="409" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C409" s="2"/>
       <c r="D409" s="2"/>
       <c r="E409" s="2"/>
       <c r="F409" s="2"/>
-      <c r="G409" s="2"/>
-    </row>
-    <row r="410" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="410" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C410" s="2"/>
       <c r="D410" s="2"/>
       <c r="E410" s="2"/>
       <c r="F410" s="2"/>
-      <c r="G410" s="2"/>
-    </row>
-    <row r="411" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="411" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C411" s="2"/>
       <c r="D411" s="2"/>
       <c r="E411" s="2"/>
       <c r="F411" s="2"/>
-      <c r="G411" s="2"/>
-    </row>
-    <row r="412" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="412" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C412" s="2"/>
       <c r="D412" s="2"/>
       <c r="E412" s="2"/>
       <c r="F412" s="2"/>
-      <c r="G412" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -9304,24 +8851,24 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" s="7">
         <v>-176.6</v>
@@ -9332,7 +8879,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="7">
         <v>-149.99</v>
@@ -9349,7 +8896,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="7">
         <v>-79.989999999999995</v>
@@ -9362,7 +8909,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="7">
         <v>-497.45</v>
@@ -9373,7 +8920,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="7">
         <v>-160</v>
@@ -9390,7 +8937,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="7">
         <v>-31.9</v>
@@ -9407,7 +8954,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" s="7">
         <v>-293</v>
@@ -9424,7 +8971,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="7">
         <v>-131.54</v>
@@ -9441,7 +8988,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C11" s="7">
         <v>-13.9</v>
@@ -9458,7 +9005,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="7">
         <v>-173.3</v>
@@ -9469,7 +9016,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C13" s="7">
         <v>-211.4</v>
@@ -11781,24 +11328,24 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2">
         <v>-700.3</v>
@@ -11815,7 +11362,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2">
         <v>-475.15</v>
@@ -11832,7 +11379,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2">
         <v>-345.58</v>
@@ -11849,7 +11396,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2">
         <v>-65.22</v>
@@ -11866,7 +11413,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2">
         <v>-139.06</v>
@@ -11883,7 +11430,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2">
         <v>-37.47</v>
@@ -11900,7 +11447,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2">
         <v>-44.55</v>
@@ -11917,7 +11464,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2">
         <v>-109.79</v>
@@ -11934,7 +11481,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2">
         <v>-221.48</v>
@@ -11951,7 +11498,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -11960,7 +11507,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2">
         <v>-180</v>
@@ -11977,7 +11524,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="2">
         <v>-660</v>
@@ -11994,7 +11541,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="2">
         <v>-40</v>
@@ -12011,7 +11558,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -12020,7 +11567,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -12029,7 +11576,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="2">
         <v>-130</v>
@@ -12046,7 +11593,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="2">
         <v>-156.37</v>
@@ -12069,7 +11616,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2">
         <v>-1276</v>
@@ -14470,22 +14017,22 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A457CDC9-2DDE-43C4-AE91-352A7587511F}">
-  <dimension ref="A1:G399"/>
+  <dimension ref="A1:F399"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="7" width="12.7109375" style="1" customWidth="1"/>
+    <col min="3" max="6" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
-        <f t="shared" ref="C1:G1" si="0">SUM(C3:C58)</f>
-        <v>0</v>
+        <f t="shared" ref="C1:F1" si="0">SUM(C3:C58)</f>
+        <v>-2000</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>-2000</v>
+        <v>-2600</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
@@ -14495,17 +14042,13 @@
         <f t="shared" si="0"/>
         <v>-2600</v>
       </c>
-      <c r="G1" s="2">
-        <f t="shared" si="0"/>
-        <v>-2600</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -14519,17 +14062,16 @@
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
+        <v>-1400</v>
+      </c>
       <c r="D3" s="2">
-        <v>-1400</v>
+        <v>-2000</v>
       </c>
       <c r="E3" s="2">
         <v>-2000</v>
@@ -14537,15 +14079,14 @@
       <c r="F3" s="2">
         <v>-2000</v>
       </c>
-      <c r="G3" s="2">
-        <v>-2000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="C4" s="2">
+        <v>-600</v>
+      </c>
       <c r="D4" s="2">
         <v>-600</v>
       </c>
@@ -14555,2774 +14096,2376 @@
       <c r="F4" s="2">
         <v>-600</v>
       </c>
-      <c r="G4" s="2">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-    </row>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-    </row>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-    </row>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-    </row>
-    <row r="53" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-    </row>
-    <row r="54" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-    </row>
-    <row r="55" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-    </row>
-    <row r="56" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-    </row>
-    <row r="57" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-    </row>
-    <row r="58" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-    </row>
-    <row r="59" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-    </row>
-    <row r="60" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-    </row>
-    <row r="61" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-    </row>
-    <row r="62" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-    </row>
-    <row r="63" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-    </row>
-    <row r="64" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-    </row>
-    <row r="65" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-    </row>
-    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-    </row>
-    <row r="67" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-    </row>
-    <row r="68" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-    </row>
-    <row r="69" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-    </row>
-    <row r="70" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-    </row>
-    <row r="71" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-    </row>
-    <row r="72" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-    </row>
-    <row r="73" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-    </row>
-    <row r="74" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-    </row>
-    <row r="75" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-    </row>
-    <row r="76" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-    </row>
-    <row r="77" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-    </row>
-    <row r="78" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-    </row>
-    <row r="79" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-    </row>
-    <row r="80" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-    </row>
-    <row r="81" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-    </row>
-    <row r="82" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-    </row>
-    <row r="83" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-    </row>
-    <row r="84" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-    </row>
-    <row r="85" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-    </row>
-    <row r="86" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-    </row>
-    <row r="87" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-    </row>
-    <row r="88" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-    </row>
-    <row r="89" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-    </row>
-    <row r="90" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-    </row>
-    <row r="91" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-    </row>
-    <row r="92" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-    </row>
-    <row r="93" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-    </row>
-    <row r="94" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-    </row>
-    <row r="95" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-    </row>
-    <row r="96" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-    </row>
-    <row r="97" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-    </row>
-    <row r="98" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-    </row>
-    <row r="99" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-    </row>
-    <row r="100" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-    </row>
-    <row r="101" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-    </row>
-    <row r="102" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-    </row>
-    <row r="103" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-    </row>
-    <row r="104" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-    </row>
-    <row r="105" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-    </row>
-    <row r="106" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-    </row>
-    <row r="107" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-    </row>
-    <row r="108" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-    </row>
-    <row r="109" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-    </row>
-    <row r="110" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-    </row>
-    <row r="111" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-    </row>
-    <row r="112" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-    </row>
-    <row r="113" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-    </row>
-    <row r="114" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-    </row>
-    <row r="115" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-    </row>
-    <row r="116" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-    </row>
-    <row r="117" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-    </row>
-    <row r="118" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-    </row>
-    <row r="119" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-    </row>
-    <row r="120" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-    </row>
-    <row r="121" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-    </row>
-    <row r="122" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
-      <c r="G122" s="2"/>
-    </row>
-    <row r="123" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
-    </row>
-    <row r="124" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
-    </row>
-    <row r="125" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-    </row>
-    <row r="126" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
-      <c r="G126" s="2"/>
-    </row>
-    <row r="127" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
-      <c r="G127" s="2"/>
-    </row>
-    <row r="128" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
-    </row>
-    <row r="129" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
-      <c r="G129" s="2"/>
-    </row>
-    <row r="130" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
-      <c r="G130" s="2"/>
-    </row>
-    <row r="131" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-    </row>
-    <row r="132" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-    </row>
-    <row r="133" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-    </row>
-    <row r="134" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
-    </row>
-    <row r="135" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-    </row>
-    <row r="136" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
-      <c r="G136" s="2"/>
-    </row>
-    <row r="137" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
-      <c r="G137" s="2"/>
-    </row>
-    <row r="138" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
-    </row>
-    <row r="139" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
-      <c r="G139" s="2"/>
-    </row>
-    <row r="140" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-    </row>
-    <row r="141" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
-      <c r="G141" s="2"/>
-    </row>
-    <row r="142" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
-      <c r="G142" s="2"/>
-    </row>
-    <row r="143" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
-      <c r="G143" s="2"/>
-    </row>
-    <row r="144" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
-      <c r="G144" s="2"/>
-    </row>
-    <row r="145" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
-      <c r="G145" s="2"/>
-    </row>
-    <row r="146" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
-      <c r="G146" s="2"/>
-    </row>
-    <row r="147" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
-      <c r="G147" s="2"/>
-    </row>
-    <row r="148" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
-      <c r="G148" s="2"/>
-    </row>
-    <row r="149" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
-      <c r="G149" s="2"/>
-    </row>
-    <row r="150" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
-      <c r="G150" s="2"/>
-    </row>
-    <row r="151" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
-      <c r="G151" s="2"/>
-    </row>
-    <row r="152" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
-      <c r="G152" s="2"/>
-    </row>
-    <row r="153" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
-      <c r="G153" s="2"/>
-    </row>
-    <row r="154" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
-      <c r="G154" s="2"/>
-    </row>
-    <row r="155" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
-      <c r="G155" s="2"/>
-    </row>
-    <row r="156" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
-      <c r="G156" s="2"/>
-    </row>
-    <row r="157" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
-      <c r="G157" s="2"/>
-    </row>
-    <row r="158" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
-      <c r="G158" s="2"/>
-    </row>
-    <row r="159" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
-      <c r="G159" s="2"/>
-    </row>
-    <row r="160" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
-      <c r="G160" s="2"/>
-    </row>
-    <row r="161" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
-      <c r="G161" s="2"/>
-    </row>
-    <row r="162" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
-      <c r="G162" s="2"/>
-    </row>
-    <row r="163" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
-      <c r="G163" s="2"/>
-    </row>
-    <row r="164" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
-      <c r="G164" s="2"/>
-    </row>
-    <row r="165" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
-      <c r="G165" s="2"/>
-    </row>
-    <row r="166" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
-      <c r="G166" s="2"/>
-    </row>
-    <row r="167" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
-      <c r="G167" s="2"/>
-    </row>
-    <row r="168" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
-      <c r="G168" s="2"/>
-    </row>
-    <row r="169" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
-      <c r="G169" s="2"/>
-    </row>
-    <row r="170" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
-      <c r="G170" s="2"/>
-    </row>
-    <row r="171" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
-      <c r="G171" s="2"/>
-    </row>
-    <row r="172" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
-      <c r="G172" s="2"/>
-    </row>
-    <row r="173" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
-      <c r="G173" s="2"/>
-    </row>
-    <row r="174" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
-      <c r="G174" s="2"/>
-    </row>
-    <row r="175" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
-      <c r="G175" s="2"/>
-    </row>
-    <row r="176" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
-      <c r="G176" s="2"/>
-    </row>
-    <row r="177" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
-      <c r="G177" s="2"/>
-    </row>
-    <row r="178" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
-      <c r="G178" s="2"/>
-    </row>
-    <row r="179" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
-      <c r="G179" s="2"/>
-    </row>
-    <row r="180" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
-      <c r="G180" s="2"/>
-    </row>
-    <row r="181" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
-      <c r="G181" s="2"/>
-    </row>
-    <row r="182" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
-      <c r="G182" s="2"/>
-    </row>
-    <row r="183" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
-      <c r="G183" s="2"/>
-    </row>
-    <row r="184" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
-      <c r="G184" s="2"/>
-    </row>
-    <row r="185" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
-      <c r="G185" s="2"/>
-    </row>
-    <row r="186" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
-      <c r="G186" s="2"/>
-    </row>
-    <row r="187" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
-      <c r="G187" s="2"/>
-    </row>
-    <row r="188" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
-      <c r="G188" s="2"/>
-    </row>
-    <row r="189" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
-      <c r="G189" s="2"/>
-    </row>
-    <row r="190" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
-      <c r="G190" s="2"/>
-    </row>
-    <row r="191" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
-      <c r="G191" s="2"/>
-    </row>
-    <row r="192" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
-      <c r="G192" s="2"/>
-    </row>
-    <row r="193" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
-      <c r="G193" s="2"/>
-    </row>
-    <row r="194" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
-      <c r="G194" s="2"/>
-    </row>
-    <row r="195" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
-      <c r="G195" s="2"/>
-    </row>
-    <row r="196" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
-      <c r="G196" s="2"/>
-    </row>
-    <row r="197" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
-      <c r="G197" s="2"/>
-    </row>
-    <row r="198" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
       <c r="F198" s="2"/>
-      <c r="G198" s="2"/>
-    </row>
-    <row r="199" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
-      <c r="G199" s="2"/>
-    </row>
-    <row r="200" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
-      <c r="G200" s="2"/>
-    </row>
-    <row r="201" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
-      <c r="G201" s="2"/>
-    </row>
-    <row r="202" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
-      <c r="G202" s="2"/>
-    </row>
-    <row r="203" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
       <c r="E203" s="2"/>
       <c r="F203" s="2"/>
-      <c r="G203" s="2"/>
-    </row>
-    <row r="204" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
       <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
-    </row>
-    <row r="205" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-    </row>
-    <row r="206" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="206" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
-      <c r="G206" s="2"/>
-    </row>
-    <row r="207" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
-      <c r="G207" s="2"/>
-    </row>
-    <row r="208" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="208" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
-      <c r="G208" s="2"/>
-    </row>
-    <row r="209" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="209" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
-      <c r="G209" s="2"/>
-    </row>
-    <row r="210" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="210" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
-      <c r="G210" s="2"/>
-    </row>
-    <row r="211" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="211" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
-      <c r="G211" s="2"/>
-    </row>
-    <row r="212" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="212" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
-      <c r="G212" s="2"/>
-    </row>
-    <row r="213" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="213" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
-      <c r="G213" s="2"/>
-    </row>
-    <row r="214" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="214" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
-      <c r="G214" s="2"/>
-    </row>
-    <row r="215" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
-      <c r="G215" s="2"/>
-    </row>
-    <row r="216" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="216" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C216" s="2"/>
       <c r="D216" s="2"/>
       <c r="E216" s="2"/>
       <c r="F216" s="2"/>
-      <c r="G216" s="2"/>
-    </row>
-    <row r="217" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="217" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C217" s="2"/>
       <c r="D217" s="2"/>
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
-      <c r="G217" s="2"/>
-    </row>
-    <row r="218" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="218" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
-      <c r="G218" s="2"/>
-    </row>
-    <row r="219" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="219" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C219" s="2"/>
       <c r="D219" s="2"/>
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
-      <c r="G219" s="2"/>
-    </row>
-    <row r="220" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
       <c r="E220" s="2"/>
       <c r="F220" s="2"/>
-      <c r="G220" s="2"/>
-    </row>
-    <row r="221" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="221" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>
       <c r="E221" s="2"/>
       <c r="F221" s="2"/>
-      <c r="G221" s="2"/>
-    </row>
-    <row r="222" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="222" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
       <c r="E222" s="2"/>
       <c r="F222" s="2"/>
-      <c r="G222" s="2"/>
-    </row>
-    <row r="223" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="223" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C223" s="2"/>
       <c r="D223" s="2"/>
       <c r="E223" s="2"/>
       <c r="F223" s="2"/>
-      <c r="G223" s="2"/>
-    </row>
-    <row r="224" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="224" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C224" s="2"/>
       <c r="D224" s="2"/>
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
-      <c r="G224" s="2"/>
-    </row>
-    <row r="225" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C225" s="2"/>
       <c r="D225" s="2"/>
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
-      <c r="G225" s="2"/>
-    </row>
-    <row r="226" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="226" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C226" s="2"/>
       <c r="D226" s="2"/>
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
-      <c r="G226" s="2"/>
-    </row>
-    <row r="227" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="227" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C227" s="2"/>
       <c r="D227" s="2"/>
       <c r="E227" s="2"/>
       <c r="F227" s="2"/>
-      <c r="G227" s="2"/>
-    </row>
-    <row r="228" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="228" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
       <c r="E228" s="2"/>
       <c r="F228" s="2"/>
-      <c r="G228" s="2"/>
-    </row>
-    <row r="229" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
-      <c r="G229" s="2"/>
-    </row>
-    <row r="230" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
-      <c r="G230" s="2"/>
-    </row>
-    <row r="231" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="231" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C231" s="2"/>
       <c r="D231" s="2"/>
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
-      <c r="G231" s="2"/>
-    </row>
-    <row r="232" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="232" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C232" s="2"/>
       <c r="D232" s="2"/>
       <c r="E232" s="2"/>
       <c r="F232" s="2"/>
-      <c r="G232" s="2"/>
-    </row>
-    <row r="233" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="233" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C233" s="2"/>
       <c r="D233" s="2"/>
       <c r="E233" s="2"/>
       <c r="F233" s="2"/>
-      <c r="G233" s="2"/>
-    </row>
-    <row r="234" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="234" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C234" s="2"/>
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
-      <c r="G234" s="2"/>
-    </row>
-    <row r="235" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="235" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C235" s="2"/>
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
-      <c r="G235" s="2"/>
-    </row>
-    <row r="236" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="236" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C236" s="2"/>
       <c r="D236" s="2"/>
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
-      <c r="G236" s="2"/>
-    </row>
-    <row r="237" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="237" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C237" s="2"/>
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
-      <c r="G237" s="2"/>
-    </row>
-    <row r="238" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="238" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C238" s="2"/>
       <c r="D238" s="2"/>
       <c r="E238" s="2"/>
       <c r="F238" s="2"/>
-      <c r="G238" s="2"/>
-    </row>
-    <row r="239" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="239" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
-      <c r="G239" s="2"/>
-    </row>
-    <row r="240" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="240" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C240" s="2"/>
       <c r="D240" s="2"/>
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
-      <c r="G240" s="2"/>
-    </row>
-    <row r="241" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
       <c r="E241" s="2"/>
       <c r="F241" s="2"/>
-      <c r="G241" s="2"/>
-    </row>
-    <row r="242" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="242" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
       <c r="E242" s="2"/>
       <c r="F242" s="2"/>
-      <c r="G242" s="2"/>
-    </row>
-    <row r="243" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="243" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
       <c r="E243" s="2"/>
       <c r="F243" s="2"/>
-      <c r="G243" s="2"/>
-    </row>
-    <row r="244" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="244" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C244" s="2"/>
       <c r="D244" s="2"/>
       <c r="E244" s="2"/>
       <c r="F244" s="2"/>
-      <c r="G244" s="2"/>
-    </row>
-    <row r="245" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="245" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C245" s="2"/>
       <c r="D245" s="2"/>
       <c r="E245" s="2"/>
       <c r="F245" s="2"/>
-      <c r="G245" s="2"/>
-    </row>
-    <row r="246" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="246" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C246" s="2"/>
       <c r="D246" s="2"/>
       <c r="E246" s="2"/>
       <c r="F246" s="2"/>
-      <c r="G246" s="2"/>
-    </row>
-    <row r="247" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="247" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C247" s="2"/>
       <c r="D247" s="2"/>
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
-      <c r="G247" s="2"/>
-    </row>
-    <row r="248" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="248" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C248" s="2"/>
       <c r="D248" s="2"/>
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
-      <c r="G248" s="2"/>
-    </row>
-    <row r="249" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="249" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
       <c r="E249" s="2"/>
       <c r="F249" s="2"/>
-      <c r="G249" s="2"/>
-    </row>
-    <row r="250" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="250" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C250" s="2"/>
       <c r="D250" s="2"/>
       <c r="E250" s="2"/>
       <c r="F250" s="2"/>
-      <c r="G250" s="2"/>
-    </row>
-    <row r="251" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="251" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C251" s="2"/>
       <c r="D251" s="2"/>
       <c r="E251" s="2"/>
       <c r="F251" s="2"/>
-      <c r="G251" s="2"/>
-    </row>
-    <row r="252" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="252" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C252" s="2"/>
       <c r="D252" s="2"/>
       <c r="E252" s="2"/>
       <c r="F252" s="2"/>
-      <c r="G252" s="2"/>
-    </row>
-    <row r="253" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="253" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C253" s="2"/>
       <c r="D253" s="2"/>
       <c r="E253" s="2"/>
       <c r="F253" s="2"/>
-      <c r="G253" s="2"/>
-    </row>
-    <row r="254" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="254" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C254" s="2"/>
       <c r="D254" s="2"/>
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
-      <c r="G254" s="2"/>
-    </row>
-    <row r="255" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="255" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C255" s="2"/>
       <c r="D255" s="2"/>
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
-      <c r="G255" s="2"/>
-    </row>
-    <row r="256" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="256" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C256" s="2"/>
       <c r="D256" s="2"/>
       <c r="E256" s="2"/>
       <c r="F256" s="2"/>
-      <c r="G256" s="2"/>
-    </row>
-    <row r="257" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="257" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C257" s="2"/>
       <c r="D257" s="2"/>
       <c r="E257" s="2"/>
       <c r="F257" s="2"/>
-      <c r="G257" s="2"/>
-    </row>
-    <row r="258" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="258" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C258" s="2"/>
       <c r="D258" s="2"/>
       <c r="E258" s="2"/>
       <c r="F258" s="2"/>
-      <c r="G258" s="2"/>
-    </row>
-    <row r="259" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C259" s="2"/>
       <c r="D259" s="2"/>
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
-      <c r="G259" s="2"/>
-    </row>
-    <row r="260" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="260" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
-      <c r="G260" s="2"/>
-    </row>
-    <row r="261" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="261" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
       <c r="E261" s="2"/>
       <c r="F261" s="2"/>
-      <c r="G261" s="2"/>
-    </row>
-    <row r="262" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="262" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
       <c r="E262" s="2"/>
       <c r="F262" s="2"/>
-      <c r="G262" s="2"/>
-    </row>
-    <row r="263" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="263" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
       <c r="E263" s="2"/>
       <c r="F263" s="2"/>
-      <c r="G263" s="2"/>
-    </row>
-    <row r="264" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="264" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
       <c r="E264" s="2"/>
       <c r="F264" s="2"/>
-      <c r="G264" s="2"/>
-    </row>
-    <row r="265" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="265" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
-      <c r="G265" s="2"/>
-    </row>
-    <row r="266" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="266" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C266" s="2"/>
       <c r="D266" s="2"/>
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
-      <c r="G266" s="2"/>
-    </row>
-    <row r="267" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="267" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C267" s="2"/>
       <c r="D267" s="2"/>
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
-      <c r="G267" s="2"/>
-    </row>
-    <row r="268" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="268" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C268" s="2"/>
       <c r="D268" s="2"/>
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
-      <c r="G268" s="2"/>
-    </row>
-    <row r="269" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="269" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
-      <c r="G269" s="2"/>
-    </row>
-    <row r="270" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="270" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C270" s="2"/>
       <c r="D270" s="2"/>
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
-      <c r="G270" s="2"/>
-    </row>
-    <row r="271" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="271" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C271" s="2"/>
       <c r="D271" s="2"/>
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
-      <c r="G271" s="2"/>
-    </row>
-    <row r="272" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="272" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
-      <c r="G272" s="2"/>
-    </row>
-    <row r="273" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="273" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
       <c r="E273" s="2"/>
       <c r="F273" s="2"/>
-      <c r="G273" s="2"/>
-    </row>
-    <row r="274" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="274" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C274" s="2"/>
       <c r="D274" s="2"/>
       <c r="E274" s="2"/>
       <c r="F274" s="2"/>
-      <c r="G274" s="2"/>
-    </row>
-    <row r="275" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="275" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
-      <c r="G275" s="2"/>
-    </row>
-    <row r="276" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="276" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
-      <c r="G276" s="2"/>
-    </row>
-    <row r="277" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="277" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C277" s="2"/>
       <c r="D277" s="2"/>
       <c r="E277" s="2"/>
       <c r="F277" s="2"/>
-      <c r="G277" s="2"/>
-    </row>
-    <row r="278" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="278" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C278" s="2"/>
       <c r="D278" s="2"/>
       <c r="E278" s="2"/>
       <c r="F278" s="2"/>
-      <c r="G278" s="2"/>
-    </row>
-    <row r="279" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="279" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C279" s="2"/>
       <c r="D279" s="2"/>
       <c r="E279" s="2"/>
       <c r="F279" s="2"/>
-      <c r="G279" s="2"/>
-    </row>
-    <row r="280" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="280" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C280" s="2"/>
       <c r="D280" s="2"/>
       <c r="E280" s="2"/>
       <c r="F280" s="2"/>
-      <c r="G280" s="2"/>
-    </row>
-    <row r="281" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="281" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C281" s="2"/>
       <c r="D281" s="2"/>
       <c r="E281" s="2"/>
       <c r="F281" s="2"/>
-      <c r="G281" s="2"/>
-    </row>
-    <row r="282" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="282" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C282" s="2"/>
       <c r="D282" s="2"/>
       <c r="E282" s="2"/>
       <c r="F282" s="2"/>
-      <c r="G282" s="2"/>
-    </row>
-    <row r="283" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="283" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C283" s="2"/>
       <c r="D283" s="2"/>
       <c r="E283" s="2"/>
       <c r="F283" s="2"/>
-      <c r="G283" s="2"/>
-    </row>
-    <row r="284" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="284" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C284" s="2"/>
       <c r="D284" s="2"/>
       <c r="E284" s="2"/>
       <c r="F284" s="2"/>
-      <c r="G284" s="2"/>
-    </row>
-    <row r="285" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="285" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C285" s="2"/>
       <c r="D285" s="2"/>
       <c r="E285" s="2"/>
       <c r="F285" s="2"/>
-      <c r="G285" s="2"/>
-    </row>
-    <row r="286" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="286" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C286" s="2"/>
       <c r="D286" s="2"/>
       <c r="E286" s="2"/>
       <c r="F286" s="2"/>
-      <c r="G286" s="2"/>
-    </row>
-    <row r="287" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="287" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C287" s="2"/>
       <c r="D287" s="2"/>
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
-      <c r="G287" s="2"/>
-    </row>
-    <row r="288" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="288" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C288" s="2"/>
       <c r="D288" s="2"/>
       <c r="E288" s="2"/>
       <c r="F288" s="2"/>
-      <c r="G288" s="2"/>
-    </row>
-    <row r="289" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="289" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C289" s="2"/>
       <c r="D289" s="2"/>
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
-      <c r="G289" s="2"/>
-    </row>
-    <row r="290" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="290" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C290" s="2"/>
       <c r="D290" s="2"/>
       <c r="E290" s="2"/>
       <c r="F290" s="2"/>
-      <c r="G290" s="2"/>
-    </row>
-    <row r="291" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="291" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C291" s="2"/>
       <c r="D291" s="2"/>
       <c r="E291" s="2"/>
       <c r="F291" s="2"/>
-      <c r="G291" s="2"/>
-    </row>
-    <row r="292" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="292" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C292" s="2"/>
       <c r="D292" s="2"/>
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
-      <c r="G292" s="2"/>
-    </row>
-    <row r="293" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="293" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C293" s="2"/>
       <c r="D293" s="2"/>
       <c r="E293" s="2"/>
       <c r="F293" s="2"/>
-      <c r="G293" s="2"/>
-    </row>
-    <row r="294" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="294" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C294" s="2"/>
       <c r="D294" s="2"/>
       <c r="E294" s="2"/>
       <c r="F294" s="2"/>
-      <c r="G294" s="2"/>
-    </row>
-    <row r="295" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="295" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C295" s="2"/>
       <c r="D295" s="2"/>
       <c r="E295" s="2"/>
       <c r="F295" s="2"/>
-      <c r="G295" s="2"/>
-    </row>
-    <row r="296" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="296" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C296" s="2"/>
       <c r="D296" s="2"/>
       <c r="E296" s="2"/>
       <c r="F296" s="2"/>
-      <c r="G296" s="2"/>
-    </row>
-    <row r="297" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="297" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C297" s="2"/>
       <c r="D297" s="2"/>
       <c r="E297" s="2"/>
       <c r="F297" s="2"/>
-      <c r="G297" s="2"/>
-    </row>
-    <row r="298" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="298" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C298" s="2"/>
       <c r="D298" s="2"/>
       <c r="E298" s="2"/>
       <c r="F298" s="2"/>
-      <c r="G298" s="2"/>
-    </row>
-    <row r="299" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="299" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C299" s="2"/>
       <c r="D299" s="2"/>
       <c r="E299" s="2"/>
       <c r="F299" s="2"/>
-      <c r="G299" s="2"/>
-    </row>
-    <row r="300" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="300" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C300" s="2"/>
       <c r="D300" s="2"/>
       <c r="E300" s="2"/>
       <c r="F300" s="2"/>
-      <c r="G300" s="2"/>
-    </row>
-    <row r="301" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="301" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C301" s="2"/>
       <c r="D301" s="2"/>
       <c r="E301" s="2"/>
       <c r="F301" s="2"/>
-      <c r="G301" s="2"/>
-    </row>
-    <row r="302" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="302" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C302" s="2"/>
       <c r="D302" s="2"/>
       <c r="E302" s="2"/>
       <c r="F302" s="2"/>
-      <c r="G302" s="2"/>
-    </row>
-    <row r="303" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="303" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C303" s="2"/>
       <c r="D303" s="2"/>
       <c r="E303" s="2"/>
       <c r="F303" s="2"/>
-      <c r="G303" s="2"/>
-    </row>
-    <row r="304" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="304" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C304" s="2"/>
       <c r="D304" s="2"/>
       <c r="E304" s="2"/>
       <c r="F304" s="2"/>
-      <c r="G304" s="2"/>
-    </row>
-    <row r="305" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="305" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C305" s="2"/>
       <c r="D305" s="2"/>
       <c r="E305" s="2"/>
       <c r="F305" s="2"/>
-      <c r="G305" s="2"/>
-    </row>
-    <row r="306" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="306" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C306" s="2"/>
       <c r="D306" s="2"/>
       <c r="E306" s="2"/>
       <c r="F306" s="2"/>
-      <c r="G306" s="2"/>
-    </row>
-    <row r="307" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="307" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C307" s="2"/>
       <c r="D307" s="2"/>
       <c r="E307" s="2"/>
       <c r="F307" s="2"/>
-      <c r="G307" s="2"/>
-    </row>
-    <row r="308" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="308" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C308" s="2"/>
       <c r="D308" s="2"/>
       <c r="E308" s="2"/>
       <c r="F308" s="2"/>
-      <c r="G308" s="2"/>
-    </row>
-    <row r="309" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="309" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C309" s="2"/>
       <c r="D309" s="2"/>
       <c r="E309" s="2"/>
       <c r="F309" s="2"/>
-      <c r="G309" s="2"/>
-    </row>
-    <row r="310" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="310" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C310" s="2"/>
       <c r="D310" s="2"/>
       <c r="E310" s="2"/>
       <c r="F310" s="2"/>
-      <c r="G310" s="2"/>
-    </row>
-    <row r="311" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="311" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C311" s="2"/>
       <c r="D311" s="2"/>
       <c r="E311" s="2"/>
       <c r="F311" s="2"/>
-      <c r="G311" s="2"/>
-    </row>
-    <row r="312" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="312" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C312" s="2"/>
       <c r="D312" s="2"/>
       <c r="E312" s="2"/>
       <c r="F312" s="2"/>
-      <c r="G312" s="2"/>
-    </row>
-    <row r="313" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="313" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C313" s="2"/>
       <c r="D313" s="2"/>
       <c r="E313" s="2"/>
       <c r="F313" s="2"/>
-      <c r="G313" s="2"/>
-    </row>
-    <row r="314" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="314" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C314" s="2"/>
       <c r="D314" s="2"/>
       <c r="E314" s="2"/>
       <c r="F314" s="2"/>
-      <c r="G314" s="2"/>
-    </row>
-    <row r="315" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="315" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C315" s="2"/>
       <c r="D315" s="2"/>
       <c r="E315" s="2"/>
       <c r="F315" s="2"/>
-      <c r="G315" s="2"/>
-    </row>
-    <row r="316" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="316" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C316" s="2"/>
       <c r="D316" s="2"/>
       <c r="E316" s="2"/>
       <c r="F316" s="2"/>
-      <c r="G316" s="2"/>
-    </row>
-    <row r="317" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="317" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C317" s="2"/>
       <c r="D317" s="2"/>
       <c r="E317" s="2"/>
       <c r="F317" s="2"/>
-      <c r="G317" s="2"/>
-    </row>
-    <row r="318" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="318" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C318" s="2"/>
       <c r="D318" s="2"/>
       <c r="E318" s="2"/>
       <c r="F318" s="2"/>
-      <c r="G318" s="2"/>
-    </row>
-    <row r="319" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="319" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C319" s="2"/>
       <c r="D319" s="2"/>
       <c r="E319" s="2"/>
       <c r="F319" s="2"/>
-      <c r="G319" s="2"/>
-    </row>
-    <row r="320" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="320" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C320" s="2"/>
       <c r="D320" s="2"/>
       <c r="E320" s="2"/>
       <c r="F320" s="2"/>
-      <c r="G320" s="2"/>
-    </row>
-    <row r="321" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="321" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C321" s="2"/>
       <c r="D321" s="2"/>
       <c r="E321" s="2"/>
       <c r="F321" s="2"/>
-      <c r="G321" s="2"/>
-    </row>
-    <row r="322" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="322" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C322" s="2"/>
       <c r="D322" s="2"/>
       <c r="E322" s="2"/>
       <c r="F322" s="2"/>
-      <c r="G322" s="2"/>
-    </row>
-    <row r="323" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="323" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C323" s="2"/>
       <c r="D323" s="2"/>
       <c r="E323" s="2"/>
       <c r="F323" s="2"/>
-      <c r="G323" s="2"/>
-    </row>
-    <row r="324" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="324" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C324" s="2"/>
       <c r="D324" s="2"/>
       <c r="E324" s="2"/>
       <c r="F324" s="2"/>
-      <c r="G324" s="2"/>
-    </row>
-    <row r="325" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="325" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C325" s="2"/>
       <c r="D325" s="2"/>
       <c r="E325" s="2"/>
       <c r="F325" s="2"/>
-      <c r="G325" s="2"/>
-    </row>
-    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="326" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C326" s="2"/>
       <c r="D326" s="2"/>
       <c r="E326" s="2"/>
       <c r="F326" s="2"/>
-      <c r="G326" s="2"/>
-    </row>
-    <row r="327" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="327" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C327" s="2"/>
       <c r="D327" s="2"/>
       <c r="E327" s="2"/>
       <c r="F327" s="2"/>
-      <c r="G327" s="2"/>
-    </row>
-    <row r="328" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="328" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C328" s="2"/>
       <c r="D328" s="2"/>
       <c r="E328" s="2"/>
       <c r="F328" s="2"/>
-      <c r="G328" s="2"/>
-    </row>
-    <row r="329" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="329" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C329" s="2"/>
       <c r="D329" s="2"/>
       <c r="E329" s="2"/>
       <c r="F329" s="2"/>
-      <c r="G329" s="2"/>
-    </row>
-    <row r="330" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="330" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C330" s="2"/>
       <c r="D330" s="2"/>
       <c r="E330" s="2"/>
       <c r="F330" s="2"/>
-      <c r="G330" s="2"/>
-    </row>
-    <row r="331" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="331" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C331" s="2"/>
       <c r="D331" s="2"/>
       <c r="E331" s="2"/>
       <c r="F331" s="2"/>
-      <c r="G331" s="2"/>
-    </row>
-    <row r="332" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="332" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C332" s="2"/>
       <c r="D332" s="2"/>
       <c r="E332" s="2"/>
       <c r="F332" s="2"/>
-      <c r="G332" s="2"/>
-    </row>
-    <row r="333" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="333" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C333" s="2"/>
       <c r="D333" s="2"/>
       <c r="E333" s="2"/>
       <c r="F333" s="2"/>
-      <c r="G333" s="2"/>
-    </row>
-    <row r="334" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="334" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C334" s="2"/>
       <c r="D334" s="2"/>
       <c r="E334" s="2"/>
       <c r="F334" s="2"/>
-      <c r="G334" s="2"/>
-    </row>
-    <row r="335" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="335" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C335" s="2"/>
       <c r="D335" s="2"/>
       <c r="E335" s="2"/>
       <c r="F335" s="2"/>
-      <c r="G335" s="2"/>
-    </row>
-    <row r="336" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="336" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C336" s="2"/>
       <c r="D336" s="2"/>
       <c r="E336" s="2"/>
       <c r="F336" s="2"/>
-      <c r="G336" s="2"/>
-    </row>
-    <row r="337" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="337" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C337" s="2"/>
       <c r="D337" s="2"/>
       <c r="E337" s="2"/>
       <c r="F337" s="2"/>
-      <c r="G337" s="2"/>
-    </row>
-    <row r="338" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="338" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C338" s="2"/>
       <c r="D338" s="2"/>
       <c r="E338" s="2"/>
       <c r="F338" s="2"/>
-      <c r="G338" s="2"/>
-    </row>
-    <row r="339" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="339" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C339" s="2"/>
       <c r="D339" s="2"/>
       <c r="E339" s="2"/>
       <c r="F339" s="2"/>
-      <c r="G339" s="2"/>
-    </row>
-    <row r="340" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="340" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C340" s="2"/>
       <c r="D340" s="2"/>
       <c r="E340" s="2"/>
       <c r="F340" s="2"/>
-      <c r="G340" s="2"/>
-    </row>
-    <row r="341" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="341" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C341" s="2"/>
       <c r="D341" s="2"/>
       <c r="E341" s="2"/>
       <c r="F341" s="2"/>
-      <c r="G341" s="2"/>
-    </row>
-    <row r="342" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="342" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C342" s="2"/>
       <c r="D342" s="2"/>
       <c r="E342" s="2"/>
       <c r="F342" s="2"/>
-      <c r="G342" s="2"/>
-    </row>
-    <row r="343" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="343" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C343" s="2"/>
       <c r="D343" s="2"/>
       <c r="E343" s="2"/>
       <c r="F343" s="2"/>
-      <c r="G343" s="2"/>
-    </row>
-    <row r="344" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="344" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C344" s="2"/>
       <c r="D344" s="2"/>
       <c r="E344" s="2"/>
       <c r="F344" s="2"/>
-      <c r="G344" s="2"/>
-    </row>
-    <row r="345" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="345" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C345" s="2"/>
       <c r="D345" s="2"/>
       <c r="E345" s="2"/>
       <c r="F345" s="2"/>
-      <c r="G345" s="2"/>
-    </row>
-    <row r="346" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="346" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C346" s="2"/>
       <c r="D346" s="2"/>
       <c r="E346" s="2"/>
       <c r="F346" s="2"/>
-      <c r="G346" s="2"/>
-    </row>
-    <row r="347" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="347" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C347" s="2"/>
       <c r="D347" s="2"/>
       <c r="E347" s="2"/>
       <c r="F347" s="2"/>
-      <c r="G347" s="2"/>
-    </row>
-    <row r="348" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="348" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C348" s="2"/>
       <c r="D348" s="2"/>
       <c r="E348" s="2"/>
       <c r="F348" s="2"/>
-      <c r="G348" s="2"/>
-    </row>
-    <row r="349" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="349" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C349" s="2"/>
       <c r="D349" s="2"/>
       <c r="E349" s="2"/>
       <c r="F349" s="2"/>
-      <c r="G349" s="2"/>
-    </row>
-    <row r="350" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="350" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C350" s="2"/>
       <c r="D350" s="2"/>
       <c r="E350" s="2"/>
       <c r="F350" s="2"/>
-      <c r="G350" s="2"/>
-    </row>
-    <row r="351" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="351" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C351" s="2"/>
       <c r="D351" s="2"/>
       <c r="E351" s="2"/>
       <c r="F351" s="2"/>
-      <c r="G351" s="2"/>
-    </row>
-    <row r="352" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="352" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C352" s="2"/>
       <c r="D352" s="2"/>
       <c r="E352" s="2"/>
       <c r="F352" s="2"/>
-      <c r="G352" s="2"/>
-    </row>
-    <row r="353" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="353" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C353" s="2"/>
       <c r="D353" s="2"/>
       <c r="E353" s="2"/>
       <c r="F353" s="2"/>
-      <c r="G353" s="2"/>
-    </row>
-    <row r="354" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="354" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C354" s="2"/>
       <c r="D354" s="2"/>
       <c r="E354" s="2"/>
       <c r="F354" s="2"/>
-      <c r="G354" s="2"/>
-    </row>
-    <row r="355" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="355" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C355" s="2"/>
       <c r="D355" s="2"/>
       <c r="E355" s="2"/>
       <c r="F355" s="2"/>
-      <c r="G355" s="2"/>
-    </row>
-    <row r="356" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="356" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C356" s="2"/>
       <c r="D356" s="2"/>
       <c r="E356" s="2"/>
       <c r="F356" s="2"/>
-      <c r="G356" s="2"/>
-    </row>
-    <row r="357" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="357" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C357" s="2"/>
       <c r="D357" s="2"/>
       <c r="E357" s="2"/>
       <c r="F357" s="2"/>
-      <c r="G357" s="2"/>
-    </row>
-    <row r="358" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="358" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C358" s="2"/>
       <c r="D358" s="2"/>
       <c r="E358" s="2"/>
       <c r="F358" s="2"/>
-      <c r="G358" s="2"/>
-    </row>
-    <row r="359" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="359" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C359" s="2"/>
       <c r="D359" s="2"/>
       <c r="E359" s="2"/>
       <c r="F359" s="2"/>
-      <c r="G359" s="2"/>
-    </row>
-    <row r="360" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="360" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C360" s="2"/>
       <c r="D360" s="2"/>
       <c r="E360" s="2"/>
       <c r="F360" s="2"/>
-      <c r="G360" s="2"/>
-    </row>
-    <row r="361" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="361" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C361" s="2"/>
       <c r="D361" s="2"/>
       <c r="E361" s="2"/>
       <c r="F361" s="2"/>
-      <c r="G361" s="2"/>
-    </row>
-    <row r="362" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="362" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C362" s="2"/>
       <c r="D362" s="2"/>
       <c r="E362" s="2"/>
       <c r="F362" s="2"/>
-      <c r="G362" s="2"/>
-    </row>
-    <row r="363" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="363" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C363" s="2"/>
       <c r="D363" s="2"/>
       <c r="E363" s="2"/>
       <c r="F363" s="2"/>
-      <c r="G363" s="2"/>
-    </row>
-    <row r="364" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="364" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C364" s="2"/>
       <c r="D364" s="2"/>
       <c r="E364" s="2"/>
       <c r="F364" s="2"/>
-      <c r="G364" s="2"/>
-    </row>
-    <row r="365" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="365" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C365" s="2"/>
       <c r="D365" s="2"/>
       <c r="E365" s="2"/>
       <c r="F365" s="2"/>
-      <c r="G365" s="2"/>
-    </row>
-    <row r="366" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="366" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C366" s="2"/>
       <c r="D366" s="2"/>
       <c r="E366" s="2"/>
       <c r="F366" s="2"/>
-      <c r="G366" s="2"/>
-    </row>
-    <row r="367" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="367" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C367" s="2"/>
       <c r="D367" s="2"/>
       <c r="E367" s="2"/>
       <c r="F367" s="2"/>
-      <c r="G367" s="2"/>
-    </row>
-    <row r="368" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="368" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C368" s="2"/>
       <c r="D368" s="2"/>
       <c r="E368" s="2"/>
       <c r="F368" s="2"/>
-      <c r="G368" s="2"/>
-    </row>
-    <row r="369" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="369" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C369" s="2"/>
       <c r="D369" s="2"/>
       <c r="E369" s="2"/>
       <c r="F369" s="2"/>
-      <c r="G369" s="2"/>
-    </row>
-    <row r="370" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="370" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C370" s="2"/>
       <c r="D370" s="2"/>
       <c r="E370" s="2"/>
       <c r="F370" s="2"/>
-      <c r="G370" s="2"/>
-    </row>
-    <row r="371" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="371" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C371" s="2"/>
       <c r="D371" s="2"/>
       <c r="E371" s="2"/>
       <c r="F371" s="2"/>
-      <c r="G371" s="2"/>
-    </row>
-    <row r="372" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="372" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C372" s="2"/>
       <c r="D372" s="2"/>
       <c r="E372" s="2"/>
       <c r="F372" s="2"/>
-      <c r="G372" s="2"/>
-    </row>
-    <row r="373" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="373" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C373" s="2"/>
       <c r="D373" s="2"/>
       <c r="E373" s="2"/>
       <c r="F373" s="2"/>
-      <c r="G373" s="2"/>
-    </row>
-    <row r="374" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="374" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C374" s="2"/>
       <c r="D374" s="2"/>
       <c r="E374" s="2"/>
       <c r="F374" s="2"/>
-      <c r="G374" s="2"/>
-    </row>
-    <row r="375" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="375" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C375" s="2"/>
       <c r="D375" s="2"/>
       <c r="E375" s="2"/>
       <c r="F375" s="2"/>
-      <c r="G375" s="2"/>
-    </row>
-    <row r="376" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="376" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C376" s="2"/>
       <c r="D376" s="2"/>
       <c r="E376" s="2"/>
       <c r="F376" s="2"/>
-      <c r="G376" s="2"/>
-    </row>
-    <row r="377" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="377" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C377" s="2"/>
       <c r="D377" s="2"/>
       <c r="E377" s="2"/>
       <c r="F377" s="2"/>
-      <c r="G377" s="2"/>
-    </row>
-    <row r="378" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="378" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C378" s="2"/>
       <c r="D378" s="2"/>
       <c r="E378" s="2"/>
       <c r="F378" s="2"/>
-      <c r="G378" s="2"/>
-    </row>
-    <row r="379" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="379" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C379" s="2"/>
       <c r="D379" s="2"/>
       <c r="E379" s="2"/>
       <c r="F379" s="2"/>
-      <c r="G379" s="2"/>
-    </row>
-    <row r="380" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="380" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C380" s="2"/>
       <c r="D380" s="2"/>
       <c r="E380" s="2"/>
       <c r="F380" s="2"/>
-      <c r="G380" s="2"/>
-    </row>
-    <row r="381" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="381" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C381" s="2"/>
       <c r="D381" s="2"/>
       <c r="E381" s="2"/>
       <c r="F381" s="2"/>
-      <c r="G381" s="2"/>
-    </row>
-    <row r="382" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="382" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C382" s="2"/>
       <c r="D382" s="2"/>
       <c r="E382" s="2"/>
       <c r="F382" s="2"/>
-      <c r="G382" s="2"/>
-    </row>
-    <row r="383" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="383" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C383" s="2"/>
       <c r="D383" s="2"/>
       <c r="E383" s="2"/>
       <c r="F383" s="2"/>
-      <c r="G383" s="2"/>
-    </row>
-    <row r="384" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="384" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C384" s="2"/>
       <c r="D384" s="2"/>
       <c r="E384" s="2"/>
       <c r="F384" s="2"/>
-      <c r="G384" s="2"/>
-    </row>
-    <row r="385" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="385" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C385" s="2"/>
       <c r="D385" s="2"/>
       <c r="E385" s="2"/>
       <c r="F385" s="2"/>
-      <c r="G385" s="2"/>
-    </row>
-    <row r="386" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="386" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C386" s="2"/>
       <c r="D386" s="2"/>
       <c r="E386" s="2"/>
       <c r="F386" s="2"/>
-      <c r="G386" s="2"/>
-    </row>
-    <row r="387" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="387" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C387" s="2"/>
       <c r="D387" s="2"/>
       <c r="E387" s="2"/>
       <c r="F387" s="2"/>
-      <c r="G387" s="2"/>
-    </row>
-    <row r="388" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="388" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C388" s="2"/>
       <c r="D388" s="2"/>
       <c r="E388" s="2"/>
       <c r="F388" s="2"/>
-      <c r="G388" s="2"/>
-    </row>
-    <row r="389" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="389" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C389" s="2"/>
       <c r="D389" s="2"/>
       <c r="E389" s="2"/>
       <c r="F389" s="2"/>
-      <c r="G389" s="2"/>
-    </row>
-    <row r="390" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="390" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C390" s="2"/>
       <c r="D390" s="2"/>
       <c r="E390" s="2"/>
       <c r="F390" s="2"/>
-      <c r="G390" s="2"/>
-    </row>
-    <row r="391" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="391" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C391" s="2"/>
       <c r="D391" s="2"/>
       <c r="E391" s="2"/>
       <c r="F391" s="2"/>
-      <c r="G391" s="2"/>
-    </row>
-    <row r="392" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="392" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C392" s="2"/>
       <c r="D392" s="2"/>
       <c r="E392" s="2"/>
       <c r="F392" s="2"/>
-      <c r="G392" s="2"/>
-    </row>
-    <row r="393" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="393" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C393" s="2"/>
       <c r="D393" s="2"/>
       <c r="E393" s="2"/>
       <c r="F393" s="2"/>
-      <c r="G393" s="2"/>
-    </row>
-    <row r="394" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="394" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C394" s="2"/>
       <c r="D394" s="2"/>
       <c r="E394" s="2"/>
       <c r="F394" s="2"/>
-      <c r="G394" s="2"/>
-    </row>
-    <row r="395" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="395" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C395" s="2"/>
       <c r="D395" s="2"/>
       <c r="E395" s="2"/>
       <c r="F395" s="2"/>
-      <c r="G395" s="2"/>
-    </row>
-    <row r="396" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="396" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C396" s="2"/>
       <c r="D396" s="2"/>
       <c r="E396" s="2"/>
       <c r="F396" s="2"/>
-      <c r="G396" s="2"/>
-    </row>
-    <row r="397" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="397" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C397" s="2"/>
       <c r="D397" s="2"/>
       <c r="E397" s="2"/>
       <c r="F397" s="2"/>
-      <c r="G397" s="2"/>
-    </row>
-    <row r="398" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="398" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C398" s="2"/>
       <c r="D398" s="2"/>
       <c r="E398" s="2"/>
       <c r="F398" s="2"/>
-      <c r="G398" s="2"/>
-    </row>
-    <row r="399" spans="3:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="399" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C399" s="2"/>
       <c r="D399" s="2"/>
       <c r="E399" s="2"/>
       <c r="F399" s="2"/>
-      <c r="G399" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/CF.xlsx
+++ b/CF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcelo.dilena\Desktop\CF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9065D8-01FE-415A-A0CB-E6480858FD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F921E7-7CBD-4F75-9D20-BCEEB439E82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77BA92B8-604E-40A7-9BF0-42801C1F048B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{77BA92B8-604E-40A7-9BF0-42801C1F048B}"/>
   </bookViews>
   <sheets>
     <sheet name="DashBord" sheetId="3" r:id="rId1"/>
@@ -26,23 +26,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>Descrição</t>
   </si>
@@ -102,9 +91,6 @@
   </si>
   <si>
     <t>Tx Bradesco</t>
-  </si>
-  <si>
-    <t>CPF</t>
   </si>
   <si>
     <t>Apice</t>
@@ -239,12 +225,6 @@
     <t>Shopee</t>
   </si>
   <si>
-    <t>Mercado</t>
-  </si>
-  <si>
-    <t>Uber</t>
-  </si>
-  <si>
     <t>Mercado Livre</t>
   </si>
   <si>
@@ -315,6 +295,18 @@
   </si>
   <si>
     <t>JIM.COM</t>
+  </si>
+  <si>
+    <t>Salgado</t>
+  </si>
+  <si>
+    <t>Briqueiros Julia</t>
+  </si>
+  <si>
+    <t>Almoço cupim</t>
+  </si>
+  <si>
+    <t>CPFL</t>
   </si>
 </sst>
 </file>
@@ -539,16 +531,13 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -573,6 +562,9 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -587,40 +579,40 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}" name="Tabela3" displayName="Tabela3" ref="B2:G8" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}" name="Tabela3" displayName="Tabela3" ref="B2:G8" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="B2:G8" xr:uid="{8D9630AA-324D-4C1D-8325-F4D7288F827E}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{58D126D3-568C-4239-BE5B-8ECB2D761C36}" name="DESCRIÇÃO" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{1F251373-CBF5-4FD2-A8E8-CF6062FD64F2}" name="Março" dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{58D126D3-568C-4239-BE5B-8ECB2D761C36}" name="DESCRIÇÃO" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{1F251373-CBF5-4FD2-A8E8-CF6062FD64F2}" name="Março" dataDxfId="40">
       <calculatedColumnFormula>'Nubank M'!#REF!</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{460D0C88-9D72-4E82-9E1F-AAB479149278}" name="Setembro" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{23262E17-D89E-4C5C-B21A-AA6FC4C1D40C}" name="Outubro" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{E80B29F7-DE09-4634-94B9-3F39D450DCAB}" name="Novembro" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{4129935B-5A93-47DA-AEA2-4182BB765146}" name="Dezembro" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{460D0C88-9D72-4E82-9E1F-AAB479149278}" name="Setembro" dataDxfId="39"/>
+    <tableColumn id="9" xr3:uid="{23262E17-D89E-4C5C-B21A-AA6FC4C1D40C}" name="Outubro" dataDxfId="38"/>
+    <tableColumn id="10" xr3:uid="{E80B29F7-DE09-4634-94B9-3F39D450DCAB}" name="Novembro" dataDxfId="37"/>
+    <tableColumn id="11" xr3:uid="{4129935B-5A93-47DA-AEA2-4182BB765146}" name="Dezembro" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07287E34-3C32-457D-AAFA-84A213BA4A5A}" name="Tabela13" displayName="Tabela13" ref="A2:F13" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07287E34-3C32-457D-AAFA-84A213BA4A5A}" name="Tabela13" displayName="Tabela13" ref="A2:F13" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
   <autoFilter ref="A2:F13" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{DCAB2E16-31E8-4D04-8D57-D2E5DE1C2D43}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{3D8A892C-E943-4ADC-99A7-8AD45EE19110}" name="Etiqueta"/>
-    <tableColumn id="9" xr3:uid="{238D4DE7-9EC7-4216-9399-4E8F8C6AB056}" name="Setembro" dataDxfId="41"/>
-    <tableColumn id="10" xr3:uid="{C47303D5-51F9-45CA-9893-ECCF6302049A}" name="Outubro" dataDxfId="40"/>
-    <tableColumn id="11" xr3:uid="{F025E820-7D9B-4E4E-975D-064D86088E6B}" name="Novembro" dataDxfId="39"/>
-    <tableColumn id="12" xr3:uid="{3257B979-DC12-48AF-ADD1-57C50933386F}" name="Dezembro" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{238D4DE7-9EC7-4216-9399-4E8F8C6AB056}" name="Setembro" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{C47303D5-51F9-45CA-9893-ECCF6302049A}" name="Outubro" dataDxfId="32"/>
+    <tableColumn id="11" xr3:uid="{F025E820-7D9B-4E4E-975D-064D86088E6B}" name="Novembro" dataDxfId="31"/>
+    <tableColumn id="12" xr3:uid="{3257B979-DC12-48AF-ADD1-57C50933386F}" name="Dezembro" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}" name="Tabela1" displayName="Tabela1" ref="A2:F38" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="A2:F38" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}" name="Tabela1" displayName="Tabela1" ref="A2:F46" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+  <autoFilter ref="A2:F46" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{C87F2D82-D889-44BD-B683-F742DA7A464D}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{0E8E6474-9FDD-4A00-9A17-A21C82D5D587}" name="Etiqueta"/>
@@ -649,8 +641,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{578AF0ED-5772-4022-8C30-EC0F3D1A9977}" name="Tabela167" displayName="Tabela167" ref="A2:F20" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A2:F20" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{578AF0ED-5772-4022-8C30-EC0F3D1A9977}" name="Tabela167" displayName="Tabela167" ref="A2:F40" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A2:F40" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{4228253B-5CDE-4046-B86A-62CA3FEFCC45}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{FB9FB8A1-7786-42A2-8D12-2078EB6F038D}" name="Etiqueta"/>
@@ -1073,31 +1065,31 @@
       </c>
       <c r="D4" s="2">
         <f>'Nubank M'!C1+'Nubank V'!C1+'C6'!C1+CONTAS!C1</f>
-        <v>-11568.28</v>
+        <v>-15463.66</v>
       </c>
       <c r="E4" s="2">
         <f>'Nubank M'!D1+'Nubank V'!D1+'C6'!D1+CONTAS!D1</f>
-        <v>-6930.03</v>
+        <v>-8670.93</v>
       </c>
       <c r="F4" s="2">
         <f>'Nubank M'!E1+'Nubank V'!E1+'C6'!E1+CONTAS!E1</f>
-        <v>-6207.73</v>
+        <v>-7948.6299999999992</v>
       </c>
       <c r="G4" s="2">
         <f>'Nubank M'!F1+'Nubank V'!F1+'C6'!F1+CONTAS!F1</f>
-        <v>-5859.73</v>
+        <v>-7340.7699999999995</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="2" t="e">
         <f>'Nubank M'!#REF!</f>
         <v>#REF!</v>
       </c>
       <c r="D5" s="2">
-        <v>-1400</v>
+        <v>-1000</v>
       </c>
       <c r="E5" s="2">
         <f>PREVISÃO!D3</f>
@@ -1114,14 +1106,14 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2" t="e">
         <f>'Nubank M'!#REF!</f>
         <v>#REF!</v>
       </c>
       <c r="D6" s="2">
-        <v>-600</v>
+        <v>-150</v>
       </c>
       <c r="E6" s="2">
         <f>PREVISÃO!D4</f>
@@ -1138,22 +1130,22 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2">
         <v>-4000</v>
       </c>
       <c r="D7" s="2">
-        <v>-4000</v>
+        <v>-2500</v>
       </c>
       <c r="E7" s="2">
-        <v>-4000</v>
+        <v>-2500</v>
       </c>
       <c r="F7" s="2">
-        <v>-4000</v>
+        <v>-2500</v>
       </c>
       <c r="G7" s="2">
-        <v>-4000</v>
+        <v>-2500</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -1166,19 +1158,19 @@
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>1690.7499999999982</v>
+        <v>145.36999999999898</v>
       </c>
       <c r="E8" s="4">
         <f t="shared" si="0"/>
-        <v>2745.0999999999985</v>
+        <v>2504.1999999999989</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="0"/>
-        <v>3467.3999999999996</v>
+        <v>3226.5</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
-        <v>3815.3999999999996</v>
+        <v>3834.3600000000006</v>
       </c>
     </row>
   </sheetData>
@@ -1354,7 +1346,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" s="2">
         <v>497</v>
@@ -1373,7 +1365,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -1388,7 +1380,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" s="2">
         <v>475.13</v>
@@ -3776,20 +3768,20 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
-        <f>SUM(C3:C38)</f>
-        <v>-4558.2800000000007</v>
+        <f>SUM(C3:C46)</f>
+        <v>-4793.1100000000006</v>
       </c>
       <c r="D1" s="2">
-        <f>SUM(D3:D38)</f>
-        <v>-1417.3700000000001</v>
+        <f>SUM(D3:D46)</f>
+        <v>-1470.42</v>
       </c>
       <c r="E1" s="2">
-        <f>SUM(E3:E38)</f>
-        <v>-775.06000000000006</v>
+        <f>SUM(E3:E46)</f>
+        <v>-828.11</v>
       </c>
       <c r="F1" s="2">
-        <f>SUM(F3:F38)</f>
-        <v>-775.06000000000006</v>
+        <f>SUM(F3:F46)</f>
+        <v>-828.11</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -3814,7 +3806,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" s="7">
         <v>-19.899999999999999</v>
@@ -3831,7 +3823,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" s="7">
         <v>-26.9</v>
@@ -3848,7 +3840,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" s="7">
         <v>-55.44</v>
@@ -3861,7 +3853,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="7">
         <v>-83.26</v>
@@ -3872,7 +3864,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="7">
         <v>-4</v>
@@ -3883,7 +3875,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="7">
         <v>-114.29</v>
@@ -3894,10 +3886,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="7">
         <v>-482.93</v>
@@ -3908,7 +3900,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C10" s="7">
         <v>-55.35</v>
@@ -3925,7 +3917,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C11" s="7">
         <v>-9.9</v>
@@ -3942,7 +3934,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C12" s="7">
         <v>-57.8</v>
@@ -3959,7 +3951,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C13" s="7">
         <v>-21.79</v>
@@ -3970,7 +3962,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C14" s="7">
         <v>-101.17</v>
@@ -3983,7 +3975,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15" s="7">
         <v>-5.21</v>
@@ -4000,7 +3992,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C16" s="2">
         <v>-8.6999999999999993</v>
@@ -4011,7 +4003,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C17" s="2">
         <v>-19</v>
@@ -4022,7 +4014,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C18" s="2">
         <v>-600</v>
@@ -4039,7 +4031,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C19" s="2">
         <v>-17.98</v>
@@ -4050,10 +4042,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" s="2">
         <v>-485.7</v>
@@ -4066,10 +4058,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" s="2">
         <v>-341.67</v>
@@ -4080,7 +4072,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C22" s="2">
         <v>-139</v>
@@ -4091,7 +4083,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C23" s="2">
         <v>-22</v>
@@ -4102,7 +4094,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C24" s="2">
         <v>-138.69999999999999</v>
@@ -4113,7 +4105,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C25" s="2">
         <v>-137.75</v>
@@ -4124,7 +4116,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C26" s="2">
         <v>-265.54000000000002</v>
@@ -4135,7 +4127,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C27" s="2">
         <v>-149.99</v>
@@ -4146,7 +4138,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C28" s="2">
         <v>-110.33</v>
@@ -4157,7 +4149,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C29" s="2">
         <v>-436.17</v>
@@ -4168,7 +4160,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2">
         <v>-30</v>
@@ -4179,7 +4171,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C31" s="2">
         <v>-18.940000000000001</v>
@@ -4190,7 +4182,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C32" s="2">
         <v>-107.12</v>
@@ -4201,7 +4193,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C33" s="2">
         <v>-40</v>
@@ -4212,7 +4204,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C34" s="2">
         <v>-27</v>
@@ -4223,7 +4215,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C35" s="2">
         <v>-15</v>
@@ -4234,7 +4226,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C36" s="2">
         <v>-290</v>
@@ -4245,7 +4237,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2">
         <v>-44.75</v>
@@ -4256,7 +4248,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C38" s="2">
         <v>-75</v>
@@ -4266,31 +4258,62 @@
       <c r="F38" s="2"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C39" s="2"/>
+      <c r="A39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="2">
+        <v>-21.25</v>
+      </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
+      <c r="A40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="2">
+        <v>-53.05</v>
+      </c>
+      <c r="D40" s="2">
+        <v>-53.05</v>
+      </c>
+      <c r="E40" s="2">
+        <v>-53.05</v>
+      </c>
+      <c r="F40" s="2">
+        <v>-53.05</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C41" s="2"/>
+      <c r="A41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="2">
+        <v>-130</v>
+      </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C42" s="2"/>
+      <c r="A42" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" s="2">
+        <v>-10.55</v>
+      </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C43" s="2"/>
+      <c r="A43" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="2">
+        <v>-19.98</v>
+      </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -6298,7 +6321,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="6">
         <v>-44.9</v>
@@ -6315,7 +6338,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="6">
         <v>-26.5</v>
@@ -6332,7 +6355,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="6">
         <v>-88.98</v>
@@ -6343,7 +6366,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" s="6">
         <v>-154.34</v>
@@ -6354,7 +6377,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" s="2">
         <v>-111</v>
@@ -6365,7 +6388,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2">
         <v>-84.24</v>
@@ -6376,7 +6399,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -6384,27 +6407,18 @@
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>65</v>
-      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>66</v>
-      </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>66</v>
-      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -8820,7 +8834,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37F3A864-C585-421C-A8F8-7E679BFCCC8A}">
-  <dimension ref="A1:F390"/>
+  <dimension ref="A1:F410"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" customWidth="1"/>
@@ -8830,20 +8844,20 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
-        <f>SUM(C3:C49)</f>
-        <v>-1919.0700000000002</v>
+        <f>SUM(C3:C69)</f>
+        <v>-5579.62</v>
       </c>
       <c r="D1" s="2">
-        <f>SUM(D3:D49)</f>
-        <v>-860.29</v>
+        <f>SUM(D3:D69)</f>
+        <v>-2548.14</v>
       </c>
       <c r="E1" s="2">
-        <f>SUM(E3:E49)</f>
-        <v>-780.3</v>
+        <f>SUM(E3:E69)</f>
+        <v>-2468.1499999999996</v>
       </c>
       <c r="F1" s="2">
-        <f>SUM(F3:F49)</f>
-        <v>-780.3</v>
+        <f>SUM(F3:F69)</f>
+        <v>-2208.29</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -8868,7 +8882,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" s="7">
         <v>-176.6</v>
@@ -8879,7 +8893,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" s="7">
         <v>-149.99</v>
@@ -8896,7 +8910,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="7">
         <v>-79.989999999999995</v>
@@ -8909,7 +8923,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="7">
         <v>-497.45</v>
@@ -8920,7 +8934,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="7">
         <v>-160</v>
@@ -8937,7 +8951,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="7">
         <v>-31.9</v>
@@ -8954,7 +8968,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="7">
         <v>-293</v>
@@ -8971,10 +8985,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="7">
-        <v>-131.54</v>
+        <v>-131.51</v>
       </c>
       <c r="D10" s="2">
         <v>-131.51</v>
@@ -8988,7 +9002,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C11" s="7">
         <v>-13.9</v>
@@ -9005,7 +9019,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C12" s="7">
         <v>-173.3</v>
@@ -9016,7 +9030,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C13" s="7">
         <v>-211.4</v>
@@ -9026,133 +9040,191 @@
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C14" s="2"/>
+      <c r="C14" s="7">
+        <v>-17.5</v>
+      </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="C15" s="7">
+        <v>-86.66</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-86.66</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-86.66</v>
+      </c>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="C16" s="7">
+        <v>-173.2</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-173.2</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-173.2</v>
+      </c>
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="2"/>
+      <c r="C17" s="7">
+        <v>-30</v>
+      </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C18" s="2"/>
+      <c r="C18" s="7">
+        <v>-101.9</v>
+      </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C19" s="2"/>
+      <c r="C19" s="7">
+        <v>-10</v>
+      </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C20" s="2"/>
+      <c r="C20" s="7">
+        <v>-220</v>
+      </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C21" s="2"/>
+      <c r="C21" s="7">
+        <v>-145</v>
+      </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C22" s="2"/>
+      <c r="C22" s="7">
+        <v>-138.6</v>
+      </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C23" s="2"/>
+      <c r="C23" s="7">
+        <v>-36.9</v>
+      </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C24" s="2"/>
+      <c r="C24" s="7">
+        <v>-68.95</v>
+      </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C25" s="2"/>
+      <c r="C25" s="7">
+        <v>-332.97</v>
+      </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C26" s="2"/>
+      <c r="C26" s="7">
+        <v>-45</v>
+      </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C27" s="2"/>
+      <c r="C27" s="7">
+        <v>-108</v>
+      </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C28" s="2"/>
+      <c r="C28" s="7">
+        <v>-40.67</v>
+      </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C29" s="2"/>
+      <c r="C29" s="7">
+        <v>-20</v>
+      </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C30" s="2"/>
+      <c r="C30" s="7">
+        <v>-151.94999999999999</v>
+      </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
     <row r="31" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
+      <c r="C31" s="7">
+        <v>-1427.99</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-1427.99</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1427.99</v>
+      </c>
+      <c r="F31" s="7">
+        <v>-1427.99</v>
+      </c>
     </row>
     <row r="32" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C32" s="2"/>
+      <c r="C32" s="7">
+        <v>-66.5</v>
+      </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
     </row>
     <row r="33" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C33" s="2"/>
+      <c r="C33" s="7">
+        <v>-259.8</v>
+      </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
     </row>
     <row r="34" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C34" s="2"/>
+      <c r="C34" s="2">
+        <v>-129</v>
+      </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
     </row>
     <row r="35" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C35" s="2"/>
+      <c r="C35" s="2">
+        <v>-49.99</v>
+      </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -11286,6 +11358,126 @@
       <c r="D390" s="2"/>
       <c r="E390" s="2"/>
       <c r="F390" s="2"/>
+    </row>
+    <row r="391" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C391" s="2"/>
+      <c r="D391" s="2"/>
+      <c r="E391" s="2"/>
+      <c r="F391" s="2"/>
+    </row>
+    <row r="392" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C392" s="2"/>
+      <c r="D392" s="2"/>
+      <c r="E392" s="2"/>
+      <c r="F392" s="2"/>
+    </row>
+    <row r="393" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C393" s="2"/>
+      <c r="D393" s="2"/>
+      <c r="E393" s="2"/>
+      <c r="F393" s="2"/>
+    </row>
+    <row r="394" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C394" s="2"/>
+      <c r="D394" s="2"/>
+      <c r="E394" s="2"/>
+      <c r="F394" s="2"/>
+    </row>
+    <row r="395" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C395" s="2"/>
+      <c r="D395" s="2"/>
+      <c r="E395" s="2"/>
+      <c r="F395" s="2"/>
+    </row>
+    <row r="396" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C396" s="2"/>
+      <c r="D396" s="2"/>
+      <c r="E396" s="2"/>
+      <c r="F396" s="2"/>
+    </row>
+    <row r="397" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C397" s="2"/>
+      <c r="D397" s="2"/>
+      <c r="E397" s="2"/>
+      <c r="F397" s="2"/>
+    </row>
+    <row r="398" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C398" s="2"/>
+      <c r="D398" s="2"/>
+      <c r="E398" s="2"/>
+      <c r="F398" s="2"/>
+    </row>
+    <row r="399" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C399" s="2"/>
+      <c r="D399" s="2"/>
+      <c r="E399" s="2"/>
+      <c r="F399" s="2"/>
+    </row>
+    <row r="400" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C400" s="2"/>
+      <c r="D400" s="2"/>
+      <c r="E400" s="2"/>
+      <c r="F400" s="2"/>
+    </row>
+    <row r="401" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C401" s="2"/>
+      <c r="D401" s="2"/>
+      <c r="E401" s="2"/>
+      <c r="F401" s="2"/>
+    </row>
+    <row r="402" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C402" s="2"/>
+      <c r="D402" s="2"/>
+      <c r="E402" s="2"/>
+      <c r="F402" s="2"/>
+    </row>
+    <row r="403" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C403" s="2"/>
+      <c r="D403" s="2"/>
+      <c r="E403" s="2"/>
+      <c r="F403" s="2"/>
+    </row>
+    <row r="404" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C404" s="2"/>
+      <c r="D404" s="2"/>
+      <c r="E404" s="2"/>
+      <c r="F404" s="2"/>
+    </row>
+    <row r="405" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C405" s="2"/>
+      <c r="D405" s="2"/>
+      <c r="E405" s="2"/>
+      <c r="F405" s="2"/>
+    </row>
+    <row r="406" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C406" s="2"/>
+      <c r="D406" s="2"/>
+      <c r="E406" s="2"/>
+      <c r="F406" s="2"/>
+    </row>
+    <row r="407" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C407" s="2"/>
+      <c r="D407" s="2"/>
+      <c r="E407" s="2"/>
+      <c r="F407" s="2"/>
+    </row>
+    <row r="408" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C408" s="2"/>
+      <c r="D408" s="2"/>
+      <c r="E408" s="2"/>
+      <c r="F408" s="2"/>
+    </row>
+    <row r="409" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C409" s="2"/>
+      <c r="D409" s="2"/>
+      <c r="E409" s="2"/>
+      <c r="F409" s="2"/>
+    </row>
+    <row r="410" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C410" s="2"/>
+      <c r="D410" s="2"/>
+      <c r="E410" s="2"/>
+      <c r="F410" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -11379,7 +11571,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="C5" s="2">
         <v>-345.58</v>
@@ -11430,7 +11622,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2">
         <v>-37.47</v>
@@ -11447,7 +11639,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="2">
         <v>-44.55</v>
@@ -11464,7 +11656,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2">
         <v>-109.79</v>
@@ -11481,7 +11673,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2">
         <v>-221.48</v>
@@ -11498,7 +11690,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -11507,7 +11699,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="2">
         <v>-180</v>
@@ -11524,7 +11716,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2">
         <v>-660</v>
@@ -11541,7 +11733,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="2">
         <v>-40</v>
@@ -11558,7 +11750,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -11567,7 +11759,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -11576,7 +11768,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" s="2">
         <v>-130</v>
@@ -11593,7 +11785,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="2">
         <v>-156.37</v>
@@ -11616,7 +11808,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" s="2">
         <v>-1276</v>
@@ -14028,7 +14220,7 @@
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:F1" si="0">SUM(C3:C58)</f>
-        <v>-2000</v>
+        <v>-1450</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
@@ -14068,7 +14260,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="2">
-        <v>-1400</v>
+        <v>-1000</v>
       </c>
       <c r="D3" s="2">
         <v>-2000</v>
@@ -14082,10 +14274,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" s="2">
-        <v>-600</v>
+        <v>-450</v>
       </c>
       <c r="D4" s="2">
         <v>-600</v>

--- a/CF.xlsx
+++ b/CF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F921E7-7CBD-4F75-9D20-BCEEB439E82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B9A787-72DB-44D2-8201-7B9707422BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{77BA92B8-604E-40A7-9BF0-42801C1F048B}"/>
   </bookViews>
@@ -1113,7 +1113,7 @@
         <v>#REF!</v>
       </c>
       <c r="D6" s="2">
-        <v>-150</v>
+        <v>-450</v>
       </c>
       <c r="E6" s="2">
         <f>PREVISÃO!D4</f>
@@ -1136,16 +1136,16 @@
         <v>-4000</v>
       </c>
       <c r="D7" s="2">
-        <v>-2500</v>
+        <v>-2000</v>
       </c>
       <c r="E7" s="2">
         <v>-2500</v>
       </c>
       <c r="F7" s="2">
-        <v>-2500</v>
+        <v>-3000</v>
       </c>
       <c r="G7" s="2">
-        <v>-2500</v>
+        <v>-3000</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>145.36999999999898</v>
+        <v>345.36999999999898</v>
       </c>
       <c r="E8" s="4">
         <f t="shared" si="0"/>
@@ -1166,11 +1166,11 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" si="0"/>
-        <v>3226.5</v>
+        <v>2726.5</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
-        <v>3834.3600000000006</v>
+        <v>3334.3600000000006</v>
       </c>
     </row>
   </sheetData>

--- a/CF.xlsx
+++ b/CF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B9A787-72DB-44D2-8201-7B9707422BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF48319A-90F3-4FA3-AB17-9A43F7048B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{77BA92B8-604E-40A7-9BF0-42801C1F048B}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="93">
   <si>
     <t>Descrição</t>
   </si>
@@ -147,9 +147,6 @@
     <t>HAVAN</t>
   </si>
   <si>
-    <t>MERCADO LIVRE</t>
-  </si>
-  <si>
     <t>Combustivel</t>
   </si>
   <si>
@@ -220,9 +217,6 @@
   </si>
   <si>
     <t>Riachuelo</t>
-  </si>
-  <si>
-    <t>Shopee</t>
   </si>
   <si>
     <t>Mercado Livre</t>
@@ -308,6 +302,15 @@
   <si>
     <t>CPFL</t>
   </si>
+  <si>
+    <t>Uber</t>
+  </si>
+  <si>
+    <t>LIVRARIA</t>
+  </si>
+  <si>
+    <t>BACIO DI LATTE</t>
+  </si>
 </sst>
 </file>
 
@@ -375,7 +378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -397,7 +400,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -611,8 +619,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}" name="Tabela1" displayName="Tabela1" ref="A2:F46" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="A2:F46" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}" name="Tabela1" displayName="Tabela1" ref="A2:F50" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+  <autoFilter ref="A2:F50" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{C87F2D82-D889-44BD-B683-F742DA7A464D}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{0E8E6474-9FDD-4A00-9A17-A21C82D5D587}" name="Etiqueta"/>
@@ -626,8 +634,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8C70EA2E-3E0C-43D6-9BC8-DC48D3EA5D71}" name="Tabela16" displayName="Tabela16" ref="A2:F21" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
-  <autoFilter ref="A2:F21" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8C70EA2E-3E0C-43D6-9BC8-DC48D3EA5D71}" name="Tabela16" displayName="Tabela16" ref="A2:F20" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+  <autoFilter ref="A2:F20" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{22A6603B-5472-41A0-9FE9-85A4D0D9BBEE}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{06CEE4B6-AC33-4E62-9594-04D875A198B2}" name="Etiqueta"/>
@@ -641,8 +649,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{578AF0ED-5772-4022-8C30-EC0F3D1A9977}" name="Tabela167" displayName="Tabela167" ref="A2:F40" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A2:F40" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{578AF0ED-5772-4022-8C30-EC0F3D1A9977}" name="Tabela167" displayName="Tabela167" ref="A2:F53" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A2:F53" xr:uid="{3FE25307-0E30-41AB-976C-B551AF53C7FB}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{4228253B-5CDE-4046-B86A-62CA3FEFCC45}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{FB9FB8A1-7786-42A2-8D12-2078EB6F038D}" name="Etiqueta"/>
@@ -1065,31 +1073,31 @@
       </c>
       <c r="D4" s="2">
         <f>'Nubank M'!C1+'Nubank V'!C1+'C6'!C1+CONTAS!C1</f>
-        <v>-15463.66</v>
+        <v>-16285.349999999999</v>
       </c>
       <c r="E4" s="2">
         <f>'Nubank M'!D1+'Nubank V'!D1+'C6'!D1+CONTAS!D1</f>
-        <v>-8670.93</v>
+        <v>-8674.3299999999981</v>
       </c>
       <c r="F4" s="2">
         <f>'Nubank M'!E1+'Nubank V'!E1+'C6'!E1+CONTAS!E1</f>
-        <v>-7948.6299999999992</v>
+        <v>-7952.0299999999988</v>
       </c>
       <c r="G4" s="2">
         <f>'Nubank M'!F1+'Nubank V'!F1+'C6'!F1+CONTAS!F1</f>
-        <v>-7340.7699999999995</v>
+        <v>-7344.1699999999992</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="e">
         <f>'Nubank M'!#REF!</f>
         <v>#REF!</v>
       </c>
       <c r="D5" s="2">
-        <v>-1000</v>
+        <v>-800</v>
       </c>
       <c r="E5" s="2">
         <f>PREVISÃO!D3</f>
@@ -1106,14 +1114,14 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="e">
         <f>'Nubank M'!#REF!</f>
         <v>#REF!</v>
       </c>
       <c r="D6" s="2">
-        <v>-450</v>
+        <v>-300</v>
       </c>
       <c r="E6" s="2">
         <f>PREVISÃO!D4</f>
@@ -1130,13 +1138,13 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2">
         <v>-4000</v>
       </c>
       <c r="D7" s="2">
-        <v>-2000</v>
+        <v>-1500</v>
       </c>
       <c r="E7" s="2">
         <v>-2500</v>
@@ -1158,19 +1166,19 @@
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>345.36999999999898</v>
+        <v>373.68000000000029</v>
       </c>
       <c r="E8" s="4">
         <f t="shared" si="0"/>
-        <v>2504.1999999999989</v>
+        <v>2500.8000000000011</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="0"/>
-        <v>2726.5</v>
+        <v>2723.1000000000004</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
-        <v>3334.3600000000006</v>
+        <v>3330.9599999999991</v>
       </c>
     </row>
   </sheetData>
@@ -1210,12 +1218,7 @@
         <f t="shared" si="0"/>
         <v>16275.13</v>
       </c>
-      <c r="N1" s="8">
-        <v>17818.68</v>
-      </c>
-      <c r="P1" s="8">
-        <v>4760</v>
-      </c>
+      <c r="P1" s="8"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -1236,12 +1239,7 @@
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="8">
-        <v>-3433.21</v>
-      </c>
-      <c r="P2" s="8">
-        <v>497</v>
-      </c>
+      <c r="P2" s="8"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1259,12 +1257,7 @@
       <c r="F3" s="2">
         <v>11000</v>
       </c>
-      <c r="N3" s="8">
-        <v>-6857.97</v>
-      </c>
-      <c r="P3" s="8">
-        <v>-574.97</v>
-      </c>
+      <c r="P3" s="8"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1282,12 +1275,7 @@
       <c r="F4" s="2">
         <v>4800</v>
       </c>
-      <c r="N4" s="8">
-        <v>-574.97</v>
-      </c>
-      <c r="P4" s="8">
-        <v>-6955.97</v>
-      </c>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1302,12 +1290,7 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="N5" s="8">
-        <v>-4099.82</v>
-      </c>
-      <c r="P5" s="8">
-        <v>-1276</v>
-      </c>
+      <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1322,12 +1305,7 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="N6" s="8">
-        <v>1000</v>
-      </c>
-      <c r="P6" s="8">
-        <v>-3850</v>
-      </c>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1346,7 +1324,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2">
         <v>497</v>
@@ -1354,18 +1332,11 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="N8" s="8">
-        <f>SUM(N1:N7)</f>
-        <v>3852.7100000000009</v>
-      </c>
-      <c r="P8" s="8">
-        <f>SUM(P1:P7)</f>
-        <v>-7399.9400000000005</v>
-      </c>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -1380,7 +1351,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10" s="2">
         <v>475.13</v>
@@ -3758,7 +3729,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D82C02-C94F-4ED8-8A51-D9DB6848ED02}">
-  <dimension ref="A1:F367"/>
+  <dimension ref="A1:F371"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" customWidth="1"/>
@@ -3768,19 +3739,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
-        <f>SUM(C3:C46)</f>
-        <v>-4793.1100000000006</v>
+        <f>SUM(C3:C50)</f>
+        <v>-4747.8600000000006</v>
       </c>
       <c r="D1" s="2">
-        <f>SUM(D3:D46)</f>
+        <f>SUM(D3:D50)</f>
         <v>-1470.42</v>
       </c>
       <c r="E1" s="2">
-        <f>SUM(E3:E46)</f>
+        <f>SUM(E3:E50)</f>
         <v>-828.11</v>
       </c>
       <c r="F1" s="2">
-        <f>SUM(F3:F46)</f>
+        <f>SUM(F3:F50)</f>
         <v>-828.11</v>
       </c>
     </row>
@@ -3806,7 +3777,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="7">
         <v>-19.899999999999999</v>
@@ -3823,7 +3794,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="7">
         <v>-26.9</v>
@@ -3840,7 +3811,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="7">
         <v>-55.44</v>
@@ -3853,7 +3824,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="7">
         <v>-83.26</v>
@@ -3864,7 +3835,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="7">
         <v>-4</v>
@@ -3875,7 +3846,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" s="7">
         <v>-114.29</v>
@@ -3886,12 +3857,12 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="7">
+        <v>55</v>
+      </c>
+      <c r="C9" s="9">
         <v>-482.93</v>
       </c>
       <c r="D9" s="2"/>
@@ -3900,7 +3871,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C10" s="7">
         <v>-55.35</v>
@@ -3917,7 +3888,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C11" s="7">
         <v>-9.9</v>
@@ -3934,7 +3905,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" s="7">
         <v>-57.8</v>
@@ -3951,9 +3922,9 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="7">
+        <v>62</v>
+      </c>
+      <c r="C13" s="9">
         <v>-21.79</v>
       </c>
       <c r="D13" s="2"/>
@@ -3962,9 +3933,9 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="7">
+        <v>67</v>
+      </c>
+      <c r="C14" s="9">
         <v>-101.17</v>
       </c>
       <c r="D14" s="2">
@@ -3975,7 +3946,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="7">
         <v>-5.21</v>
@@ -3992,9 +3963,9 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="2">
+        <v>83</v>
+      </c>
+      <c r="C16" s="7">
         <v>-8.6999999999999993</v>
       </c>
       <c r="D16" s="2"/>
@@ -4003,9 +3974,9 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="2">
+        <v>82</v>
+      </c>
+      <c r="C17" s="7">
         <v>-19</v>
       </c>
       <c r="D17" s="2"/>
@@ -4014,9 +3985,9 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="2">
+        <v>81</v>
+      </c>
+      <c r="C18" s="7">
         <v>-600</v>
       </c>
       <c r="D18" s="2">
@@ -4031,9 +4002,9 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="2">
+        <v>80</v>
+      </c>
+      <c r="C19" s="7">
         <v>-17.98</v>
       </c>
       <c r="D19" s="2"/>
@@ -4042,12 +4013,12 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="2">
+        <v>55</v>
+      </c>
+      <c r="C20" s="7">
         <v>-485.7</v>
       </c>
       <c r="D20" s="2">
@@ -4058,12 +4029,12 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="2">
+        <v>56</v>
+      </c>
+      <c r="C21" s="7">
         <v>-341.67</v>
       </c>
       <c r="D21" s="2"/>
@@ -4072,9 +4043,9 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" s="2">
+        <v>78</v>
+      </c>
+      <c r="C22" s="7">
         <v>-139</v>
       </c>
       <c r="D22" s="2"/>
@@ -4083,9 +4054,9 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="2">
+        <v>77</v>
+      </c>
+      <c r="C23" s="7">
         <v>-22</v>
       </c>
       <c r="D23" s="2"/>
@@ -4094,9 +4065,9 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="2">
+        <v>74</v>
+      </c>
+      <c r="C24" s="7">
         <v>-138.69999999999999</v>
       </c>
       <c r="D24" s="2"/>
@@ -4105,9 +4076,9 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="2">
+        <v>76</v>
+      </c>
+      <c r="C25" s="7">
         <v>-137.75</v>
       </c>
       <c r="D25" s="2"/>
@@ -4116,9 +4087,9 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="2">
+        <v>73</v>
+      </c>
+      <c r="C26" s="7">
         <v>-265.54000000000002</v>
       </c>
       <c r="D26" s="2"/>
@@ -4127,9 +4098,9 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="2">
+        <v>75</v>
+      </c>
+      <c r="C27" s="7">
         <v>-149.99</v>
       </c>
       <c r="D27" s="2"/>
@@ -4138,9 +4109,9 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="2">
+        <v>74</v>
+      </c>
+      <c r="C28" s="7">
         <v>-110.33</v>
       </c>
       <c r="D28" s="2"/>
@@ -4149,9 +4120,9 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="2">
+        <v>73</v>
+      </c>
+      <c r="C29" s="7">
         <v>-436.17</v>
       </c>
       <c r="D29" s="2"/>
@@ -4160,9 +4131,9 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="2">
+        <v>46</v>
+      </c>
+      <c r="C30" s="7">
         <v>-30</v>
       </c>
       <c r="D30" s="2"/>
@@ -4171,9 +4142,9 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="2">
+        <v>73</v>
+      </c>
+      <c r="C31" s="7">
         <v>-18.940000000000001</v>
       </c>
       <c r="D31" s="2"/>
@@ -4182,9 +4153,9 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="2">
+        <v>72</v>
+      </c>
+      <c r="C32" s="7">
         <v>-107.12</v>
       </c>
       <c r="D32" s="2"/>
@@ -4193,9 +4164,9 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="2">
+        <v>71</v>
+      </c>
+      <c r="C33" s="7">
         <v>-40</v>
       </c>
       <c r="D33" s="2"/>
@@ -4204,9 +4175,9 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" s="2">
+        <v>71</v>
+      </c>
+      <c r="C34" s="7">
         <v>-27</v>
       </c>
       <c r="D34" s="2"/>
@@ -4215,9 +4186,9 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" s="2">
+        <v>71</v>
+      </c>
+      <c r="C35" s="7">
         <v>-15</v>
       </c>
       <c r="D35" s="2"/>
@@ -4226,9 +4197,9 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="2">
+        <v>69</v>
+      </c>
+      <c r="C36" s="7">
         <v>-290</v>
       </c>
       <c r="D36" s="2"/>
@@ -4237,9 +4208,9 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="2">
+        <v>70</v>
+      </c>
+      <c r="C37" s="7">
         <v>-44.75</v>
       </c>
       <c r="D37" s="2"/>
@@ -4248,9 +4219,9 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="2">
+        <v>68</v>
+      </c>
+      <c r="C38" s="7">
         <v>-75</v>
       </c>
       <c r="D38" s="2"/>
@@ -4259,9 +4230,9 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="2">
+        <v>86</v>
+      </c>
+      <c r="C39" s="7">
         <v>-21.25</v>
       </c>
       <c r="D39" s="2"/>
@@ -4270,9 +4241,9 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>89</v>
-      </c>
-      <c r="C40" s="2">
+        <v>87</v>
+      </c>
+      <c r="C40" s="7">
         <v>-53.05</v>
       </c>
       <c r="D40" s="2">
@@ -4287,9 +4258,9 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" s="2">
+        <v>88</v>
+      </c>
+      <c r="C41" s="7">
         <v>-130</v>
       </c>
       <c r="D41" s="2"/>
@@ -4298,9 +4269,9 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" s="2">
+        <v>73</v>
+      </c>
+      <c r="C42" s="7">
         <v>-10.55</v>
       </c>
       <c r="D42" s="2"/>
@@ -4309,9 +4280,9 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" s="2">
+        <v>70</v>
+      </c>
+      <c r="C43" s="7">
         <v>-19.98</v>
       </c>
       <c r="D43" s="2"/>
@@ -4319,19 +4290,31 @@
       <c r="F43" s="2"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C44" s="2"/>
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-124.8</v>
+      </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C45" s="2"/>
+      <c r="A45" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-29.95</v>
+      </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C46" s="2"/>
+      <c r="C46" s="2">
+        <v>200</v>
+      </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -6261,6 +6244,30 @@
       <c r="D367" s="2"/>
       <c r="E367" s="2"/>
       <c r="F367" s="2"/>
+    </row>
+    <row r="368" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C368" s="2"/>
+      <c r="D368" s="2"/>
+      <c r="E368" s="2"/>
+      <c r="F368" s="2"/>
+    </row>
+    <row r="369" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C369" s="2"/>
+      <c r="D369" s="2"/>
+      <c r="E369" s="2"/>
+      <c r="F369" s="2"/>
+    </row>
+    <row r="370" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C370" s="2"/>
+      <c r="D370" s="2"/>
+      <c r="E370" s="2"/>
+      <c r="F370" s="2"/>
+    </row>
+    <row r="371" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C371" s="2"/>
+      <c r="D371" s="2"/>
+      <c r="E371" s="2"/>
+      <c r="F371" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -6273,7 +6280,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F01D07ED-902F-4033-9A87-355F7134C802}">
-  <dimension ref="A1:F412"/>
+  <dimension ref="A1:F411"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" customWidth="1"/>
@@ -6283,20 +6290,20 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
-        <f t="shared" ref="C1:F1" si="0">SUM(C3:C71)</f>
-        <v>-509.96000000000004</v>
+        <f t="shared" ref="C1:F1" si="0">SUM(C3:C70)</f>
+        <v>-426.46999999999997</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>-71.400000000000006</v>
+        <v>-74.8</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
-        <v>-71.400000000000006</v>
+        <v>-74.8</v>
       </c>
       <c r="F1" s="2">
         <f t="shared" si="0"/>
-        <v>-71.400000000000006</v>
+        <v>-74.8</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6323,7 +6330,7 @@
       <c r="A3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="10">
         <v>-44.9</v>
       </c>
       <c r="D3" s="6">
@@ -6340,47 +6347,47 @@
       <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="6">
-        <v>-26.5</v>
+      <c r="C4" s="10">
+        <v>-29.9</v>
       </c>
       <c r="D4" s="6">
-        <v>-26.5</v>
+        <v>-29.9</v>
       </c>
       <c r="E4" s="6">
-        <v>-26.5</v>
+        <v>-29.9</v>
       </c>
       <c r="F4" s="6">
-        <v>-26.5</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="6">
-        <v>-88.98</v>
+      <c r="A5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="10">
+        <v>-154.34</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="6">
-        <v>-154.34</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-111</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="2">
-        <v>-111</v>
+      <c r="C7" s="7">
+        <v>-84.24</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -6388,19 +6395,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="2">
-        <v>-84.24</v>
+        <v>90</v>
+      </c>
+      <c r="C8" s="7">
+        <v>-2.09</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -8817,12 +8821,6 @@
       <c r="D411" s="2"/>
       <c r="E411" s="2"/>
       <c r="F411" s="2"/>
-    </row>
-    <row r="412" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C412" s="2"/>
-      <c r="D412" s="2"/>
-      <c r="E412" s="2"/>
-      <c r="F412" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -8834,7 +8832,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37F3A864-C585-421C-A8F8-7E679BFCCC8A}">
-  <dimension ref="A1:F410"/>
+  <dimension ref="A1:F423"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" customWidth="1"/>
@@ -8844,19 +8842,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
-        <f>SUM(C3:C69)</f>
-        <v>-5579.62</v>
+        <f>SUM(C3:C82)</f>
+        <v>-6609.4699999999993</v>
       </c>
       <c r="D1" s="2">
-        <f>SUM(D3:D69)</f>
+        <f>SUM(D3:D82)</f>
         <v>-2548.14</v>
       </c>
       <c r="E1" s="2">
-        <f>SUM(E3:E69)</f>
+        <f>SUM(E3:E82)</f>
         <v>-2468.1499999999996</v>
       </c>
       <c r="F1" s="2">
-        <f>SUM(F3:F69)</f>
+        <f>SUM(F3:F82)</f>
         <v>-2208.29</v>
       </c>
     </row>
@@ -8882,9 +8880,9 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="7">
+        <v>44</v>
+      </c>
+      <c r="C3" s="9">
         <v>-176.6</v>
       </c>
       <c r="D3" s="2"/>
@@ -8893,7 +8891,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="7">
         <v>-149.99</v>
@@ -8912,7 +8910,7 @@
       <c r="A5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="9">
         <v>-79.989999999999995</v>
       </c>
       <c r="D5" s="2">
@@ -8923,9 +8921,9 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="7">
+        <v>43</v>
+      </c>
+      <c r="C6" s="9">
         <v>-497.45</v>
       </c>
       <c r="D6" s="2"/>
@@ -8934,7 +8932,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="7">
         <v>-160</v>
@@ -8987,7 +8985,7 @@
       <c r="A10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="9">
         <v>-131.51</v>
       </c>
       <c r="D10" s="2">
@@ -9002,9 +9000,9 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="7">
+        <v>63</v>
+      </c>
+      <c r="C11" s="9">
         <v>-13.9</v>
       </c>
       <c r="D11" s="2">
@@ -9019,9 +9017,9 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="7">
+        <v>84</v>
+      </c>
+      <c r="C12" s="9">
         <v>-173.3</v>
       </c>
       <c r="D12" s="2"/>
@@ -9030,9 +9028,9 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="7">
+        <v>85</v>
+      </c>
+      <c r="C13" s="9">
         <v>-211.4</v>
       </c>
       <c r="D13" s="2"/>
@@ -9214,7 +9212,7 @@
       <c r="F33" s="2"/>
     </row>
     <row r="34" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C34" s="2">
+      <c r="C34" s="7">
         <v>-129</v>
       </c>
       <c r="D34" s="2"/>
@@ -9222,7 +9220,7 @@
       <c r="F34" s="2"/>
     </row>
     <row r="35" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C35" s="2">
+      <c r="C35" s="7">
         <v>-49.99</v>
       </c>
       <c r="D35" s="2"/>
@@ -9230,85 +9228,109 @@
       <c r="F35" s="2"/>
     </row>
     <row r="36" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C36" s="2"/>
+      <c r="C36" s="7">
+        <v>-262.2</v>
+      </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
     </row>
     <row r="37" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C37" s="2"/>
+      <c r="C37" s="7">
+        <v>-13</v>
+      </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
     </row>
     <row r="38" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C38" s="2"/>
+      <c r="C38" s="7">
+        <v>-74.989999999999995</v>
+      </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
     </row>
     <row r="39" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C39" s="2"/>
+      <c r="C39" s="7">
+        <v>-239.9</v>
+      </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
     </row>
     <row r="40" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C40" s="2"/>
+      <c r="C40" s="7">
+        <v>-100</v>
+      </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
     </row>
     <row r="41" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C41" s="2"/>
+      <c r="C41" s="7">
+        <v>-32.159999999999997</v>
+      </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
     </row>
     <row r="42" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C42" s="2"/>
+      <c r="C42" s="7">
+        <v>-68.47</v>
+      </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
     </row>
     <row r="43" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C43" s="2"/>
+      <c r="C43" s="7">
+        <v>-73.47</v>
+      </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
     </row>
     <row r="44" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C44" s="2"/>
+      <c r="C44" s="7">
+        <v>-22.22</v>
+      </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
     </row>
     <row r="45" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C45" s="2"/>
+      <c r="C45" s="7">
+        <v>-17.899999999999999</v>
+      </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
     <row r="46" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C46" s="2"/>
+      <c r="C46" s="7">
+        <v>-28.03</v>
+      </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
     </row>
     <row r="47" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C47" s="2"/>
+      <c r="C47" s="7">
+        <v>-97.51</v>
+      </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
     </row>
     <row r="48" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C48" s="2"/>
+      <c r="C48" s="9"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
     </row>
     <row r="49" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C49" s="2"/>
+      <c r="C49" s="9"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -11478,6 +11500,84 @@
       <c r="D410" s="2"/>
       <c r="E410" s="2"/>
       <c r="F410" s="2"/>
+    </row>
+    <row r="411" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C411" s="2"/>
+      <c r="D411" s="2"/>
+      <c r="E411" s="2"/>
+      <c r="F411" s="2"/>
+    </row>
+    <row r="412" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C412" s="2"/>
+      <c r="D412" s="2"/>
+      <c r="E412" s="2"/>
+      <c r="F412" s="2"/>
+    </row>
+    <row r="413" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C413" s="2"/>
+      <c r="D413" s="2"/>
+      <c r="E413" s="2"/>
+      <c r="F413" s="2"/>
+    </row>
+    <row r="414" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C414" s="2"/>
+      <c r="D414" s="2"/>
+      <c r="E414" s="2"/>
+      <c r="F414" s="2"/>
+    </row>
+    <row r="415" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C415" s="2"/>
+      <c r="D415" s="2"/>
+      <c r="E415" s="2"/>
+      <c r="F415" s="2"/>
+    </row>
+    <row r="416" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C416" s="2"/>
+      <c r="D416" s="2"/>
+      <c r="E416" s="2"/>
+      <c r="F416" s="2"/>
+    </row>
+    <row r="417" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C417" s="2"/>
+      <c r="D417" s="2"/>
+      <c r="E417" s="2"/>
+      <c r="F417" s="2"/>
+    </row>
+    <row r="418" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C418" s="2"/>
+      <c r="D418" s="2"/>
+      <c r="E418" s="2"/>
+      <c r="F418" s="2"/>
+    </row>
+    <row r="419" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C419" s="2"/>
+      <c r="D419" s="2"/>
+      <c r="E419" s="2"/>
+      <c r="F419" s="2"/>
+    </row>
+    <row r="420" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C420" s="2"/>
+      <c r="D420" s="2"/>
+      <c r="E420" s="2"/>
+      <c r="F420" s="2"/>
+    </row>
+    <row r="421" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C421" s="2"/>
+      <c r="D421" s="2"/>
+      <c r="E421" s="2"/>
+      <c r="F421" s="2"/>
+    </row>
+    <row r="422" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C422" s="2"/>
+      <c r="D422" s="2"/>
+      <c r="E422" s="2"/>
+      <c r="F422" s="2"/>
+    </row>
+    <row r="423" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C423" s="2"/>
+      <c r="D423" s="2"/>
+      <c r="E423" s="2"/>
+      <c r="F423" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -11500,7 +11600,7 @@
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C1" s="2">
         <f t="shared" ref="C1:F1" si="0">SUM(C3:C76)</f>
-        <v>-4580.9699999999993</v>
+        <v>-4501.5499999999993</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
@@ -11571,10 +11671,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C5" s="2">
-        <v>-345.58</v>
+        <v>-266.16000000000003</v>
       </c>
       <c r="D5" s="2">
         <v>-345.58</v>
@@ -11808,7 +11908,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" s="2">
         <v>-1276</v>
@@ -14274,7 +14374,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2">
         <v>-450</v>
